--- a/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
+++ b/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
@@ -7,14 +7,15 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tasks" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Steps" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Handover" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tasks" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Steps" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tasks'!$A$2:$K$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Steps'!$A$1:$I$129</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tasks'!$A$2:$K$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Steps'!$A$1:$I$129</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -25,7 +26,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -66,8 +67,34 @@
       <color rgb="FF808080"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="10"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -99,8 +126,23 @@
         <fgColor rgb="FFFCE5CD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -123,11 +165,16 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00D9E2F3"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -165,6 +212,18 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -923,6 +982,194 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:B16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="115" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>Atomic Media handover</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="19" t="inlineStr">
+        <is>
+          <t>Created for the next agent. Continue from the tracker, not from memory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B4" s="20" t="inlineStr">
+        <is>
+          <t>Current value</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="21" t="inlineStr">
+        <is>
+          <t>Repository</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>C:\Users\Warwick\.codex\.chatgpt-projects\g-p-6a89e2d97fa08191bee04f4c7a2099a9\Atomic-Chat</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="21" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>feature/atomic-code-foundation</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="21" t="inlineStr">
+        <is>
+          <t>Latest local commit</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>166b5758f chore(guard): re-baseline Atomic Media protected hashes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t>Where to start</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>Task 0 remains In progress. make verify is the active gate before Task 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t>Tracker progress noted</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>Q1 is Answered. T00-S01 through T00-S07 are Done. Task 0 is In progress.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="21" t="inlineStr">
+        <is>
+          <t>Do not commit</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>downloads/index.html; extensions/yarn.lock; src-tauri/icons/icon.png; web-app/src/lib/models.ts; web-app/src/hooks/useModelSources.ts; web-app/src/lib/__tests__/models.test.ts</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1">
+      <c r="A11" s="21" t="inlineStr">
+        <is>
+          <t>Verification passed</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>make test-selective-v2032 exits 0; node guard tests pass 4/4; node scripts/verify-selective-v2032.mjs prints boundaries verified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="34" customHeight="1">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>Verification blocker</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>make verify reaches test-quality and fails on pre-existing call-only assertion findings. Fix or allowlist that guard before Task 0 can be marked Done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="34" customHeight="1">
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>Local tool setup</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>GNU Make is installed at C:\Users\Warwick\AppData\Local\Programs\GnuWin32\bin\make.exe. yarn.cmd shim there delegates to Corepack Yarn 4.5.3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="21" t="inlineStr">
+        <is>
+          <t>Command note</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>In this Codex shell, prepend PATH with C:\Users\Warwick\AppData\Local\Programs\GnuWin32\bin before running make. New terminals should inherit the user PATH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="21" t="inlineStr">
+        <is>
+          <t>Last make verify output</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>Lint produced 13 warnings, typecheck completed, then test-quality failed with call-only-assertions in nine existing test files.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="21" t="inlineStr">
+        <is>
+          <t>Next action</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>Resolve the test-quality guard failures, rerun make verify, then update Task 0 status only if the full gate is green.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
@@ -1828,7 +2075,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6622,7 +6869,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6869,7 +7116,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
+++ b/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
@@ -174,7 +174,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -223,6 +223,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1003,6 +1006,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="20" t="inlineStr">
         <is>
@@ -1047,7 +1051,7 @@
       </c>
       <c r="B7" s="22" t="inlineStr">
         <is>
-          <t>166b5758f chore(guard): re-baseline Atomic Media protected hashes</t>
+          <t>f4f27751a test: document existing quality guard exceptions</t>
         </is>
       </c>
     </row>
@@ -1059,7 +1063,7 @@
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>Task 0 remains In progress. make verify is the active gate before Task 1.</t>
+          <t>Task 0 remains In progress. make verify is still the active gate before Task 1.</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1099,7 @@
       </c>
       <c r="B11" s="22" t="inlineStr">
         <is>
-          <t>make test-selective-v2032 exits 0; node guard tests pass 4/4; node scripts/verify-selective-v2032.mjs prints boundaries verified.</t>
+          <t>make test-quality now exits 0 after documenting seven existing call-only assertion exceptions. make test-selective-v2032 exits 0; node guard tests pass 4/4; node scripts/verify-selective-v2032.mjs prints boundaries verified.</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1111,7 @@
       </c>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t>make verify reaches test-quality and fails on pre-existing call-only assertion findings. Fix or allowlist that guard before Task 0 can be marked Done.</t>
+          <t>make verify now reaches test-coverage-critical and fails with 4 tests: main.test.tsx timeout; formatDate old-date timezone expectation; two huggingface-conversion assertions in the model-catalog/GGUF area that is already dirty and forbidden to commit in this task.</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1147,7 @@
       </c>
       <c r="B15" s="22" t="inlineStr">
         <is>
-          <t>Lint produced 13 warnings, typecheck completed, then test-quality failed with call-only-assertions in nine existing test files.</t>
+          <t>Lint produced 13 warnings, typecheck passed, test-quality passed, hardening contracts passed, then coverage failed: 3 files failed, 4 tests failed, 2227 passed, 16 skipped.</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1159,7 @@
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>Resolve the test-quality guard failures, rerun make verify, then update Task 0 status only if the full gate is green.</t>
+          <t>Do not start Task 1 until make verify is green. Resolve or coordinate the existing coverage failures without committing the six forbidden dirty paths unless the user changes that rule.</t>
         </is>
       </c>
     </row>
@@ -7122,7 +7126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7474,6 +7478,28 @@
       <c r="F13" s="15" t="n"/>
       <c r="G13" s="15" t="n"/>
     </row>
+    <row r="14">
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>make verify after f4f27751a</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>FAIL at test-coverage-critical: main.test.tsx timeout; formatDate timezone expectation; two huggingface-conversion failures in current model-catalog dirty area.</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>Task 0 remains In progress; Task 1 blocked.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="E2:E13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">

--- a/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
+++ b/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Handover" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tasks" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Steps" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisions" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidence" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Handover" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Tasks" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Steps" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Decisions" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Evidence" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tasks'!$A$2:$K$20</definedName>
@@ -1006,7 +1006,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="20" t="inlineStr">
         <is>
@@ -1063,7 +1062,7 @@
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>Task 0 remains In progress. make verify is still the active gate before Task 1.</t>
+          <t>Task 0 gate met: make verify exits 0 in the working tree (2026-09-09). Next work is Task 1 (T01-S01) once the enabling changes are committed. Do not start Task 1 until Task 0 changes are committed.</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1074,7 @@
       </c>
       <c r="B9" s="22" t="inlineStr">
         <is>
-          <t>Q1 is Answered. T00-S01 through T00-S07 are Done. Task 0 is In progress.</t>
+          <t>Q1 Answered. T00-S01..S07 Done. Task 0 marked Done 2026-09-09 on green make verify (working tree; uncommitted).</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1110,7 @@
       </c>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t>make verify now reaches test-coverage-critical and fails with 4 tests: main.test.tsx timeout; formatDate old-date timezone expectation; two huggingface-conversion assertions in the model-catalog/GGUF area that is already dirty and forbidden to commit in this task.</t>
+          <t>RESOLVED 2026-09-09. Prior blocker was Rust desktop test linking (LNK1104 ucrt.lib) plus, once linking worked, two Windows-only test issues (shell contract needed printf on PATH; utils path.rs test assumed Unix / semantics) and web-coverage worker-starvation timeouts. All fixed. See Tasks!K3.</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1146,7 @@
       </c>
       <c r="B15" s="22" t="inlineStr">
         <is>
-          <t>Lint produced 13 warnings, typecheck passed, test-quality passed, hardening contracts passed, then coverage failed: 3 files failed, 4 tests failed, 2227 passed, 16 skipped.</t>
+          <t>2026-09-09 make verify EXITCODE=0. Environment: run from a VS x64 developer shell (vcvars64.bat) with a printf.exe-only directory appended to PATH (Git usr/bin as a whole must NOT be added, or make switches to sh and breaks the PowerShell stub-resources recipe, and Git link.exe shadows MSVC link.exe).</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1276,7 @@
       </c>
       <c r="E3" s="13" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F3" s="13" t="n"/>
@@ -1299,7 +1298,7 @@
       </c>
       <c r="K3" s="15" t="inlineStr">
         <is>
-          <t>Q1 answered 2026-09-08: Option A (re-baseline). Gate is open; proceed at T00-S02.</t>
+          <t>Q1 answered 2026-09-08: Option A (re-baseline). Gate is open; proceed at T00-S02. | 2026-09-09: make verify exits 0 (full green). Web coverage 2234 passed/16 skipped; extension 250+276; Rust 487+12+167+205+28+4; coverage floor 9 files; selective v2.0.32 boundaries verified. GREEN DEPENDS ON uncommitted working-tree fixes (previous agent test fixes + this session: src-tauri/utils/src/path.rs Windows test gating, web-app/vitest.config.ts testTimeout 30s) AND a VS x64 dev env (vcvars64.bat) plus a printf.exe-only dir on PATH so link.exe finds ucrt.lib and make stays on cmd for stub-resources. Nothing committed pending user authorization.</t>
         </is>
       </c>
     </row>

--- a/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
+++ b/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
@@ -1050,7 +1050,7 @@
       </c>
       <c r="B7" s="22" t="inlineStr">
         <is>
-          <t>f4f27751a test: document existing quality guard exceptions</t>
+          <t>8ec82bef3 merge: integrate remote task0 quality-gate exceptions (pushed to origin)</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>Task 0 gate met: make verify exits 0 in the working tree (2026-09-09). Next work is Task 1 (T01-S01) once the enabling changes are committed. Do not start Task 1 until Task 0 changes are committed.</t>
+          <t>Task 0 Done and committed (9e8249046, pushed in 8ec82bef3). Task 1 code complete through T01-S05 in the working tree and uncommitted; next action is T01-S06 (commit) once the user authorises it, then Task 2 (T02-S01).</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B9" s="22" t="inlineStr">
         <is>
-          <t>Q1 Answered. T00-S01..S07 Done. Task 0 marked Done 2026-09-09 on green make verify (working tree; uncommitted).</t>
+          <t>Q1 Answered. T00-S01..S07 Done. Task 0 Done. T01-S01..S05 Done 2026-09-09. T01-S06 (commit) outstanding.</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="B15" s="22" t="inlineStr">
         <is>
-          <t>2026-09-09 make verify EXITCODE=0. Environment: run from a VS x64 developer shell (vcvars64.bat) with a printf.exe-only directory appended to PATH (Git usr/bin as a whole must NOT be added, or make switches to sh and breaks the PowerShell stub-resources recipe, and Git link.exe shadows MSVC link.exe).</t>
+          <t>2026-09-09 make verify EXITCODE=0, re-run after the Task 1 contract landed in the working tree. Environment: VS x64 developer shell (vcvars64.bat) with a printf.exe-only directory appended to PATH (Git usr/bin as a whole must NOT be added, or make switches to sh and breaks the PowerShell stub-resources recipe, and Git link.exe shadows MSVC link.exe).</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>Do not start Task 1 until make verify is green. Resolve or coordinate the existing coverage failures without committing the six forbidden dirty paths unless the user changes that rule.</t>
+          <t>Commit the Task 1 contract when the user authorises it (feat(media): add model-agnostic media contract v2), staging ONLY web-app/src/services/media/contract/** and the tracker. Then Task 2 (T02-S01): capture a v1 capabilities payload as a fixture. Resolve the plan's modulus tie-break contradiction with the user before Task 2's parity test is written.</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F4" s="13" t="n"/>
@@ -1345,7 +1345,11 @@
           <t>Pure types + validateParams. No UI change, no I/O.</t>
         </is>
       </c>
-      <c r="K4" s="15" t="n"/>
+      <c r="K4" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09: T01-S01..S05 Done. Contract lives in web-app/src/services/media/contract/ (tasks.ts, params.ts, models.ts, jobs.ts, index.ts + __tests__/params.test.ts). 45 focused tests pass; full make verify EXIT 0. Only T01-S06 (commit) outstanding, which needs user authorisation. Open question for the user: the plan Step 1 text contradicts itself on modulus tie-breaking ("19 -&gt; 21" vs "ties round down"); implemented round-down to match v1 nearestFrame and keep the Task 2 parity test valid.</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="39.6" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
@@ -2429,7 +2433,7 @@
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F9" s="13" t="n"/>
@@ -2443,7 +2447,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I9" s="15" t="n"/>
+      <c r="I9" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09: 45 pure tests in web-app/src/services/media/contract/__tests__/params.test.ts. Covers clamping, modulus quantisation (ties round DOWN, matching v1 nearestFrame), enum/resolution rejection, required vs default, depends_on hiding (incl. chained and multi-clause), unknown-key drop, seed empty = omitted so the provider randomises, totality and non-mutation.</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="26.4" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
@@ -2466,7 +2474,7 @@
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F10" s="13" t="n"/>
@@ -2480,7 +2488,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I10" s="15" t="n"/>
+      <c r="I10" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09: confirmed RED for the right reason - vitest failed to resolve "../params" (module not found), 1 test file failed, no tests collected.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -2503,7 +2515,7 @@
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F11" s="13" t="n"/>
@@ -2517,7 +2529,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I11" s="15" t="n"/>
+      <c r="I11" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09: tasks.ts, models.ts, jobs.ts, index.ts created. All of plan SS4.1-4.4. Pure types only; no I/O, no React, no import from @/services/atomicMedia.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -2540,7 +2556,7 @@
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F12" s="13" t="n"/>
@@ -2554,7 +2570,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I12" s="15" t="n"/>
+      <c r="I12" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09: validateParams in params.ts. Total (never throws), result discriminated on ok, collects every error. Quantisation lifted from MediaGenerationForm nearestFrame with tie-break preserved for the Task 2 parity test. NOTE the plan step text is self-contradictory: it says both "19 -&gt; 21" and "ties round down"; 19 is equidistant (17/21) so round-down was implemented, per v1 behaviour and the parity requirement.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -2577,7 +2597,7 @@
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F13" s="13" t="n"/>
@@ -2591,7 +2611,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I13" s="15" t="n"/>
+      <c r="I13" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09: focused suite PASS 45/45. Then full make verify EXIT 0 - lint 0 errors, tsc -b clean, test-quality 266 files, web coverage 2279 passed/16 skipped, extensions 250+276, Rust 487+12+167+205+28+4, selective-v2032 boundaries verified.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -2628,7 +2652,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I14" s="15" t="n"/>
+      <c r="I14" s="15" t="inlineStr">
+        <is>
+          <t>Awaiting user authorisation. Do not stage the pre-existing dirty paths.</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="26.4" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
@@ -7125,7 +7153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -7499,6 +7527,28 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>make verify after the Task 1 contract</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EXIT 0 (full green). lint 0 errors / 13 pre-existing warnings; tsc -b clean; test-quality 266 files; web coverage 232 files, 2279 passed / 16 skipped; extensions 250 + 276; Rust 487 + 12 + 167 + 205 + 28 + 4; selective-v2032 guard tests 4/4 and boundaries verified.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Task 1 code complete through T01-S05; commit (T01-S06) not yet authorised.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="E2:E13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">

--- a/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
+++ b/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
@@ -1050,7 +1050,7 @@
       </c>
       <c r="B7" s="22" t="inlineStr">
         <is>
-          <t>8ec82bef3 merge: integrate remote task0 quality-gate exceptions (pushed to origin)</t>
+          <t>c62b11da8 feat(media): add model-agnostic media contract v2 (local, not yet pushed)</t>
         </is>
       </c>
     </row>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>Task 0 Done and committed (9e8249046, pushed in 8ec82bef3). Task 1 code complete through T01-S05 in the working tree and uncommitted; next action is T01-S06 (commit) once the user authorises it, then Task 2 (T02-S01).</t>
+          <t>Task 0 Done and pushed (9e8249046 in merge 8ec82bef3). Task 1 Done and committed locally (c62b11da8); not yet pushed. Next work is Task 2, starting at T02-S01: capture a v1 capabilities payload as a fixture. Live worker capture is preferred; the laptop fallback is MediaStudio.test.tsx:9-58 - record which source was used.</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B9" s="22" t="inlineStr">
         <is>
-          <t>Q1 Answered. T00-S01..S07 Done. Task 0 Done. T01-S01..S05 Done 2026-09-09. T01-S06 (commit) outstanding.</t>
+          <t>Q1 Answered. T00-S01..S07 Done, Task 0 Done. T01-S01..S06 Done, Task 1 Done 2026-09-09 on green make verify, committed c62b11da8. Next not-done step is T02-S01.</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>Commit the Task 1 contract when the user authorises it (feat(media): add model-agnostic media contract v2), staging ONLY web-app/src/services/media/contract/** and the tracker. Then Task 2 (T02-S01): capture a v1 capabilities payload as a fixture. Resolve the plan's modulus tie-break contradiction with the user before Task 2's parity test is written.</t>
+          <t>Start Task 2 at T02-S01. Before T02-S02 writes the parity test, settle the plan's self-contradictory modulus tie-break text with the user ("19 -&gt; 21" vs "ties round down"): the contract implements round-down, matching v1 nearestFrame. Also decide whether to push feature/atomic-code-foundation - c62b11da8 is local only.</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F4" s="13" t="n"/>
@@ -1339,7 +1339,11 @@
           <t>Upcaster round-trip tests green</t>
         </is>
       </c>
-      <c r="I4" s="13" t="n"/>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>c62b11da8</t>
+        </is>
+      </c>
       <c r="J4" s="14" t="inlineStr">
         <is>
           <t>Pure types + validateParams. No UI change, no I/O.</t>
@@ -1347,7 +1351,7 @@
       </c>
       <c r="K4" s="15" t="inlineStr">
         <is>
-          <t>2026-09-09: T01-S01..S05 Done. Contract lives in web-app/src/services/media/contract/ (tasks.ts, params.ts, models.ts, jobs.ts, index.ts + __tests__/params.test.ts). 45 focused tests pass; full make verify EXIT 0. Only T01-S06 (commit) outstanding, which needs user authorisation. Open question for the user: the plan Step 1 text contradicts itself on modulus tie-breaking ("19 -&gt; 21" vs "ties round down"); implemented round-down to match v1 nearestFrame and keep the Task 2 parity test valid.</t>
+          <t>2026-09-09: Task 1 complete, T01-S01..S06 all Done. Contract in web-app/src/services/media/contract/ (tasks.ts, params.ts, models.ts, jobs.ts, index.ts + __tests__/params.test.ts). 45 focused tests pass; full make verify EXIT 0. Committed c62b11da8 (local; not yet pushed). OPEN QUESTION for the user: the plan Step 1 text contradicts itself on modulus tie-breaking ("19 -&gt; 21" vs "ties round down"); round-down was implemented to match v1 nearestFrame and keep the Task 2 parity test valid. Settle this before T02-S02 writes that parity test.</t>
         </is>
       </c>
     </row>
@@ -2638,7 +2642,7 @@
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F14" s="13" t="n"/>
@@ -2654,7 +2658,7 @@
       </c>
       <c r="I14" s="15" t="inlineStr">
         <is>
-          <t>Awaiting user authorisation. Do not stage the pre-existing dirty paths.</t>
+          <t>2026-09-09: committed c62b11da8 "feat(media): add model-agnostic media contract v2". 7 files, 1292 insertions - the six contract files plus this tracker. The 11 pre-existing dirty paths were left unstaged and are still dirty.</t>
         </is>
       </c>
     </row>

--- a/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
+++ b/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
@@ -593,7 +593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -683,7 +683,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Task 0 is a hard gate. `make verify` is currently RED because commit a13b71a83 changed 8 of the 11 files frozen in scripts/selective-v2032-protected.json. Nothing downstream can be verified until Task 0 lands.</t>
+          <t>Task 0 is a hard gate and it is now CLOSED. It was red because commit a13b71a83 changed 8 of the 11 files frozen in scripts/selective-v2032-protected.json; they were re-baselined and `make verify` exits 0 (2026-09-09). Caveat: green depends on uncommitted model-catalog/GGUF test fixes still sitting in the working tree, so a FRESH CLONE is still red. See Decision Q6.</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Decision Q1 on the Decisions sheet blocks Task 0. It is the user's call, not yours. Do not guess it.</t>
+          <t>Decision Q1 is answered (Option A, 2026-09-08). Q2-Q6 on the Decisions sheet are still OPEN and are the user's call, not yours. Do not guess one. They only bite when their own task comes up.</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Never commit the four pre-existing dirty paths: downloads/index.html, extensions/yarn.lock, src-tauri/icons/icon.png, web-app/src/containers/DownloadManegement.tsx.</t>
+          <t>Never commit the pre-existing dirty paths. As of 2026-09-09 there are eleven: downloads/index.html, extensions/yarn.lock, src-tauri/Cargo.lock, src-tauri/icons/icon.png, web-app/src/hooks/useModelSources.ts, web-app/src/lib/models.ts, web-app/src/lib/__tests__/models.test.ts, web-app/src/routes/hub/__tests__/huggingface-conversion.test.ts, web-app/src/services/models/default.ts, web-app/src/utils/__tests__/formatDate.test.ts, web-app/src/utils/getModelToStart.test.ts.</t>
         </is>
       </c>
     </row>
@@ -972,6 +972,37 @@
       <c r="B38" s="7">
         <f>COUNTIF(Decisions!F2:F7,"Open")</f>
         <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>AGENTS: WORKING AGREEMENT (see the Handover sheet for the full version)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>7.</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>You may NOT commit, push, re-baseline the protected guard, or change scope without the user authorising that specific action. Approval for one action is never approval for the next.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>8.</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>The user has NO coding experience. Do not wait to be told when to commit, push, or decide - he will not know, and his silence is not an instruction to wait. YOU must raise it, in plain language, every time the normal process says an action is due. See the WORKING AGREEMENT block on the Handover sheet.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -985,7 +1016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1159,6 +1190,102 @@
       <c r="B16" s="23" t="inlineStr">
         <is>
           <t>Start Task 2 at T02-S01. Before T02-S02 writes the parity test, settle the plan's self-contradictory modulus tie-break text with the user ("19 -&gt; 21" vs "ties round down"): the contract implements round-down, matching v1 nearestFrame. Also decide whether to push feature/atomic-code-foundation - c62b11da8 is local only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="20" t="inlineStr">
+        <is>
+          <t>WORKING AGREEMENT</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>How to work with Warwick. This is not optional and it does not expire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="21" t="inlineStr">
+        <is>
+          <t>Who authorises what</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>The agent must NEVER commit, push, force-push, re-baseline the protected-surface guard, switch or create branches, or change the scope of a task without the user authorising that specific action first. Approval for one action is not approval for the next one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="21" t="inlineStr">
+        <is>
+          <t>The user is not a coder</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>Warwick has no coding experience. He should NOT be expected to know when a commit, a push, or a decision is due, and his silence is not an instruction to wait. The obligation to raise it sits with the AGENT, every time. Never leave finished, verified work sitting there because nobody asked for it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="21" t="inlineStr">
+        <is>
+          <t>So the agent must prompt</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>At every point where the normal process says an action is due, say so in plain language, unprompted: what stage we are at, what the normal next step is, and what you need from him (usually a yes, or an answer to an open decision). If he has not asked for something that clearly should have happened by now - a commit after a green make verify, a push after a task is committed, an answer to a decision that is now blocking - remind him and say why it matters.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="21" t="inlineStr">
+        <is>
+          <t>The normal process, per step</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>Write a failing test -&gt; run it and confirm it fails for the RIGHT reason -&gt; implement -&gt; focused tests green -&gt; full make verify green -&gt; THEN ask the user to authorise the commit -&gt; update this tracker -&gt; ask whether to push. A step is Done only when its stated command has actually been run and passed. Never mark Done on partial success; record which phase failed instead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="21" t="inlineStr">
+        <is>
+          <t>How to ask, concretely</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>Example wording after a green verify: "This is the point where we would normally commit. The change is X, the verification is Y, and I would stage only these files with this commit message. Do you want me to commit it? After that the usual next step is pushing to origin - tell me if you want that too." Name the files and the message so he can approve without reading any code. Explain trade-offs in plain terms, not in jargon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="21" t="inlineStr">
+        <is>
+          <t>Open decisions are his call</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>Q2-Q6 on the Decisions sheet belong to the user. NEVER guess one. When work reaches a point where an open decision blocks it, stop, ask, and explain in plain language what each option would mean for him and what it would cost to change later. Also flag any contradiction found in the plan itself rather than quietly picking a side - say which side you picked and why.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="21" t="inlineStr">
+        <is>
+          <t>Never stage these paths</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>These are pre-existing dirty files that belong to other in-flight work (Decision Q6). Leave them dirty and unstaged unless the user specifically authorises otherwise: downloads/index.html; extensions/yarn.lock; src-tauri/Cargo.lock; src-tauri/icons/icon.png; web-app/src/hooks/useModelSources.ts; web-app/src/lib/models.ts; web-app/src/lib/__tests__/models.test.ts; web-app/src/routes/hub/__tests__/huggingface-conversion.test.ts; web-app/src/services/models/default.ts; web-app/src/utils/__tests__/formatDate.test.ts; web-app/src/utils/getModelToStart.test.ts</t>
         </is>
       </c>
     </row>

--- a/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
+++ b/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="B38" s="7">
-        <f>COUNTIF(Decisions!F2:F7,"Open")</f>
+        <f>COUNTIF(Decisions!F2:F50,"Open")</f>
         <v/>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F5" s="13" t="n"/>
@@ -1525,7 +1525,11 @@
           <t>Live worker capture preferred for the fixture; the fixture at MediaStudio.test.tsx:9-58 is the laptop fallback. Deletes ATOMIC_MEDIA_DEFAULT_VIDEO_REQUEST.</t>
         </is>
       </c>
-      <c r="K5" s="15" t="n"/>
+      <c r="K5" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09: T02-S01..S07 Done. Acceptance test renders the LIVE MediaGenerationForm and asserts byte-identical submitted bodies across five scenarios; mutation-tested (flipping the quantiser tie-break broke exactly one parity test) so it is provably not vacuously green. 85 contract tests, 97 across all media suites. S06 required editing two guard-protected files - authorised by the user - so the manifest was re-baselined in an isolated commit. One deliberate v1 divergence recorded as D1 on the Decisions sheet. Awaiting green make verify, then S08 commit.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="26.4" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
@@ -2810,7 +2814,7 @@
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F15" s="13" t="n"/>
@@ -2824,7 +2828,11 @@
           <t>Laptop (GPU preferred)</t>
         </is>
       </c>
-      <c r="I15" s="15" t="n"/>
+      <c r="I15" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09: NO live worker available - http://127.0.0.1:13420 refused the connection (nothing listening), so the plan's sanctioned laptop fallback was used. Fixture copied verbatim from MediaStudio.test.tsx:9-58 into __tests__/fixtures/worker-v1-capabilities.json, with a _source block recording the provenance, the reason and the observed contract_version. A live GPU-box capture can replace the payload later without touching the tests.</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="26.4" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
@@ -2847,7 +2855,7 @@
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F16" s="13" t="n"/>
@@ -2861,7 +2869,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I16" s="15" t="n"/>
+      <c r="I16" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09: written as TWO files. upcast.test.ts holds the pure mapping tests. parity.test.tsx is the real acceptance test: it RENDERS the live MediaGenerationForm with the v1 fixture, drives the same user input through the v2 contract path, and asserts JSON.stringify equality of the submitted body. It seeds the contract path from the upcast schema's own defaults, so it also proves the upcaster reproduced v1's defaults rather than just proving downcast works.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -2884,7 +2896,7 @@
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F17" s="13" t="n"/>
@@ -2898,7 +2910,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I17" s="15" t="n"/>
+      <c r="I17" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09: confirmed RED for the right reason - both new files failed to resolve "../upcast". Task 1 params.test.ts stayed green throughout.</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="26.4" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
@@ -2921,7 +2937,7 @@
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F18" s="13" t="n"/>
@@ -2935,7 +2951,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I18" s="15" t="n"/>
+      <c r="I18" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09: upcastV1Capabilities implemented per the SS5.1 table. Total - unknown v1 fields ignored, empty/malformed payload yields an empty-but-valid v2 payload, a model claiming no kinds is skipped. Video-only params (num_frames, fps) attach only to tasks whose output_media_type is video.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -2958,7 +2978,7 @@
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F19" s="13" t="n"/>
@@ -2972,7 +2992,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I19" s="15" t="n"/>
+      <c r="I19" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09: downcastV2Request implemented. Key INSERTION ORDER deliberately matches the object literal in the form's submit() so JSON.stringify is byte-identical. Unknown ids dropped with exactly one console.warn naming the provider and the dropped keys. Sends the unqualified v1 model_id.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -2995,7 +3019,7 @@
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F20" s="13" t="n"/>
@@ -3009,7 +3033,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I20" s="15" t="n"/>
+      <c r="I20" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09: AUTHORISED by the user, then done. ATOMIC_MEDIA_DEFAULT_VIDEO_REQUEST deleted from atomicMedia/client.ts; its two spread sites in client.test.ts now use a local videoRequest fixture, with a comment recording why the constant left production (coupling C8 - the client has no business knowing one model's good frame count). Both files are guard-protected, so the guard went RED as expected and was re-baselined in its own isolated commit per Decision Q1. Exactly two hashes changed - no collateral.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -3032,7 +3060,7 @@
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F21" s="13" t="n"/>
@@ -3046,7 +3074,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I21" s="15" t="n"/>
+      <c r="I21" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09: vitest run src/services/media src/services/atomicMedia src/containers/media -&gt; 5 files, 97 tests, all PASS. Contract-only run: 3 files, 85 tests PASS. Mutation-tested the acceptance test by flipping the quantiser tie-break from &lt;= to &lt;: exactly one parity test failed, proving the test is not vacuously green. Mutation reverted.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -3083,7 +3115,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I22" s="15" t="n"/>
+      <c r="I22" s="15" t="inlineStr">
+        <is>
+          <t>Awaiting T02-S06 and user authorisation to commit.</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="26.4" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
@@ -7037,7 +7073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7267,6 +7303,43 @@
         </is>
       </c>
       <c r="G7" s="13" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Recorded divergence, not a question: for a VIDEO model that declares neither frame_rule nor a default num_frames, the v1 form still submits num_frames: 0 while rendering no Frames control. The v2 contract omits the key instead.</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>Nothing. No model in the fixture or the curated catalog is in this shape.</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>Keep the contract behaviour. num_frames: 0 is not a meaningful frame count and a worker would reject it; reproducing it bug-for-bug would lock a defect into the new contract. Flagged here so the divergence is discoverable rather than silent, per plan SS5.4.</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>Agent judgement, 2026-09-09. Reverse it if a real worker is ever found to depend on the zero.</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>Noted</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
+++ b/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
@@ -1081,7 +1081,7 @@
       </c>
       <c r="B7" s="22" t="inlineStr">
         <is>
-          <t>c62b11da8 feat(media): add model-agnostic media contract v2 (local, not yet pushed)</t>
+          <t>c54856d2e fix(verify): stop icon generation from degrading the icon.png master</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>Task 0 Done and pushed (9e8249046 in merge 8ec82bef3). Task 1 Done and committed locally (c62b11da8); not yet pushed. Next work is Task 2, starting at T02-S01: capture a v1 capabilities payload as a fixture. Live worker capture is preferred; the laptop fallback is MediaStudio.test.tsx:9-58 - record which source was used.</t>
+          <t>Tasks 0, 1 and 2 are all Done and committed. Next work is Task 3 (T03-S01): write the shared adapter conformance suite FIRST, parameterised over an adapter factory plus a mock transport - every later adapter must pass it unmodified.</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="B9" s="22" t="inlineStr">
         <is>
-          <t>Q1 Answered. T00-S01..S07 Done, Task 0 Done. T01-S01..S06 Done, Task 1 Done 2026-09-09 on green make verify, committed c62b11da8. Next not-done step is T02-S01.</t>
+          <t>Q1 Answered. Task 0 Done. Task 1 Done (c62b11da8). Task 2 Done (8ca22ff6e + isolated re-baseline 59ee8b7fb). D1 and D2 recorded on the Decisions sheet. Q2-Q6 still Open. Next not-done step: T03-S01.</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="B11" s="22" t="inlineStr">
         <is>
-          <t>make test-quality now exits 0 after documenting seven existing call-only assertion exceptions. make test-selective-v2032 exits 0; node guard tests pass 4/4; node scripts/verify-selective-v2032.mjs prints boundaries verified.</t>
+          <t>make verify exit 0 on the working tree and, as of 2026-09-09, on a FROM-SCRATCH CLEAN CLONE - the clean-checkout gap is closed and proven, not inferred. See Evidence rows 2 and 5 and Decision D2.</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t>RESOLVED 2026-09-09. Prior blocker was Rust desktop test linking (LNK1104 ucrt.lib) plus, once linking worked, two Windows-only test issues (shell contract needed printf on PATH; utils path.rs test assumed Unix / semantics) and web-coverage worker-starvation timeouts. All fixed. See Tasks!K3.</t>
+          <t>None. The two historic blockers are both fixed: the uncommitted model-catalog/GGUF test fixes are committed, and the missing generated app icons are now produced by the make app-icons target.</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>Start Task 2 at T02-S01. Before T02-S02 writes the parity test, settle the plan's self-contradictory modulus tie-break text with the user ("19 -&gt; 21" vs "ties round down"): the contract implements round-down, matching v1 nearestFrame. Also decide whether to push feature/atomic-code-foundation - c62b11da8 is local only.</t>
+          <t>Start Task 3 at T03-S01. Note the conformance suite is the deliverable that constrains every future provider, so write it before the adapter. Q2-Q6 remain the user's call and are not needed for Task 3.</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F5" s="13" t="n"/>
@@ -1519,7 +1519,11 @@
           <t>Upcaster round-trip tests green</t>
         </is>
       </c>
-      <c r="I5" s="13" t="n"/>
+      <c r="I5" s="13" t="inlineStr">
+        <is>
+          <t>8ca22ff6e (+ 59ee8b7fb guard re-baseline)</t>
+        </is>
+      </c>
       <c r="J5" s="14" t="inlineStr">
         <is>
           <t>Live worker capture preferred for the fixture; the fixture at MediaStudio.test.tsx:9-58 is the laptop fallback. Deletes ATOMIC_MEDIA_DEFAULT_VIDEO_REQUEST.</t>
@@ -3101,7 +3105,7 @@
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F22" s="13" t="n"/>
@@ -3117,7 +3121,7 @@
       </c>
       <c r="I22" s="15" t="inlineStr">
         <is>
-          <t>Awaiting T02-S06 and user authorisation to commit.</t>
+          <t>2026-09-09: committed 8ca22ff6e "feat(media): upcast v1 worker capabilities to contract v2" (contract work + the C8 removal + fixture), then 59ee8b7fb as the isolated guard re-baseline per Q1. make verify exit 0; web coverage 2319 passed/16 skipped, up from 2279 by the 40 tests added.</t>
         </is>
       </c>
     </row>
@@ -7073,7 +7077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7336,6 +7340,43 @@
         </is>
       </c>
       <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>CORRECTION to the record: "clean-checkout verify is red" was attributed solely to the uncommitted model-catalog/GGUF test fixes (Decision Q6). That was incomplete. There were TWO independent causes.</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>Nothing now. Both causes are fixed and a clean clone verifies green.</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>Cause 1: the uncommitted test fixes (timezone-dependent formatDate assertions, GGUF catalog filtering) - committed 2026-09-09 as 784adb09a / 0d3c2b470 / 9621b112c after user authorisation. Cause 2, previously unrecorded and independent of Q6: every icon except src-tauri/icons/icon.png is gitignored and generated, and tauri-build needs icons/icon.ico to compile the Tauri test target, so a fresh clone died before running a single test. test-rust's TAURI_CONFIG override does NOT avoid this on Windows - measured. Fixed by f8772ec2d (generate icons when missing) and c54856d2e (stop that generation overwriting the 1024x1024 master with its own 512x512 output - the cause of the long-unexplained icon.png diff).</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>PROVEN, not inferred: a fresh clone of the branch, installed and built from scratch, ran make verify to exit 0 on 2026-09-09. Cause 1 alone was necessary but NOT sufficient; committing those files would not have made a clean clone green on its own.</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>Noted</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
         <is>
           <t>2026-09-09</t>
         </is>
@@ -7426,11 +7467,19 @@
       </c>
       <c r="E2" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F2" s="15" t="n"/>
-      <c r="G2" s="15" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F2" s="15" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+      <c r="G2" s="15" t="inlineStr">
+        <is>
+          <t>contract: web-app/src/services/media/contract/{tasks,params,models,jobs,index,upcast}.ts + __tests__/{params,upcast}.test.ts, parity.test.tsx, fixtures/worker-v1-capabilities.json. v1 residue: services/atomicMedia/client{,.test}.ts. catalog: lib/models.ts, hooks/useModelSources.ts, services/models/default.ts (+3 test files). build: Makefile (app-icons). guard: scripts/selective-v2032-protected.json. docs: this tracker. No UI file changed.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="n">
@@ -7453,11 +7502,19 @@
       </c>
       <c r="E3" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F3" s="15" t="n"/>
-      <c r="G3" s="15" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F3" s="15" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+      <c r="G3" s="15" t="inlineStr">
+        <is>
+          <t>make verify exit 0 on the working tree AND on a from-scratch clean clone (2026-09-09). Web coverage 2319 passed/16 skipped; extensions 250+276; Rust 487+12+167+205+28+4; coverage floor 9 critical files; selective-v2032 boundaries verified. Nothing was skipped or unavailable in either run.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="n">
@@ -7480,11 +7537,19 @@
       </c>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F4" s="15" t="n"/>
-      <c r="G4" s="15" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+      <c r="G4" s="15" t="inlineStr">
+        <is>
+          <t>parity.test.tsx - 6 tests, all passing. It renders the live MediaGenerationForm and asserts JSON.stringify equality of the submitted body across defaults, negative prompt + seed, a non-default resolution, the quantiser tie, and image_to_video with a reference image. Mutation-checked: flipping the tie-break from &lt;= to &lt; fails exactly one case, so the green is earned not vacuous.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
@@ -7530,11 +7595,19 @@
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F6" s="15" t="n"/>
-      <c r="G6" s="15" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F6" s="15" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+      <c r="G6" s="15" t="inlineStr">
+        <is>
+          <t>make test-selective-v2032 green. Re-baseline commits: Task 0 = 9e8249046 era (8 media files); Task 2 = 59ee8b7fb (exactly 2 entries - atomicMedia/client.ts and client.test.ts). Each re-baseline is an isolated commit containing only the manifest, per Q1.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="26.4" customHeight="1">
       <c r="A7" s="6" t="n">
@@ -7553,11 +7626,19 @@
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F7" s="15" t="n"/>
-      <c r="G7" s="15" t="n"/>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+      <c r="G7" s="15" t="inlineStr">
+        <is>
+          <t>PREMISE VOID as of 2026-09-09: the user authorised committing the pre-existing dirty paths, so they are no longer dirty. 8 of 11 were committed after review (784adb09a, 0d3c2b470, 9621b112c) and downloads/index.html was deleted on request (6ed0979bb). Two were reviewed and DISCARDED as damage/churn: src-tauri/icons/icon.png (a 512x512 overwrite of the 1024x1024 master - see D2) and extensions/yarn.lock (rebuild fingerprint of the locally built core tarball, re-churns on every build).</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">

--- a/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
+++ b/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
@@ -1093,7 +1093,7 @@
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>Tasks 0, 1 and 2 are all Done and committed. Next work is Task 3 (T03-S01): write the shared adapter conformance suite FIRST, parameterised over an adapter factory plus a mock transport - every later adapter must pass it unmodified.</t>
+          <t>Tasks 0-3 all Done and committed. Next work is Task 4 (T04-S01): failing store tests for the multi-provider registry - baseline present, enable/disable persists, two providers merge without id collision, disabling clears a stale selection. Note Task 4 persists to the EXISTING settings surface: no new config file, and any secret goes where cloud LLM keys go, never localStorage.</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="B9" s="22" t="inlineStr">
         <is>
-          <t>Q1 Answered. Task 0 Done. Task 1 Done (c62b11da8). Task 2 Done (8ca22ff6e + isolated re-baseline 59ee8b7fb). D1 and D2 recorded on the Decisions sheet. Q2-Q6 still Open. Next not-done step: T03-S01.</t>
+          <t>Q1 Answered. Tasks 0, 1, 2, 3 Done. D1 and D2 recorded. Q2-Q6 still Open. Next not-done step: T04-S01. The adapter conformance suite at services/media/adapters/__tests__/conformance.ts is now the contract for every future provider - do not weaken it to make an adapter pass.</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>Start Task 3 at T03-S01. Note the conformance suite is the deliverable that constrains every future provider, so write it before the adapter. Q2-Q6 remain the user's call and are not needed for Task 3.</t>
+          <t>Start Task 4 at T04-S01. Two guard re-baselines have happened so far (Task 2 and Task 3), each isolated per Q1; expect to need authorisation again if a protected file must change. Task 5 (ComfyUI) is the first real test of the abstraction, since an adapter-specific branch in the conformance suite would mean the contract is wrong.</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F6" s="13" t="n"/>
@@ -1578,7 +1578,11 @@
           <t>Mock transport. Writes the shared conformance suite that every later adapter must pass.</t>
         </is>
       </c>
-      <c r="K6" s="15" t="n"/>
+      <c r="K6" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09: Task 3 complete, T03-S01..S06 all Done. The conformance suite is the lasting deliverable: 30 tests every future adapter must pass unmodified, covering health as a renderable state, v2-whatever-the-wire-speaks, provider-qualified ids, client_job_id echo, queued-&gt;running-&gt;succeeded, structured failure, optional methods matching declared features, and AbortSignal reaching the transport. The worker adapter passes all 30. atomicMedia is now one provider's private detail. Full make verify exit 0. Phase gate "two adapters pass one conformance suite" is HALF met - the ComfyUI adapter in Task 5 is the real test of whether the abstraction holds.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="26.4" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
@@ -3146,7 +3150,7 @@
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F23" s="13" t="n"/>
@@ -3160,7 +3164,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I23" s="15" t="n"/>
+      <c r="I23" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09: adapters/__tests__/conformance.ts. Parameterised over an adapter factory plus a ConformanceScenarios object, because wire formats are provider-specific while behaviour is not. Asserts: health online/offline/unauthorised as STATES not exceptions (offline must carry a renderable reason); capabilities always v2 whatever the wire speaks; every model id provider-qualified; a params schema for every claimed task and none for unclaimed ones; submit echoes the caller's client_job_id and starts in a live state; poll walks queued-&gt;running-&gt;succeeded; a failed job carries structured error {code,message,retryable} and NO outputs; optional methods present if and only if capabilities.features says so; and the caller's AbortSignal reaches the transport on all four required methods. An inapplicable scenario (local worker cannot be unauthorised) is declared and asserted, never silently skipped. Deliberately not a .test.ts so it is not collected alone.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -3183,7 +3191,7 @@
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F24" s="13" t="n"/>
@@ -3197,7 +3205,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I24" s="15" t="n"/>
+      <c r="I24" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09: adapters/__tests__/atomicWorker.test.ts implements the scenarios over a stubbed global fetch (the same transport seam the existing client tests use) and reuses the Task 2 v1 fixture. Confirmed RED first for the right reason: "../atomicWorker" unresolved.</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="26.4" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
@@ -3220,7 +3232,7 @@
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F25" s="13" t="n"/>
@@ -3234,7 +3246,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I25" s="15" t="n"/>
+      <c r="I25" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09: createAtomicWorkerAdapter implemented. Injects descriptor.base_url (AtomicMediaClient already accepted one, so the client change the plan listed for that purpose was unnecessary). capabilities() routes v1 through upcastV1Capabilities, uses v2 directly, and REFUSES contract &gt; 2 rather than partially parsing it (plan 5.2); a v2 payload is trusted for content but re-qualified with the local descriptor id, since a worker cannot know what this install calls it. Missing /capabilities becomes an empty-but-valid v2 payload. No cancel/subscribe/install methods exist at all, matching features.* - C11 admitted, not faked. Also fixed contract/index.ts, which had never exported upcast/downcast (Task 2 tests imported the module directly, so this was the first consumer to notice).</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -3257,7 +3273,7 @@
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F26" s="13" t="n"/>
@@ -3271,7 +3287,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I26" s="15" t="n"/>
+      <c r="I26" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09: internal client_job_id -&gt; provider job_id Map in the adapter closure, reattached to every snapshot. poll() accepts a handle carrying either id, so a restored job manager can poll with only the provider id.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -3294,7 +3314,7 @@
       </c>
       <c r="E27" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F27" s="13" t="n"/>
@@ -3308,7 +3328,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I27" s="15" t="n"/>
+      <c r="I27" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09: 30/30 PASS. The 4 AbortSignal failures were resolved properly, not by weakening the suite: the user authorised adding an optional signal parameter to AtomicMediaClient (health/capabilities/createJob/getJob), forwarded into the existing requestJson init and on to fetch, so an abandoned request actually stops. client.ts is guard-protected, so the manifest was re-baselined in an isolated commit - exactly one hash changed. Full make verify exit 0; web coverage 2349 passed/16 skipped, up from 2319 by these 30 tests.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -3331,7 +3355,7 @@
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F28" s="13" t="n"/>
@@ -3345,7 +3369,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I28" s="15" t="n"/>
+      <c r="I28" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09: committed, with the guard re-baseline isolated in its own commit per Q1.</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="26.4" customHeight="1">
       <c r="A29" s="6" t="inlineStr">

--- a/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
+++ b/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
@@ -1607,7 +1607,7 @@
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F7" s="13" t="n"/>
@@ -1627,7 +1627,11 @@
           <t>Bundled baseline is the existing local worker, so current users see no change.</t>
         </is>
       </c>
-      <c r="K7" s="15" t="n"/>
+      <c r="K7" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09: T04-S01..S07 Done. Providers are a list, not a hardcoded worker, with per-provider isolation so one bad provider cannot block another. No secrets stored - see D3 for the plan contradiction that was deferred rather than guessed. 19 tests, mutation-checked.</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="26.4" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
@@ -3396,7 +3400,7 @@
       </c>
       <c r="E29" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F29" s="13" t="n"/>
@@ -3410,7 +3414,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I29" s="15" t="n"/>
+      <c r="I29" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09: stores/__tests__/media-provider-store.test.ts, 19 tests. Covers the baseline present and enabled; enable/disable persisting to localStorage; a user-added provider persisting; duplicate ids refused; builtin providers never removable (only disablable); per-provider health; two providers exposing the SAME local_id merging without collision via provider-qualified ids; one provider failing without blocking another; a disabled provider never contacted; a hung provider timing out without hanging the refresh; and a stale selection cleared on disable and on remove. Mutation-checked: removing the selection-clearing rule fails exactly one test.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -3433,7 +3441,7 @@
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F30" s="13" t="n"/>
@@ -3447,7 +3455,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I30" s="15" t="n"/>
+      <c r="I30" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09: confirmed RED - "../media-provider-store" unresolved.</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="26.4" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
@@ -3470,7 +3482,7 @@
       </c>
       <c r="E31" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F31" s="13" t="n"/>
@@ -3484,7 +3496,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I31" s="15" t="n"/>
+      <c r="I31" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09: constants/mediaProviders.ts. Exactly one entry - the local worker at 127.0.0.1:13420, origin builtin, enabled, auth type none. Existing users see no change and need no migration.</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="26.4" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
@@ -3507,7 +3523,7 @@
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F32" s="13" t="n"/>
@@ -3521,7 +3537,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I32" s="15" t="n"/>
+      <c r="I32" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09: stores/media-provider-store.ts, mirroring provider-registry-store. Persists ONLY descriptors + selectedModelId via zustand persist to the existing localStorage settings surface - no new config file. Health/capabilities/errors are deliberately NOT persisted: restoring yesterday's "online" would be a confident lie about a worker that is not running. Baseline merges with persisted state so a user's disable survives while a later release's new baseline entry still appears. SECRETS: none are stored. A descriptor may carry auth.setting_key naming where a credential lives; the credential never enters this store, and a test asserts the persisted blob contains the key NAME and no value. See D3 for the plan contradiction behind that choice.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -3544,7 +3564,7 @@
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F33" s="13" t="n"/>
@@ -3558,7 +3578,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I33" s="15" t="n"/>
+      <c r="I33" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09: refresh() uses Promise.allSettled with a per-provider AbortController timeout (default 8s) and writes health/capabilities/errors per provider, so a provider that is down, slow or malformed cannot block another's capabilities. An offline provider is not then asked for capabilities - that would only produce a second, less useful error. Error text names both the state and the reason.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -3581,7 +3605,7 @@
       </c>
       <c r="E34" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F34" s="13" t="n"/>
@@ -3595,7 +3619,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I34" s="15" t="n"/>
+      <c r="I34" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09: 19/19 PASS. NOTE: the first full make verify FAILED (exit 2) on lint - an omit-by-destructuring pattern left unused bindings, which this repo's eslint rejects. Replaced with an explicit helper. Local pre-flight must be lint + typecheck + focused tests; only the latter two had been run.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -7105,7 +7133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7409,6 +7437,39 @@
           <t>2026-09-09</t>
         </is>
       </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>CONTRADICTION in the plan, Task 4 Step 4: it says provider secrets are "stored the same way cloud LLM provider keys already are" AND "never in localStorage". Both cannot hold - cloud LLM keys ARE in localStorage today.</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>Task 6 (cloud adapters), which is gated on Q2 and not started. Task 4 is unaffected.</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>Verified, not assumed: hooks/useModelProvider.ts persists its whole state - api_key included, no partialize - to localStorage under the "model-provider" key. So "the same way as cloud keys" means localStorage, which the next clause forbids. Task 4 sidesteps it legitimately by storing NO secrets: the only bundled provider is a loopback worker with auth type none, and a descriptor records only auth.setting_key (a name), never a value. Resolve this when Task 6 actually needs a secret, with the user, since it is a security decision and not the agent's to make. Separately worth knowing: cloud provider API keys sit in plaintext localStorage today. Pre-existing, out of scope, untouched - but the plan's wording implies otherwise.</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>Deferred to Task 6. Not guessed.</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
+++ b/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
@@ -1081,7 +1081,7 @@
       </c>
       <c r="B7" s="22" t="inlineStr">
         <is>
-          <t>c54856d2e fix(verify): stop icon generation from degrading the icon.png master</t>
+          <t>f224ce822 feat(media): support multiple media providers (pushed)</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>Tasks 0-3 all Done and committed. Next work is Task 4 (T04-S01): failing store tests for the multi-provider registry - baseline present, enable/disable persists, two providers merge without id collision, disabling clears a stale selection. Note Task 4 persists to the EXISTING settings surface: no new config file, and any secret goes where cloud LLM keys go, never localStorage.</t>
+          <t>Tasks 0-4 all Done, committed and pushed. Next work is Task 5 (T05-S01): READ the ComfyUI HTTP/WS surface before writing anything (/object_info, /prompt, /history/{id}, /queue, /interrupt, /view, /ws) and record which ComfyUI version was validated against. Then build from RECORDED FIXTURES, never a live server.</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="B9" s="22" t="inlineStr">
         <is>
-          <t>Q1 Answered. Tasks 0, 1, 2, 3 Done. D1 and D2 recorded. Q2-Q6 still Open. Next not-done step: T04-S01. The adapter conformance suite at services/media/adapters/__tests__/conformance.ts is now the contract for every future provider - do not weaken it to make an adapter pass.</t>
+          <t>Q1 Answered. Tasks 0, 1, 2, 3, 4 Done. D1/D2 Noted, D3 OPEN (secrets - a security decision for the user at Task 6). Q2-Q6 still Open. Next not-done step: T05-S01.</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>Start Task 4 at T04-S01. Two guard re-baselines have happened so far (Task 2 and Task 3), each isolated per Q1; expect to need authorisation again if a protected file must change. Task 5 (ComfyUI) is the first real test of the abstraction, since an adapter-specific branch in the conformance suite would mean the contract is wrong.</t>
+          <t>Start Task 5 at T05-S01. It is the real test of the abstraction: the ComfyUI adapter must pass services/media/adapters/__tests__/conformance.ts UNMODIFIED. If a test needs bending to fit, the contract is underspecified and the CONTRACT changes - never the suite. Local pre-flight before any full gate: yarn lint AND tsc -b AND the focused tests (a run was lost to skipping lint). Three guard re-baselines have happened (Tasks 0, 2, 3), each isolated per Q1; authorisation is needed again for any further protected-file change.</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,11 @@
           <t>make verify green</t>
         </is>
       </c>
-      <c r="I3" s="13" t="n"/>
+      <c r="I3" s="13" t="inlineStr">
+        <is>
+          <t>9e8249046 (in merge 8ec82bef3)</t>
+        </is>
+      </c>
       <c r="J3" s="14" t="inlineStr">
         <is>
           <t>HARD GATE. Guard is red now: 8 of 11 protected media files changed by a13b71a83. Adds scripts/rebaseline-selective-v2032.mjs.</t>
@@ -1572,7 +1576,11 @@
           <t>Two adapters pass one conformance suite</t>
         </is>
       </c>
-      <c r="I6" s="13" t="n"/>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>eda596d8d (+ abcc50d48 guard re-baseline)</t>
+        </is>
+      </c>
       <c r="J6" s="14" t="inlineStr">
         <is>
           <t>Mock transport. Writes the shared conformance suite that every later adapter must pass.</t>
@@ -1621,7 +1629,11 @@
           <t>Two adapters pass one conformance suite</t>
         </is>
       </c>
-      <c r="I7" s="13" t="n"/>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>f224ce822</t>
+        </is>
+      </c>
       <c r="J7" s="14" t="inlineStr">
         <is>
           <t>Bundled baseline is the existing local worker, so current users see no change.</t>
@@ -3646,7 +3658,7 @@
       </c>
       <c r="E35" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F35" s="13" t="n"/>
@@ -3660,7 +3672,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I35" s="15" t="n"/>
+      <c r="I35" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09: committed f224ce822 "feat(media): support multiple media providers" and pushed. No protected file changed, so no guard re-baseline was needed this time. Full make verify exit 0.</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="26.4" customHeight="1">
       <c r="A36" s="6" t="inlineStr">
@@ -7601,7 +7617,7 @@
       </c>
       <c r="G3" s="15" t="inlineStr">
         <is>
-          <t>make verify exit 0 on the working tree AND on a from-scratch clean clone (2026-09-09). Web coverage 2319 passed/16 skipped; extensions 250+276; Rust 487+12+167+205+28+4; coverage floor 9 critical files; selective-v2032 boundaries verified. Nothing was skipped or unavailable in either run.</t>
+          <t>make verify exit 0 on the working tree at every task boundary, AND on a from-scratch clean clone (2026-09-09). Latest run: web coverage 2368 passed / 16 skipped (up from 2234 at session start); extensions 250 + 276; Rust 487 + 12 + 167 + 205 + 28 + 4; coverage floor 9 critical files; selective-v2032 boundaries verified. Nothing skipped or unavailable. One run FAILED on lint (exit 2) from an omit-by-destructuring pattern leaving unused bindings; fixed and re-run green.</t>
         </is>
       </c>
     </row>
@@ -7657,11 +7673,19 @@
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F5" s="15" t="n"/>
-      <c r="G5" s="15" t="n"/>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+      <c r="G5" s="15" t="inlineStr">
+        <is>
+          <t>30/30 for the Atomic Media Worker adapter. ONE adapter only - the phase gate is "two adapters pass one conformance suite", so this is half met until Task 5's ComfyUI adapter passes the same suite UNMODIFIED. An adapter-specific branch in the suite would mean the contract is wrong.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">

--- a/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
+++ b/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
@@ -1081,7 +1081,7 @@
       </c>
       <c r="B7" s="22" t="inlineStr">
         <is>
-          <t>f224ce822 feat(media): support multiple media providers (pushed)</t>
+          <t>746c75579 docs(tracker): record Task 4 commit and backfill missing SHAs (pushed). Task 5's work is in the working tree, UNCOMMITTED, awaiting the user's authorisation.</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>Tasks 0-4 all Done, committed and pushed. Next work is Task 5 (T05-S01): READ the ComfyUI HTTP/WS surface before writing anything (/object_info, /prompt, /history/{id}, /queue, /interrupt, /view, /ws) and record which ComfyUI version was validated against. Then build from RECORDED FIXTURES, never a live server.</t>
+          <t>Tasks 0-5 all Done. Task 5 is COMMITTED but NOT PUSHED - ask the user whether to push before starting anything else. Next work is Task 7 (T07-S01), by the user's explicit choice ahead of the now-unblocked Task 6. Task 7's scope is fixed by decision D5: leave useAtomicMediaJob.ts and MediaStudio.tsx untouched, new files only.</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="B9" s="22" t="inlineStr">
         <is>
-          <t>Q1 Answered. Tasks 0, 1, 2, 3, 4 Done. D1/D2 Noted, D3 OPEN (secrets - a security decision for the user at Task 6). Q2-Q6 still Open. Next not-done step: T05-S01.</t>
+          <t>Q1 Answered. Q2 ANSWERED 2026-09-09: cloud providers ARE in scope, so Task 6 is live (deferred by the user's choice, not skipped). Tasks 0-4 Done. Task 5 In progress (only the commit step remains). D1/D2/D4 Noted. D5 Answered 2026-09-09 (Task 7 leaves useAtomicMediaJob alone - no protected file, no re-baseline). D3 is now a LIVE blocker for Task 6. Q3-Q6 still Open. Next not-done step: T05-S06, then Task 7 (T07-S01).</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="B11" s="22" t="inlineStr">
         <is>
-          <t>make verify exit 0 on the working tree and, as of 2026-09-09, on a FROM-SCRATCH CLEAN CLONE - the clean-checkout gap is closed and proven, not inferred. See Evidence rows 2 and 5 and Decision D2.</t>
+          <t>2026-09-09 for Task 5: make verify EXITCODE=0 in a VS x64 developer shell (vcvars64.bat), GnuWin32 make on PATH, plus a printf-ONLY directory that also contains msys-2.0.dll / msys-intl-8.dll / msys-iconv-2.dll - printf.exe without its msys runtime cannot start and fails one Rust shell-contract test. Do NOT add Git's usr/bin wholesale: make then switches to sh and breaks the PowerShell stub-resources recipe, and Git's link.exe shadows MSVC's. Results: web-app 2426 passed/16 skipped, extension 250, llamacpp extension 276, Rust 487+12 passed/0 failed, coverage floor passed, Selective v2.0.32 boundaries verified.</t>
         </is>
       </c>
     </row>
@@ -1189,10 +1189,11 @@
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>Start Task 5 at T05-S01. It is the real test of the abstraction: the ComfyUI adapter must pass services/media/adapters/__tests__/conformance.ts UNMODIFIED. If a test needs bending to fit, the contract is underspecified and the CONTRACT changes - never the suite. Local pre-flight before any full gate: yarn lint AND tsc -b AND the focused tests (a run was lost to skipping lint). Three guard re-baselines have happened (Tasks 0, 2, 3), each isolated per Q1; authorisation is needed again for any further protected-file change.</t>
-        </is>
-      </c>
-    </row>
+          <t>Ask the user whether to push the Task 5 commit to origin/feature/atomic-code-foundation, and backfill its SHA into the Commit SHA column on the Tasks sheet (Task 4's SHA was backfilled the same way in 746c75579). Then start Task 7 at T07-S01. Task 6 is unblocked (Q2 answered: cloud IS in scope) but deferred by the user; do NOT start it until D3 - where the API key is stored - is answered, because that is a security decision and his call.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
@@ -1668,7 +1669,7 @@
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F8" s="13" t="n"/>
@@ -1688,7 +1689,11 @@
           <t>Fixtures only, never live. ComfyUI runs CPU-only and /object_info responds without generating.</t>
         </is>
       </c>
-      <c r="K8" s="15" t="n"/>
+      <c r="K8" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09: Task 5 complete, T05-S01..S06 all Done. Committed on feature/atomic-code-foundation; NOT pushed yet. The abstraction held: conformance.ts was imported UNMODIFIED and the contract did not have to change. Atomic Media Worker 30/30, ComfyUI 58/58 (30 conformance + 28 ComfyUI-specific). Version validated against: ComfyUI 0.35.0 (comfyui_version.py on master, read 2026-09-09). Divergences recorded as D4: fixtures transcribed from source rather than captured live (no ComfyUI on this laptop), and no separate RED observed - four mutations used as evidence instead, each killing exactly one test after a real gap in the node-class guard test was found and closed. Gate: make verify EXITCODE=0, protected-surface guard verified, no protected file touched.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="26.4" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
@@ -1719,7 +1724,7 @@
       <c r="F9" s="13" t="n"/>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q2 (answered - cloud IS in scope); D3 must be answered before starting</t>
         </is>
       </c>
       <c r="H9" s="14" t="inlineStr">
@@ -1733,7 +1738,11 @@
           <t>GATED on Q2. Skip entirely if local-only. Cloud does the compute, so this is ideal laptop work.</t>
         </is>
       </c>
-      <c r="K9" s="15" t="n"/>
+      <c r="K9" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09: UNBLOCKED - Q2 answered 'yes, include cloud providers'. Deliberately DEFERRED, not skipped: the user chose Task 7 as the next piece of work. Strict tracker order would have taken Task 6 next; this deviation is the user's call, recorded here rather than made silently. Task 6 is self-contained and nothing downstream depends on it, so it can be slotted in at any point. Do NOT start it until D3 (where the API key is stored) is answered.</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="26.4" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
@@ -1778,7 +1787,11 @@
           <t>Fake timers. Fixes C10, C11, C12.</t>
         </is>
       </c>
-      <c r="K10" s="15" t="n"/>
+      <c r="K10" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09: agreed with the user as the next task after Task 5, ahead of the now-unblocked Task 6. Not started yet - Task 5's commit lands first so the two tasks' changes do not tangle in one working tree. SCOPE FIXED BY DECISION D5: leave useAtomicMediaJob.ts and MediaStudio.tsx UNTOUCHED. New files only (jobManager.ts, __tests__/jobManager.test.ts, hooks/useMediaGeneration.ts, hooks/useMediaGeneration.test.tsx). Task 7 therefore touches no protected file and needs no guard re-baseline.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="26.4" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
@@ -3699,7 +3712,7 @@
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F36" s="13" t="n"/>
@@ -3713,7 +3726,11 @@
           <t>Laptop (CPU ComfyUI)</t>
         </is>
       </c>
-      <c r="I36" s="15" t="n"/>
+      <c r="I36" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09 Done. Surface read from source, not inferred (AGENTS.md 6.2): server.py (routes, node_info), execution.py (history entry and status.messages), main.py (status_str for an interrupt), comfy_execution/progress.py (progress_state), nodes.py INPUT_TYPES, comfy/samplers.py. VERSION VALIDATED AGAINST: comfyui_version.py __version__ = 0.35.0 on github.com/comfyanonymous/ComfyUI@master, read 2026-09-09. Two findings that changed the design: (1) POST /prompt accepts a caller-supplied prompt_id but only as a canonical UUID, and client_job_id is a ULID, so ComfyUI mints the id and the adapter keeps the mapping; (2) an interrupted prompt is recorded as status_str=error, so cancelled is only distinguishable from failed by an execution_interrupted entry in status.messages. Full endpoint table in the comfyui.ts header.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -3736,7 +3753,7 @@
       </c>
       <c r="E37" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F37" s="13" t="n"/>
@@ -3750,7 +3767,11 @@
           <t>Laptop (CPU ComfyUI)</t>
         </is>
       </c>
-      <c r="I37" s="15" t="n"/>
+      <c r="I37" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09 Done, with a recorded divergence - see Decision D4. No ComfyUI is installed on this laptop, so the fixtures were transcribed from the ComfyUI source at 0.35.0 rather than captured from a live server; each fixture carries a _source block naming the file, version, read date and exactly what was trimmed. Tests and implementation were written in one pass, so a separate RED was not observed; mutation testing was used as the evidence instead (see T05-S05).</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="26.4" customHeight="1">
       <c r="A38" s="6" t="inlineStr">
@@ -3773,7 +3794,7 @@
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F38" s="13" t="n"/>
@@ -3787,7 +3808,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I38" s="15" t="n"/>
+      <c r="I38" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09 Done. comfyWorkflows.ts declares two templates (txt2img, txt2img-hires); each IS one MediaModelDescriptor. /object_info is consulted only to confirm every node class exists and to derive MediaParamSpecs from the exposed inputs' types and bounds. A template is dropped if a node class is missing OR an exposed input is gone. Seed ceiling clamped from ComfyUI's 2^64-1 to Number.MAX_SAFE_INTEGER, because a larger value does not survive JSON.stringify and the job would then run on a seed nobody chose.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -3810,7 +3835,7 @@
       </c>
       <c r="E39" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F39" s="13" t="n"/>
@@ -3824,7 +3849,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I39" s="15" t="n"/>
+      <c r="I39" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09 Done. submit builds the declared graph and POSTs /prompt with the adapter's client_id; poll reads /history/{id} then falls back to /queue to tell queued from running; cancel posts BOTH /interrupt and /queue delete (which of the two applies is a race the caller cannot win by asking first); subscribe opens /ws?clientId= with the SAME client_id it submits under, handles progress_state and the legacy progress frame, and degrades to polling every 1.5s on socket error or close without losing the job.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -3847,7 +3876,7 @@
       </c>
       <c r="E40" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F40" s="13" t="n"/>
@@ -3861,7 +3890,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I40" s="15" t="n"/>
+      <c r="I40" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09 Done. Both adapters pass conformance.ts UNMODIFIED - Atomic Media Worker 30/30, ComfyUI 58/58 (30 conformance + 28 ComfyUI-specific). No adapter-specific branch was needed and the contract did not have to change: the abstraction held. Mutation tested in place of a separate RED - four mutations (interrupt read as a failure; seed ceiling unclamped; node-class guard disabled; socket opened with a fresh client id) each killed exactly one test after a gap was found and closed. The node-class guard mutation initially killed NOTHING: the test was deleting LatentUpscale, which the exposed-input check already catches, so a SaveImage case was added - the guard only matters for classes a graph uses but never exposes.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -3884,7 +3917,7 @@
       </c>
       <c r="E41" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F41" s="13" t="n"/>
@@ -3898,7 +3931,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I41" s="15" t="n"/>
+      <c r="I41" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09 Done. Authorised by the user in writing ('commit it once verify is green') after a genuinely green gate. make verify EXITCODE=0 in a VS x64 developer shell: web-app 2426 passed/16 skipped, extension 250, llamacpp extension 276, @janhq/core suites green, Rust 487+12 passed/0 failed, coverage floor passed, and 'Selective v2.0.32 boundaries verified'. NOTE for the next agent: two earlier verify runs looked green from the wrapper's exit code but were not - always read the log's own EXITCODE line. Run 1 died at stub-resources (make invoked from Git Bash picks sh, which eats the $files variable in the PowerShell recipe). Run 2 failed one Rust test, core::agent::tools::contract_tests::shell_contract_covers_safe_execution_hard_block_denial_and_cancellation, because a printf.exe copied into an isolated directory without msys-2.0.dll cannot start (exit 0xC0000135). Copy the msys DLLs alongside printf.exe.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -7149,7 +7186,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7256,13 +7293,21 @@
           <t>Answering local-only removes Task 6 cleanly and costs nothing - the adapter seam still exists and a remote adapter can be added later.</t>
         </is>
       </c>
-      <c r="E3" s="15" t="n"/>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>Cloud media providers ARE in scope. Answered by the user in writing 2026-09-09. Task 6 is therefore live, not skipped. Consequence the user was told before answering: the app has to hold an API key, which makes D3 (where the secret lives) a real security decision that must be settled BEFORE Task 6 starts, and cloud generations can cost him money.</t>
+        </is>
+      </c>
       <c r="F3" s="13" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="G3" s="13" t="n"/>
+          <t>Answered</t>
+        </is>
+      </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -7477,7 +7522,7 @@
       </c>
       <c r="E10" s="15" t="inlineStr">
         <is>
-          <t>Deferred to Task 6. Not guessed.</t>
+          <t>Deferred to Task 6. Not guessed. | 2026-09-09 UPDATE: Q2 was answered 'cloud in scope', so this is now a LIVE blocker for Task 6, not a deferred hypothetical. It must be answered before T06-S02 is written.</t>
         </is>
       </c>
       <c r="F10" s="13" t="inlineStr">
@@ -7486,6 +7531,80 @@
         </is>
       </c>
       <c r="G10" s="13" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Recorded divergence, not a question: Task 5's fixtures were transcribed from the ComfyUI source, not captured from a running ComfyUI. The plan assumed a CPU ComfyUI on the laptop (Where = 'Laptop (CPU ComfyUI)'); there is no ComfyUI installed on this machine.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Nothing today - the plan already forbids live calls ('Fixtures only, never live'), and both adapters pass the conformance suite. It bites only if ComfyUI's real payloads differ from its own source in a way that reading the source cannot reveal.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Keep the transcribed fixtures. They were read from the authoritative source at a named version rather than from a client library or from memory, which is what AGENTS.md 6.2 asks for. If a ComfyUI is ever installed, re-capture /object_info, /history/{id} and a /queue response and diff them against the fixtures.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Agent judgement, 2026-09-09. Recorded rather than hidden. Version validated against: comfyui_version.py __version__ = 0.35.0, github.com/comfyanonymous/ComfyUI@master, read 2026-09-09. Every fixture carries a _source block with file, version, read date and what was trimmed. Second divergence in the same task: tests and implementation were written in one pass, so no separate RED was observed; four mutations were used as the evidence instead and each killed exactly one test.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Noted</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CONTRADICTION in the plan, Task 7 Step 5. It says to keep useAtomicMediaJob 'exported and delegating' to the new job manager. But web-app/src/hooks/useAtomicMediaJob.ts is one of the eleven files frozen by scripts/selective-v2032-protected.json, and so is its only consumer, web-app/src/containers/media/MediaStudio.tsx. Rewriting it to delegate would edit a protected file and force a FOURTH guard re-baseline.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Task 7 Step 5. Not Task 8 or later - nothing downstream reads useAtomicMediaJob.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Leave useAtomicMediaJob.ts and MediaStudio.tsx completely untouched in Task 7. Add jobManager.ts and useMediaGeneration.ts as new files only. The current Media Studio keeps working exactly as it does today, which is what Step 5's stated purpose ('so this task does not break the current UI') actually asks for. Task 11 is already designated as the task that edits the protected files, so the switchover belongs there. The alternative buys nothing visible today and costs a re-baseline of a frozen file.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ANSWERED BY THE USER in writing 2026-09-09: 'go with the first, leave useAtomicMediaJob alone'. Flagged to him rather than silently picked, per the working agreement. Consequence: Task 7 touches NO protected file, needs NO guard re-baseline, and needs no further authorisation on that front. useAtomicMediaJob keeps its current standalone implementation until Task 11 removes its last consumer.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Answered</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -7683,7 +7802,7 @@
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>30/30 for the Atomic Media Worker adapter. ONE adapter only - the phase gate is "two adapters pass one conformance suite", so this is half met until Task 5's ComfyUI adapter passes the same suite UNMODIFIED. An adapter-specific branch in the suite would mean the contract is wrong.</t>
+          <t>2026-09-09: both adapters that exist pass conformance.ts unmodified - Atomic Media Worker 30/30, ComfyUI 58/58 (30 conformance + 28 ComfyUI-specific). Still Partial only because Task 6's remote adapter does not exist yet.</t>
         </is>
       </c>
     </row>

--- a/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
+++ b/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
@@ -1081,7 +1081,7 @@
       </c>
       <c r="B7" s="22" t="inlineStr">
         <is>
-          <t>746c75579 docs(tracker): record Task 4 commit and backfill missing SHAs (pushed). Task 5's work is in the working tree, UNCOMMITTED, awaiting the user's authorisation.</t>
+          <t>051aa223e feat(media): add ComfyUI provider adapter - COMMITTED 2026-09-09, NOT PUSHED. Branch is ahead of origin/feature/atomic-code-foundation by 1. Ask the user before pushing.</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
@@ -1683,7 +1682,11 @@
           <t>Two adapters pass one conformance suite</t>
         </is>
       </c>
-      <c r="I8" s="13" t="n"/>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>051aa223e</t>
+        </is>
+      </c>
       <c r="J8" s="14" t="inlineStr">
         <is>
           <t>Fixtures only, never live. ComfyUI runs CPU-only and /object_info responds without generating.</t>

--- a/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
+++ b/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
@@ -1093,7 +1093,7 @@
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>Tasks 0-5 all Done. Task 5 is COMMITTED but NOT PUSHED - ask the user whether to push before starting anything else. Next work is Task 7 (T07-S01), by the user's explicit choice ahead of the now-unblocked Task 6. Task 7's scope is fixed by decision D5: leave useAtomicMediaJob.ts and MediaStudio.tsx untouched, new files only.</t>
+          <t>Tasks 0-5 and 7 Done. Task 6 is UNBLOCKED (Q2 answered: cloud IS in scope) but deferred by the user, and must NOT be started until D3 - where the API key is stored - is answered, because that is a security decision and his call. Otherwise the next not-Done row is Task 8 (T08-S01), which is unblocked now that Task 7 has landed.</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="B11" s="22" t="inlineStr">
         <is>
-          <t>2026-09-09 for Task 5: make verify EXITCODE=0 in a VS x64 developer shell (vcvars64.bat), GnuWin32 make on PATH, plus a printf-ONLY directory that also contains msys-2.0.dll / msys-intl-8.dll / msys-iconv-2.dll - printf.exe without its msys runtime cannot start and fails one Rust shell-contract test. Do NOT add Git's usr/bin wholesale: make then switches to sh and breaks the PowerShell stub-resources recipe, and Git's link.exe shadows MSVC's. Results: web-app 2426 passed/16 skipped, extension 250, llamacpp extension 276, Rust 487+12 passed/0 failed, coverage floor passed, Selective v2.0.32 boundaries verified.</t>
+          <t>2026-09-09 for Task 7: make verify EXITCODE=0 in a VS x64 developer shell. PRE-FLIGHT MUST INCLUDE 'node scripts/check-test-quality.mjs' - lint, tsc and vitest all passed while that guard was red. Environment reminder: vcvars64.bat, GnuWin32 make on PATH, plus a printf-ONLY directory that also contains msys-2.0.dll / msys-intl-8.dll / msys-iconv-2.dll (printf.exe without its msys runtime cannot start and fails one Rust shell-contract test). Do NOT add Git's usr/bin wholesale. ALWAYS read the log's own EXITCODE line - a wrapper's exit code reported 0 on three runs that were actually red.</t>
         </is>
       </c>
     </row>
@@ -1189,10 +1189,11 @@
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>Ask the user whether to push the Task 5 commit to origin/feature/atomic-code-foundation, and backfill its SHA into the Commit SHA column on the Tasks sheet (Task 4's SHA was backfilled the same way in 746c75579). Then start Task 7 at T07-S01. Task 6 is unblocked (Q2 answered: cloud IS in scope) but deferred by the user; do NOT start it until D3 - where the API key is stored - is answered, because that is a security decision and his call.</t>
-        </is>
-      </c>
-    </row>
+          <t>Raise D3 with the user if Task 6 is wanted next; otherwise start Task 8 (asset materialisation and the media library), which Task 7 has just unblocked. Task 10 (schema-driven parameter renderer) is also unblocked and is the plan's 'biggest single win' - it is what would make the ComfyUI adapter visible on screen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
@@ -1770,7 +1771,7 @@
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F10" s="13" t="n"/>
@@ -1792,7 +1793,7 @@
       </c>
       <c r="K10" s="15" t="inlineStr">
         <is>
-          <t>2026-09-09: agreed with the user as the next task after Task 5, ahead of the now-unblocked Task 6. Not started yet - Task 5's commit lands first so the two tasks' changes do not tangle in one working tree. SCOPE FIXED BY DECISION D5: leave useAtomicMediaJob.ts and MediaStudio.tsx UNTOUCHED. New files only (jobManager.ts, __tests__/jobManager.test.ts, hooks/useMediaGeneration.ts, hooks/useMediaGeneration.test.tsx). Task 7 therefore touches no protected file and needs no guard re-baseline.</t>
+          <t>2026-09-09: Task 7 complete, T07-S01..S07 all Done. Fixes C10 (jobs were ephemeral React state, lost on unmount), C11 (cancel cleared a timer and never told the worker) and C12 (fixed 1s poll, re-armed on error forever). New files only per D5 - useAtomicMediaJob.ts and MediaStudio.tsx untouched, and their suites still pass (5 and 6 tests). No protected file, no guard re-baseline. RED was genuinely observed first this time (T07-S02), unlike Task 5. 26 new tests; 7 mutations each kill exactly one test, two of which initially killed nothing and exposed real gaps that were closed. Contract gap found and recorded as D6: subscribe has no error channel.</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4180,7 @@
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F48" s="13" t="n"/>
@@ -4193,7 +4194,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I48" s="15" t="n"/>
+      <c r="I48" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09 Done. 18 tests written BEFORE any implementation existed, in services/media/__tests__/jobManager.test.ts, covering exactly what the plan listed: two concurrent jobs on two providers tracked independently; a job that keeps polling with nobody subscribed (C10); backoff 1s-2s-4s-8s capped at 10s (C12); give-up after N consecutive failures marking the job failed + retryable:true; the failure counter resetting on a successful poll; cancel not offered when features.cancel is false and REFUSED rather than silently no-opped (C11); real cancellation on a capable provider; and client_job_id idempotency.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
@@ -4216,7 +4221,7 @@
       </c>
       <c r="E49" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F49" s="13" t="n"/>
@@ -4230,7 +4235,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I49" s="15" t="n"/>
+      <c r="I49" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09 Done - RED genuinely observed this time, unlike Task 5 (see D4). Output: 'Failed to resolve import "../jobManager" from src/services/media/__tests__/jobManager.test.ts', Test Files 1 failed, 'Tests no tests'. Failing for the right reason: the module under test did not exist.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -4253,7 +4262,7 @@
       </c>
       <c r="E50" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F50" s="13" t="n"/>
@@ -4267,7 +4276,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I50" s="15" t="n"/>
+      <c r="I50" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09 Done. services/media/jobManager.ts - a module-scoped singleton (mediaJobManager) over a VANILLA zustand store (zustand/vanilla createStore), with no React import anywhere in the service. createMediaJobManager(deps) is exported separately so tests build their own instance with fake adapters. Per-job bookkeeping (timers, unsubscribe, attempt, failure count) is deliberately kept OUT of the store - none of it is renderable.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -4290,7 +4303,7 @@
       </c>
       <c r="E51" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F51" s="13" t="n"/>
@@ -4304,7 +4317,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I51" s="15" t="n"/>
+      <c r="I51" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09 Done. subscribe is preferred whenever capabilities.features.events is true and the adapter implements it, with polling as the fallback. Two fallback paths, because there are two ways a stream fails: subscribe THROWING (caught, polls immediately) and a stream going SILENT. See D6 - the contract's subscribe returns only an unsubscribe function and has no error channel, so a socket that dies quietly cannot be distinguished from one with nothing to say; a silence watchdog is the only defence. The subscription is kept alive, not torn down, so a recovered stream is still welcome.</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="26.4" customHeight="1">
       <c r="A52" s="6" t="inlineStr">
@@ -4327,7 +4344,7 @@
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F52" s="13" t="n"/>
@@ -4341,7 +4358,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I52" s="15" t="n"/>
+      <c r="I52" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09 Done. hooks/useMediaGeneration.ts subscribes to the manager's store and owns nothing. Selects the two stable slices (jobs, order) rather than a derived array, because zustand v5 compares with Object.is and a selector building a new array would re-render on every read. Per decision D5, useAtomicMediaJob.ts and MediaStudio.tsx were NOT touched - both are protected files and Task 11 is the designated task for them. Their suites still pass untouched (5 and 6 tests).</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
@@ -4364,7 +4385,7 @@
       </c>
       <c r="E53" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F53" s="13" t="n"/>
@@ -4378,7 +4399,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I53" s="15" t="n"/>
+      <c r="I53" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09 Done. 26/26 for the two new suites (19 jobManager + 7 useMediaGeneration); 229/229 across every media suite including the protected useAtomicMediaJob and MediaStudio ones. yarn lint 0 errors, tsc -b exit 0. Mutation tested: 7 mutations (backoff flattened; never gives up; give-up marked non-retryable; cancel silently no-ops; concurrent-submit guard removed; terminal job resurrectable; silence watchdog removed) each kill exactly one test. Two initially killed NOTHING and exposed real gaps that were then closed: the terminal-resurrection guard was unreachable because unsubscribe already detached the fake's listener, so a leaky-unsubscribe adapter case was added.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
@@ -4401,7 +4426,7 @@
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F54" s="13" t="n"/>
@@ -4415,7 +4440,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I54" s="15" t="n"/>
+      <c r="I54" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09 Done. Authorised by the user in writing ('commit and push it') after a genuinely green gate. make verify EXITCODE=0: web-app 2452 passed/16 skipped (up 26, exactly the new tests), extension 250, llamacpp extension 276, Rust 487+12+167+205+28+4 passed / 0 failed, coverage floor passed, 'Selective v2.0.32 boundaries verified'. NOTE: the FIRST verify attempt for this task was RED and neither lint nor tsc nor vitest caught it - scripts/check-test-quality.mjs did, with [call-only-assertions] against jobManager.test.ts. Five tests asserted only that a mock had been called, which passes even if the manager throws the result away. They were fixed with real behavioural assertions rather than added to tests/test-quality-allowlist.json. Run that guard in the pre-flight, not just lint + tsc + vitest.</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="26.4" customHeight="1">
       <c r="A55" s="6" t="inlineStr">
@@ -7189,7 +7218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7604,6 +7633,43 @@
         </is>
       </c>
       <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CONTRACT GAP found while building Task 7, not a plan contradiction. MediaProviderAdapter.subscribe returns only an unsubscribe function - it has no channel for telling the caller that the stream has died. A socket that drops quietly is therefore indistinguishable, from the job manager's side, from a healthy stream with nothing to report.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Nothing is blocked. It affects how honestly Task 7 Step 4's 'fall back to polling on stream error' can be implemented, and it would affect any future adapter that streams.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Not changing the contract now. Changing subscribe's signature would ripple into both existing adapters AND the conformance suite, which is a bigger change than this task should make on its own judgement. Implemented instead: subscribe throwing is caught and falls back immediately, and a silence watchdog (MEDIA_SUBSCRIBE_SILENCE_MS) starts polling alongside a stream that has said nothing for too long, keeping the subscription in case it recovers. If a third streaming adapter arrives, revisit and consider giving subscribe an onError callback.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Agent judgement, 2026-09-09, recorded rather than hidden. Flagged for the user because it is a real limitation of the v2 contract rather than of this implementation. The watchdog is covered by two tests: one proving it starts polling after silence, one proving it does NOT start while events keep arriving.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Noted</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>2026-09-09</t>
         </is>

--- a/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
+++ b/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
@@ -1081,7 +1081,7 @@
       </c>
       <c r="B7" s="22" t="inlineStr">
         <is>
-          <t>051aa223e feat(media): add ComfyUI provider adapter - COMMITTED 2026-09-09, NOT PUSHED. Branch is ahead of origin/feature/atomic-code-foundation by 1. Ask the user before pushing.</t>
+          <t>94d164c02 feat(media): add cross-provider media job manager - COMMITTED AND PUSHED 2026-09-09. Branch is in sync with origin/feature/atomic-code-foundation.</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
@@ -1785,7 +1784,11 @@
           <t>Job manager and library unit tests green</t>
         </is>
       </c>
-      <c r="I10" s="13" t="n"/>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>94d164c02</t>
+        </is>
+      </c>
       <c r="J10" s="14" t="inlineStr">
         <is>
           <t>Fake timers. Fixes C10, C11, C12.</t>

--- a/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
+++ b/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
@@ -1105,7 +1105,7 @@
       </c>
       <c r="B9" s="22" t="inlineStr">
         <is>
-          <t>Q1 Answered. Q2 ANSWERED 2026-09-09: cloud providers ARE in scope, so Task 6 is live (deferred by the user's choice, not skipped). Tasks 0-4 Done. Task 5 In progress (only the commit step remains). D1/D2/D4 Noted. D5 Answered 2026-09-09 (Task 7 leaves useAtomicMediaJob alone - no protected file, no re-baseline). D3 is now a LIVE blocker for Task 6. Q3-Q6 still Open. Next not-done step: T05-S06, then Task 7 (T07-S01).</t>
+          <t>Q1, Q2, D3, D5, Q5 all Answered. Tasks 0-5 and 7 Done and pushed. D1/D2/D4/D6 Noted. Q3, Q4, Q6 still Open. Task 6 is now FULLY UNBLOCKED (cloud in scope; OS credential store; four keyring crates approved for credential storage only). Task 8 and Task 10 are also unblocked. Nothing is waiting on the user.</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>Raise D3 with the user if Task 6 is wanted next; otherwise start Task 8 (asset materialisation and the media library), which Task 7 has just unblocked. Task 10 (schema-driven parameter renderer) is also unblocked and is the plan's 'biggest single win' - it is what would make the ComfyUI adapter visible on screen.</t>
+          <t>Ask the user which he wants next - nothing is blocked now. Task 6 (cloud adapter, now fully unblocked), Task 8 (asset materialisation and the media library, unblocked by Task 7), or Task 10 (schema-driven parameter renderer - the plan calls it the biggest single win, and it is what would finally make the ComfyUI adapter visible on screen; everything built so far is invisible plumbing). If Task 6: settle the Linux no-daemon fallback FIRST.</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
       <c r="F9" s="13" t="n"/>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>Q2 (answered - cloud IS in scope); D3 must be answered before starting</t>
+          <t>Q2, D3, Q5 all answered - UNBLOCKED</t>
         </is>
       </c>
       <c r="H9" s="14" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="K9" s="15" t="inlineStr">
         <is>
-          <t>2026-09-09: UNBLOCKED - Q2 answered 'yes, include cloud providers'. Deliberately DEFERRED, not skipped: the user chose Task 7 as the next piece of work. Strict tracker order would have taken Task 6 next; this deviation is the user's call, recorded here rather than made silently. Task 6 is self-contained and nothing downstream depends on it, so it can be slotted in at any point. Do NOT start it until D3 (where the API key is stored) is answered.</t>
+          <t>2026-09-09: FULLY UNBLOCKED. Q2 answered (cloud IS in scope), D3 answered (OS credential store), Q5 answered (the four keyring crates approved, for credential storage only). Not started. Before writing code: settle what keyring does on Linux with no Secret Service daemon and design the fallback. Note the user was told, and accepted, that cloud LLM api_keys remain in plaintext localStorage - hardening those is a separate piece of work he has not commissioned.</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,11 @@
           <t>GATED on Q3. Rust spawn/stop/restart testable against a stub process.</t>
         </is>
       </c>
-      <c r="K12" s="15" t="n"/>
+      <c r="K12" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09: still gated on Q3 (unanswered). Q5 was answered on 2026-09-09 but SCOPED to four credential-storage crates only - it is NOT approval for any dependency this task might want. Ask again, naming the crate and reason.</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="26.4" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
@@ -7423,13 +7427,21 @@
           <t>Plan aims for zero. AGENTS.md 6.6 requires a name-and-reason approval; ask at the point of need rather than assuming here.</t>
         </is>
       </c>
-      <c r="E6" s="15" t="n"/>
+      <c r="E6" s="15" t="inlineStr">
+        <is>
+          <t>ANSWERED BY THE USER 2026-09-09, SCOPED - this is an ok for FOUR NAMED CRATES FOR CREDENTIAL STORAGE ONLY, not a blanket yes to new dependencies. He was shown the names, the count and the reason before answering, per AGENTS.md rule 6. Approved: keyring 4.2 (core), windows-native-keyring-store, apple-native-keyring-store, and a Linux Secret Service backend (dbus-secret-service-keyring-store or zbus-). Target-gated, so exactly one backend compiles into any given build, but four Cargo.toml entries against a plan that aimed for zero. REASON: it is what D3's answer (OS credential store) requires; keyring 4.x keeps its platform backends as separate optional crates rather than bundling them as 3.x did. STILL NEEDS ITS OWN OK: any dependency for Task 9 (worker supervision) or Task 8 Step 5. This answer does not cover them - approval for one action is never approval for the next. UNRESOLVED, MUST BE SETTLED BEFORE T06 CODE IS WRITTEN: what keyring does on Linux when no Secret Service daemon is running. Not documented in docs.rs as fetched 2026-09-09, and it is a common case on minimal installs. A fallback path is needed or those users hit an error they cannot fix. Find out for certain; do not assume.</t>
+        </is>
+      </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="G6" s="13" t="n"/>
+          <t>Answered</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="26.4" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
@@ -7557,15 +7569,19 @@
       </c>
       <c r="E10" s="15" t="inlineStr">
         <is>
-          <t>Deferred to Task 6. Not guessed. | 2026-09-09 UPDATE: Q2 was answered 'cloud in scope', so this is now a LIVE blocker for Task 6, not a deferred hypothetical. It must be answered before T06-S02 is written.</t>
+          <t>ANSWERED BY THE USER 2026-09-09: the OS credential store (Windows Credential Manager, macOS Keychain, Linux Secret Service). NOT localStorage, which resolves the plan's contradiction in favour of the 'never in localStorage' clause and against 'the same way cloud LLM keys already are'. He was shown, and chose against, three alternatives: tauri-plugin-store (already a dependency, but plaintext on disk), localStorage (consistent with today but plaintext and readable from the web view), and never storing the key at all. Rationale given to him: it is the only option where the key is actually encrypted at rest rather than merely tucked away. CONSEQUENCE, RAISED SEPARATELY: this requires at least one new Rust runtime dependency, which AGENTS.md rule 6 says needs his explicit ok naming the crate and reason, and which is what Q5 asks. D3 is NOT blanket approval for Q5. COST OF CHANGING LATER: low for the code - the contract stores only auth.setting_key, a name, never a value, so the storage sits behind one indirection - but any keys already saved would need migrating. PRE-EXISTING AND UNTOUCHED: cloud LLM provider api_keys are in plaintext localStorage today via hooks/useModelProvider.ts, which persists its whole state with no partialize. Out of scope, but he has been told.</t>
         </is>
       </c>
       <c r="F10" s="13" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="G10" s="13" t="n"/>
+          <t>Answered</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">

--- a/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
+++ b/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
@@ -1093,7 +1093,7 @@
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>Tasks 0-5 and 7 Done. Task 6 is UNBLOCKED (Q2 answered: cloud IS in scope) but deferred by the user, and must NOT be started until D3 - where the API key is stored - is answered, because that is a security decision and his call. Otherwise the next not-Done row is Task 8 (T08-S01), which is unblocked now that Task 7 has landed.</t>
+          <t>Tasks 0-7 all Done. The next work is EITHER the OS credential store (Rust: keyring-core plus the three platform backends, approved in D3/Q5) which is what makes Task 6 actually usable, OR Task 8 (asset materialisation and the media library), OR Task 10 (schema-driven parameter renderer - the plan's 'biggest single win', and the first thing that would make any of this visible on screen; everything built so far is invisible plumbing).</t>
         </is>
       </c>
     </row>
@@ -1189,10 +1189,11 @@
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>Ask the user which he wants next - nothing is blocked now. Task 6 (cloud adapter, now fully unblocked), Task 8 (asset materialisation and the media library, unblocked by Task 7), or Task 10 (schema-driven parameter renderer - the plan calls it the biggest single win, and it is what would finally make the ComfyUI adapter visible on screen; everything built so far is invisible plumbing). If Task 6: settle the Linux no-daemon fallback FIRST.</t>
-        </is>
-      </c>
-    </row>
+          <t>Ask the user which of those three he wants. If the credential store: settle FIRST what keyring does on Linux with no Secret Service daemon - the crate's own docs acknowledge 'known issues' in headless environments and document no automatic fallback, so a fallback must be designed rather than discovered by a user. Do NOT silently downgrade to plaintext; surface the choice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
@@ -1721,7 +1722,7 @@
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F9" s="13" t="n"/>
@@ -1743,7 +1744,7 @@
       </c>
       <c r="K9" s="15" t="inlineStr">
         <is>
-          <t>2026-09-09: FULLY UNBLOCKED. Q2 answered (cloud IS in scope), D3 answered (OS credential store), Q5 answered (the four keyring crates approved, for credential storage only). Not started. Before writing code: settle what keyring does on Linux with no Secret Service daemon and design the fallback. Note the user was told, and accepted, that cloud LLM api_keys remain in plaintext localStorage - hardening those is a separate piece of work he has not commissioned.</t>
+          <t>2026-09-09: T06-S01..S06 Done. adapters/remoteHttp.ts + tests, and the contract gained features.synchronous (D7). The third adapter is what finally broke the contract - risk R3 in the plan, which survived adapter two and not three. NOT YET USABLE BY THE USER: no secret resolver is wired, because the OS credential store approved in D3/Q5 is follow-on work. providerFactory builds the adapter without a resolver, so a cloud provider reports unauthorised rather than silently sending a blank Authorization header. That Rust work (keyring-core plus three platform backends) is the next thing Task 6 needs to be real.</t>
         </is>
       </c>
     </row>
@@ -3969,7 +3970,7 @@
       </c>
       <c r="E42" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F42" s="13" t="n"/>
@@ -3983,7 +3984,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I42" s="15" t="n"/>
+      <c r="I42" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09 Done. Q2 confirmed answered in writing before any code: cloud IS in scope. D3 (OS credential store) and Q5 (four named crates) were also answered first. Surface read from the official OpenAI Node SDK SOURCE, not from docs prose and not from memory - the docs site returns 403 to automated fetches. src/resources/images.ts for the request/response shapes, src/core/error.ts for the {error:{message,type,param,code}} envelope and the 401/403/429 mapping.</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="26.4" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
@@ -4006,7 +4011,7 @@
       </c>
       <c r="E43" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F43" s="13" t="n"/>
@@ -4020,7 +4025,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I43" s="15" t="n"/>
+      <c r="I43" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09 Done, RED observed first: 'Failed to resolve import "../remoteHttp"', Test Files 1 failed, 'Tests no tests'. Tests cover exactly what the plan listed: bearer header injection, 401 -&gt; unauthorised health, 429 -&gt; retryable, an expires_at carried through when a provider sends one, and the key never reaching a console call or a thrown error. Plus a refusal to submit at all when no key is configured, so a blank Authorization header is never sent.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -4043,7 +4052,7 @@
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F44" s="13" t="n"/>
@@ -4053,7 +4062,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I44" s="15" t="n"/>
+      <c r="I44" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09 Done. adapters/remoteHttp.ts against the OpenAI-compatible images shape. Models are DECLARED, not discovered - GET /models lists chat models alongside image ones and cannot say which is which, the same reasoning as ComfyUI's templates. The secret is resolved through an injected resolveSecret, never read from the descriptor, and written to exactly one place: the Authorization header. It is deliberately never interpolated into an error message, because an error object is the most likely thing to reach a log line or a Sentry breadcrumb.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -4076,7 +4089,7 @@
       </c>
       <c r="E45" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F45" s="13" t="n"/>
@@ -4090,7 +4103,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I45" s="15" t="n"/>
+      <c r="I45" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09 Done - and the plan's premise was only HALF right, which matters. Verified in src-tauri/tauri.conf.json: img-src includes https:, so a remote IMAGE url renders directly; media-src does NOT include https:, so remote VIDEO and AUDIO are blocked. So skipping materialisation would appear to work for images and silently fail for video - an inconsistent failure that would ship. Materialisation stays mandatory. The adapter therefore returns url/inline MediaOutputRefs and never assumes the renderer can fetch them; Task 8 owns bringing them to disk.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
@@ -4113,7 +4130,7 @@
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F46" s="13" t="n"/>
@@ -4127,7 +4144,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I46" s="15" t="n"/>
+      <c r="I46" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09 Done. All THREE adapters now pass one conformance suite: 229 tests across 7 files in services/media. This is where the contract actually broke - see D7. The suite assumed every provider is job-based, which a synchronous cloud API is not. Resolved by CHANGING THE CONTRACT, not by bending the suite, exactly as the handover requires.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
@@ -4150,7 +4171,7 @@
       </c>
       <c r="E47" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F47" s="13" t="n"/>
@@ -4164,7 +4185,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I47" s="15" t="n"/>
+      <c r="I47" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09 Done. Committed after a green gate.</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="26.4" customHeight="1">
       <c r="A48" s="6" t="inlineStr">
@@ -7225,7 +7250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7689,6 +7714,43 @@
         </is>
       </c>
       <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>D7</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CONTRACT DEFECT found by the third adapter, which is what Task 5 predicted might happen (plan risk R3: 'the contract proves wrong on the second adapter'). It survived adapter two and failed on three. conformance.ts assumed every provider is job-based: that poll is a transport operation which can report queued -&gt; running -&gt; succeeded, be made to fail on demand, and forward an AbortSignal. An OpenAI-compatible images endpoint is SYNCHRONOUS - the finished image arrives in the submit response, so there is no job resource to query, nothing to abort, and no progression to observe. Three conformance tests could not pass; the other 34 did.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Task 6, and any future synchronous provider. Also the contract (models.ts), the shared conformance suite, and the two existing adapters' test files.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Change the CONTRACT, never the suite - the handover's rule. Added features.synchronous, declared by the provider, and gave ConformanceScenarios an optional synchronous() hook. The three tests that cannot apply now assert the DECLARATION instead of silently passing, copying the pattern the suite already used for unauthorised() on local providers that cannot authenticate. The assertions were made stronger, not weaker: a synchronous provider must declare queue:false, must still reach a terminal state through poll so no caller needs to know which kind it holds, and its poll must make NO network call - a second request would generate and charge twice.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ANSWERED BY THE USER 2026-09-09, having been shown the alternatives (ship with three known failures; drop synchronous providers entirely; pause for review). Raised rather than decided alone because it changes the contract and touches Tasks 1, 3 and 5. No existing adapter's behaviour changed - the Atomic Media Worker and ComfyUI simply declare synchronous() false.</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Answered</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>2026-09-09</t>
         </is>

--- a/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
+++ b/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
@@ -1081,7 +1081,7 @@
       </c>
       <c r="B7" s="22" t="inlineStr">
         <is>
-          <t>94d164c02 feat(media): add cross-provider media job manager - COMMITTED AND PUSHED 2026-09-09. Branch is in sync with origin/feature/atomic-code-foundation.</t>
+          <t>bfc35573f feat(media): add remote HTTP media provider adapter - COMMITTED AND PUSHED 2026-09-09.</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
@@ -1736,7 +1735,11 @@
           <t>Two adapters pass one conformance suite</t>
         </is>
       </c>
-      <c r="I9" s="13" t="n"/>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>bfc35573f</t>
+        </is>
+      </c>
       <c r="J9" s="14" t="inlineStr">
         <is>
           <t>GATED on Q2. Skip entirely if local-only. Cloud does the compute, so this is ideal laptop work.</t>

--- a/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
+++ b/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
@@ -1827,7 +1827,7 @@
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F11" s="13" t="n"/>
@@ -1847,7 +1847,11 @@
           <t>Mocked fs. Thumbnails are WebView2, not GPU.</t>
         </is>
       </c>
-      <c r="K11" s="15" t="n"/>
+      <c r="K11" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09: T08-S01..S04, S06, S07 Done; S05 PARTIAL - the thumbnailer is implemented but its canvas path cannot run under jsdom, so it awaits verification in the real app. Logged against Evidence row 10 with the other environment-limited steps, which is how this plan already handles GPU-only work. New: services/media/assets.ts, services/media/library.ts, stores/media-library-store.ts and two test files. No protected file touched. NOT WIRED: nothing calls materialize() yet - the job manager does not know the library exists, and the plan puts that meeting point in Tasks 11 and 13. New finding recorded as D8.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="26.4" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
@@ -4502,7 +4506,7 @@
       </c>
       <c r="E55" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F55" s="13" t="n"/>
@@ -4516,7 +4520,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I55" s="15" t="n"/>
+      <c r="I55" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09 Done. 31 tests written before either module existed: assets.test.ts (19) and library.test.ts (12). Covers exactly the plan's list - local_path adopted in place not copied, url fetched to outputs/&lt;yyyy&gt;/&lt;mm&gt;/, inline base64 decoded and written, mime to extension mapping, provenance capturing the FULL params bag, the index surviving a reload, a corrupt index.json degrading to empty with a warning, and the data folder always injected, never hardcoded.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
@@ -4539,7 +4547,7 @@
       </c>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F56" s="13" t="n"/>
@@ -4553,7 +4561,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I56" s="15" t="n"/>
+      <c r="I56" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09 Done, RED observed for both modules separately: 'Failed to resolve import "../assets"' and then 'Failed to resolve import "../library"', each with Test Files 1 failed / 'Tests no tests'.</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="26.4" customHeight="1">
       <c r="A57" s="6" t="inlineStr">
@@ -4576,7 +4588,7 @@
       </c>
       <c r="E57" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F57" s="13" t="n"/>
@@ -4590,7 +4602,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I57" s="15" t="n"/>
+      <c r="I57" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09 Done. services/media/assets.ts. Bytes go to a .partial and are promoted by rename - the jan_utils::backend_bundle pattern - and a failed write removes the .partial rather than leaving it looking like an asset. Per-asset ceiling MEDIA_ASSET_MAX_BYTES (512 MiB), configurable per call. Filesystem access goes through a small MediaFileSystem port so the whole module tests against a Map, with no disk and no Tauri.</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="26.4" customHeight="1">
       <c r="A58" s="6" t="inlineStr">
@@ -4613,7 +4629,7 @@
       </c>
       <c r="E58" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F58" s="13" t="n"/>
@@ -4627,7 +4643,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I58" s="15" t="n"/>
+      <c r="I58" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09 Done. services/media/library.ts. schema_version written from the first save. Writes are atomic (temp + rename) and COALESCED - three changes in one turn produce one rewrite, so a batch of eight images does not serialise the whole library eight times, which is what 'never block the UI on a full index rewrite' actually requires. Two failure modes are deliberate: a corrupt or wrongly-shaped index degrades to empty WITH a warning rather than throwing; and an index whose schema_version is NEWER than this build puts the library into read-only mode and is never overwritten. Degrading to empty is survivable, destroying a library an upgraded app wrote is not.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
@@ -4650,7 +4670,7 @@
       </c>
       <c r="E59" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F59" s="13" t="n"/>
@@ -4664,7 +4684,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I59" s="15" t="n"/>
+      <c r="I59" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09 PARTIAL - implemented but NOT verified, and marked Partial rather than Done on purpose. createBrowserThumbnailer() in assets.ts does the canvas downscale to WebP for images and a first-frame capture through a detached &lt;video&gt; for video, seeking ~0.1s in to avoid the black first frame many encoders emit, and revoking its blob URL so nothing holds a reference to a large video. What is TESTED is the contract around it: thumbnailing is optional and its failure is non-fatal, proven by a test that throws from the thumbnailer and asserts the asset is still saved with thumb_path undefined. What is NOT tested is the canvas path itself - jsdom implements neither HTMLCanvasElement.toBlob nor video decoding, so it cannot run here. Needs a real WebView2 to verify. Belongs with Evidence row 8.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
@@ -4687,7 +4711,7 @@
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F60" s="13" t="n"/>
@@ -4701,7 +4725,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I60" s="15" t="n"/>
+      <c r="I60" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09 Done. 31/31 for the two new suites; 260 passing across all 9 services/media suites. yarn lint 0 errors, tsc -b TSC_EXIT=0, test-quality guard passed (277 files). NOTE: tsc caught a real error the tests could not - a Uint8Array is not a valid BlobPart because it may be backed by a SharedArrayBuffer. Also a reminder that 'echo exit=$?' after a PIPE reports the pipeline's status, not the command's; that has now hidden a failure three times in this project. Capture the exit code directly.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
@@ -4724,7 +4752,7 @@
       </c>
       <c r="E61" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F61" s="13" t="n"/>
@@ -4738,7 +4766,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I61" s="15" t="n"/>
+      <c r="I61" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09 Done. make verify EXITCODE=0: web-app 2520 passed/16 skipped (up 31, exactly the new tests), extension 250, llamacpp extension 276, Rust suites green, coverage floor passed, test-quality guard passed (277 files), Selective v2.0.32 boundaries verified.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
@@ -7253,7 +7285,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7754,6 +7786,43 @@
         </is>
       </c>
       <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>D8</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CONTRACT GAP found building Task 8's provenance. MediaJobSnapshot has no field in which a provider can report the seed it actually used. The contract says an empty seed means 'the provider picks one', and the ComfyUI adapter duly randomises it inside buildGraph - but that number is then unrecoverable. So for any generation where the user left the seed blank, provenance.resolved_seed is genuinely unknown.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Not blocking. It degrades section 4.5's stated purpose: 're-run', 're-run with a new seed' and a truthful answer to 'how did I make this?' all depend on the seed. Bites Task 13 (library detail and re-run) most.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Recorded, not silently papered over. materialize() sets resolved_seed ONLY when the caller supplied a numeric seed, and omits it otherwise - a fabricated 0 would make 're-run identically' quietly produce a different image, which is worse than an honest gap. Two ways to close it properly, both bigger than Task 8: add a resolved_params/resolved_seed field to MediaJobSnapshot so a provider can report what it chose, or move seed resolution out of the adapters so the caller always knows. The second is cleaner and needs no contract change, but changes ComfyUI adapter behaviour. Decide before Task 13.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Agent judgement, 2026-09-09. Flagged to the user rather than hidden, in the same spirit as D6 and D7. Covered by a test that asserts resolved_seed is undefined when the seed was left to the provider.</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Noted</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>2026-09-09</t>
         </is>
@@ -8127,7 +8196,11 @@
         </is>
       </c>
       <c r="F11" s="15" t="n"/>
-      <c r="G11" s="15" t="n"/>
+      <c r="G11" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-09: add the Task 8 thumbnailer to this list. createBrowserThumbnailer() (canvas downscale to WebP for images, first-frame capture for video) cannot be exercised under jsdom, which implements neither HTMLCanvasElement.toBlob nor video decoding. Its failure path IS tested - a throwing thumbnailer still saves the asset. The success path needs a real WebView2.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">

--- a/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
+++ b/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
@@ -1081,7 +1081,7 @@
       </c>
       <c r="B7" s="22" t="inlineStr">
         <is>
-          <t>bfc35573f feat(media): add remote HTTP media provider adapter - COMMITTED AND PUSHED 2026-09-09.</t>
+          <t>a635958f5 feat(media): materialise outputs and persist a media library - COMMITTED AND PUSHED 2026-09-09.</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,11 @@
           <t>Job manager and library unit tests green</t>
         </is>
       </c>
-      <c r="I11" s="13" t="n"/>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>a635958f5</t>
+        </is>
+      </c>
       <c r="J11" s="14" t="inlineStr">
         <is>
           <t>Mocked fs. Thumbnails are WebView2, not GPU.</t>

--- a/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
+++ b/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
@@ -1093,7 +1093,7 @@
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>Tasks 0-7 all Done. The next work is EITHER the OS credential store (Rust: keyring-core plus the three platform backends, approved in D3/Q5) which is what makes Task 6 actually usable, OR Task 8 (asset materialisation and the media library), OR Task 10 (schema-driven parameter renderer - the plan's 'biggest single win', and the first thing that would make any of this visible on screen; everything built so far is invisible plumbing).</t>
+          <t>Tasks 0-8 and 10 Done. Next is Task 11 (refit the Media Studio onto the platform) - it is the first task that EDITS THE PROTECTED FILES (MediaGenerationForm.tsx, MediaStudio.tsx, useAtomicMediaJob.ts), so it needs a guard re-baseline and the user's explicit authorisation for it under the Q1 rule. It is also the task that finally makes all of this visible on screen: everything built so far is working, tested plumbing that the user cannot yet see.</t>
         </is>
       </c>
     </row>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F13" s="13" t="n"/>
@@ -1949,7 +1949,11 @@
           <t>Pure React + RTL. Biggest single win, needs nothing but a laptop.</t>
         </is>
       </c>
-      <c r="K13" s="15" t="n"/>
+      <c r="K13" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-10: T10-S01..S06 Done, T10-S07 (commit) pending the gate. Fixes coupling C5 - roughly 180 lines of hand-written controls in a FROZEN file, which is why adding one parameter used to mean editing the protected surface. New: containers/media/params/{MediaParamField.tsx, MediaParamGroup.tsx, useMediaParamState.ts, paramIdentity.ts} plus one test file. No protected file touched. Also extracted visibleParams() from validateParams in contract/params.ts and exported it, so the renderer decides what to DRAW using the same function that decides what to SUBMIT - a second depends_on implementation in the UI would have drifted from the first one the moment either changed. Behaviour-preserving: the 85 contract tests still pass. NOT WIRED YET: MediaGenerationForm.tsx still hand-writes its controls. Task 11 is where the Media Studio is refitted onto this, and Task 11 is the task that edits the protected files.</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="26.4" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
@@ -5019,7 +5023,7 @@
       </c>
       <c r="E68" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F68" s="13" t="n"/>
@@ -5033,7 +5037,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I68" s="15" t="n"/>
+      <c r="I68" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-10 Done. 32 tests written before any of the three modules existed: one per MediaParamType (string, text, int, float, bool, enum, seed, resolution, image_ref/audio_ref, stringlist), plus depends_on hiding and re-showing a field AND dropping its value from the submitted bag, advanced collapsing behind a disclosure, an unknown MediaParamType rendering disabled with a 'not supported by this version' note instead of crashing, modulus quantising on blur with ties breaking DOWN exactly as nearestFrame does, and resolution rendering one control.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
@@ -5056,7 +5064,7 @@
       </c>
       <c r="E69" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F69" s="13" t="n"/>
@@ -5070,7 +5078,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I69" s="15" t="n"/>
+      <c r="I69" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-10 Done, RED observed: 'Failed to resolve import "../MediaParamField"', Test Files 1 failed, 'Tests no tests'.</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="26.4" customHeight="1">
       <c r="A70" s="6" t="inlineStr">
@@ -5093,7 +5105,7 @@
       </c>
       <c r="E70" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F70" s="13" t="n"/>
@@ -5107,7 +5119,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I70" s="15" t="n"/>
+      <c r="I70" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-10 Done. containers/media/params/MediaParamField.tsx. fieldClass and labelClass copied VERBATIM from MediaGenerationForm.tsx:11-14 so the rendered result is visually identical. Every well-known id and aria-label preserved exactly - they are not derivable (negative_prompt is media-negative, guidance_scale is media-guidance) so they are listed, and anything else gets media-&lt;id&gt;. An unknown type renders inert and explained rather than taking the form down.</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="26.4" customHeight="1">
       <c r="A71" s="6" t="inlineStr">
@@ -5130,7 +5146,7 @@
       </c>
       <c r="E71" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F71" s="13" t="n"/>
@@ -5144,7 +5160,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I71" s="15" t="n"/>
+      <c r="I71" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-10 Done. containers/media/params/MediaParamGroup.tsx. Known groups core, output, sampling, motion, advanced first; unknown groups after, alphabetically; order within a group; id as the final tiebreak so two specs sharing an order never swap places between renders.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
@@ -5167,7 +5187,7 @@
       </c>
       <c r="E72" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F72" s="13" t="n"/>
@@ -5181,7 +5201,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I72" s="15" t="n"/>
+      <c r="I72" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-10 Done. containers/media/params/useMediaParamState.ts. Applies defaults on first render and re-applies them when the SCHEMA changes - keyed on shape, not array identity, or a fresh array every render would reset the form constantly. Correction runs on BLUR, never on change: clamping mid-keystroke means someone typing 120 watches it become 1, then 12. Quantisation delegates to validateParams rather than reimplementing nearestFrame, so there is one tie-breaking rule and Task 2's parity test still covers it.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
@@ -5204,7 +5228,7 @@
       </c>
       <c r="E73" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F73" s="13" t="n"/>
@@ -5218,7 +5242,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I73" s="15" t="n"/>
+      <c r="I73" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-10 Done. 32/32 for the new suite; 298 across containers/media and services/media. Six mutations each kill at least one test: unknown type treated as supported; well-known dom ids not preserved (kills 3); group order ignored (kills 2); correction applied while typing instead of on blur; defaults not re-applied on a model switch; the renderer ignoring depends_on visibility. The test-quality guard was run IN THE PRE-FLIGHT this time - lesson from Task 7 - and caught a call-only assertion before the gate did. Fixed the test rather than allowlisting it. Also moved the non-component exports into paramIdentity.ts, which is a fifth file beyond the plan's list, because react-refresh/only-export-components flagged four new warnings and the rule's own advice is to put shared constants in their own file. Lint is back to the pre-existing 13 warnings.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
@@ -5241,7 +5269,7 @@
       </c>
       <c r="E74" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F74" s="13" t="n"/>
@@ -5255,7 +5283,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I74" s="15" t="n"/>
+      <c r="I74" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-10 Done. make verify EXITCODE=0: web-app 2552 passed/16 skipped (up 32, exactly the new tests), extension 250, llamacpp extension 276, Rust green, coverage floor passed, test-quality guard passed, Selective v2.0.32 boundaries verified.</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="26.4" customHeight="1">
       <c r="A75" s="6" t="inlineStr">

--- a/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
+++ b/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
@@ -1081,7 +1081,7 @@
       </c>
       <c r="B7" s="22" t="inlineStr">
         <is>
-          <t>a635958f5 feat(media): materialise outputs and persist a media library - COMMITTED AND PUSHED 2026-09-09.</t>
+          <t>642223616 feat(media): render generation parameters from schema - COMMITTED AND PUSHED 2026-09-10.</t>
         </is>
       </c>
     </row>
@@ -1943,7 +1943,11 @@
           <t>make verify-fast green; visual parity</t>
         </is>
       </c>
-      <c r="I13" s="13" t="n"/>
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>642223616</t>
+        </is>
+      </c>
       <c r="J13" s="14" t="inlineStr">
         <is>
           <t>Pure React + RTL. Biggest single win, needs nothing but a laptop.</t>

--- a/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
+++ b/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
@@ -1982,13 +1982,13 @@
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F14" s="13" t="n"/>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>Task 0, Task 10</t>
+          <t>Task 0, Task 10 - AUTHORISED 2026-09-10</t>
         </is>
       </c>
       <c r="H14" s="14" t="inlineStr">
@@ -2002,7 +2002,11 @@
           <t>EDITS THE PROTECTED FILES - Task 0 must be green first. Includes the payload-parity regression test.</t>
         </is>
       </c>
-      <c r="K14" s="15" t="n"/>
+      <c r="K14" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-10: S01 Done (visual-parity guard, no protected file touched). Both blockers CLEARED by the user on 2026-09-10. (1) AUTHORISED to proceed: S04-S08 edit SEVEN of the eleven protected files (MediaGenerationForm.tsx, MediaStudio.tsx, MediaPreview.tsx, MediaJobStatus.tsx, MediaStudio.test.tsx, useAtomicMediaJob.ts + its test, the last two deleted) and S10 re-baselines the guard - he gave the explicit ok for this specific task, re-baseline included, per Q1's rule. (2) Q4 ANSWERED: always materialise, CSP untouched. Verified while sizing the work, not assumed: tauri.conf.json img-src allows https: but media-src does NOT, so today's toPreviewSrc https: passthrough renders a remote IMAGE fine and silently blocks a remote VIDEO. That is the CSP bug the step note names.</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="26.4" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
@@ -5314,7 +5318,7 @@
       </c>
       <c r="E75" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F75" s="13" t="n"/>
@@ -5328,7 +5332,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I75" s="15" t="n"/>
+      <c r="I75" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-10 Done. New file containers/media/__tests__/visualParity.test.tsx - 19 tests, NO protected file touched. Pins the RENDERED SURFACE (control inventory and DOM order, visible captions, aria-labels, model/device/resolution defaults, frame-rule and range bounds, guidance step 0.1, blur-quantisation with ties DOWN, Generate gating, and the three non-happy-path states); Task 2's parity.test.tsx already pins the submitted payload, so the two together are what make 'refit' provable. Every expected value is read from the fixture, so it cannot drift from the payload the worker reported. Eight mutations of MediaGenerationForm each kill at least one test: visible label rename (1), drop step=0.1 (1), frame tie-break &lt;= to &lt; (1), reorder Seed above Frames (4), input-image shown in every mode (3), hardcoded Frames min (1), fps default not applied (1), quantise on change not blur (1). The label mutation initially killed NOTHING and exposed a real gap - getByLabelText matches an aria-label, so a renamed VISIBLE caption went unnoticed; closed with a visibleLabels() helper reading label[for] text. Pre-flight: check-test-quality PASSED (279 files), tsc --noEmit clean, media suite 803 passed / 54 files.</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="26.4" customHeight="1">
       <c r="A76" s="6" t="inlineStr">
@@ -7325,7 +7333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7498,13 +7506,21 @@
           <t>Keep CSP as it is and always materialise. Widening media-src weakens every surface, not just Media.</t>
         </is>
       </c>
-      <c r="E5" s="15" t="n"/>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>ANSWERED BY THE USER 2026-09-10: ALWAYS MATERIALISE. The CSP is left exactly as it is and media-src is NOT widened to https:. Every provider output is downloaded to a local file before the preview points at it, so toPreviewSrc's https: passthrough is deleted in T11-S06 rather than accommodated. He was shown the verified evidence rather than the plan's assertion: tauri.conf.json line 27 img-src ALREADY allows https: but line 28 media-src does NOT, so a remote IMAGE renders today while a remote VIDEO is silently blocked - the passthrough is a latent bug, not a working feature being removed. Alternatives he was shown and chose against: widen media-src (less code, but weakens a protection covering the whole app, not just Media, and remote assets break offline). COST OF REVERSING LATER: low - it is one branch in toPreviewSrc plus one CSP line. CONSEQUENCE: Task 8's materialize() is now load-bearing for the preview, and D8's unresolved-seed gap becomes more visible in Task 13.</t>
+        </is>
+      </c>
       <c r="F5" s="13" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="G5" s="13" t="n"/>
+          <t>Answered</t>
+        </is>
+      </c>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="26.4" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
@@ -7865,6 +7881,43 @@
       <c r="G15" t="inlineStr">
         <is>
           <t>2026-09-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>D9</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CONTRADICTION in the plan, Task 11 Step 1. It says to 'write the FAILING visual-parity test first', but the same step defines that test as 'same controls, order, labels, defaults, bounds AND the same submitted payload AS TODAY'. A test that pins today's behaviour is green against today's code by construction; one that failed today would be pinning something other than today's behaviour.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Nothing. Task 11 Step 1 only.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Wrote it as a CHARACTERISATION test: green before the refit and required to stay green after it, which is what a parity guard is for and is the same shape Task 2's parity.test.tsx already uses ('this test is what must still pass afterwards'). Because green-by-construction is exactly the false confidence this plan keeps catching, it was mutation-tested instead of RED-tested: eight mutations of MediaGenerationForm, each killing at least one test, and one of them found a real gap that was then closed. The genuinely-red-first tests for Task 11 are Step 2's, which cover behaviour that does not exist yet (capability-driven tabs, provider selector, cross-provider routing, cancel gating).</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Agent judgement, 2026-09-10. Flagged rather than quietly picked, per the working agreement.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Noted</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>

--- a/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
+++ b/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
@@ -7333,7 +7333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7916,6 +7916,43 @@
         </is>
       </c>
       <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>D10</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>TASK 11's PHASE GATE CANNOT BE MET AS WRITTEN, plus one defect found and fixed on the way. The gate is 'visual parity', and T11-S01's own wording is 'same controls, order, labels, defaults, bounds as today'. Driving the form from the Task 10 schema renderer necessarily REORDERS it, because that renderer lays out by GROUP (core, output, sampling, motion, advanced) while today's form is a hand-written sequence. The two cannot both hold. THE DEFECT (fixed): the upcaster set no `order` on any spec, so within a group every spec tied and the renderer's last-resort alphabetical id tiebreak decided the layout - Guidance above Steps, FPS above Frames, both backwards. Task 2 wrote the upcaster before Task 10 built the renderer, so there was nothing to order against at the time.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Task 11 Steps 4 and 5, and the Phase 4 gate for Tasks 11-14.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>MEASURED, not predicted - MediaParamGroups was rendered against the upcast fixture and the DOM order read back. TODAY: model, resolution, device, frames, fps, steps, guidance, seed, negative, prompt. AFTER the order fix: prompt, negative, resolution, steps, guidance, frames, fps (plus model/device as structural selectors, and seed behind the Advanced disclosure). The order fix landed because it is correct under any answer below. THREE differences remain and they are the user's call, not the agent's: (1) prompt and negative prompt rise to the top, where today prompt sits at the bottom in its own composer card alongside the Generate button; (2) sampling (steps, guidance) now precedes motion (frames, fps); (3) seed is behind the Advanced disclosure rather than always visible - a deliberate Task 2 choice already covered by the test 'maps supports.seed to a seed param behind Advanced'.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>ANSWERED BY THE USER 2026-09-10: keep the PROMPT COMPOSER where it is - its own card at the bottom, beside the Generate button - and accept the grouped order for everything else, with seed left behind the Advanced disclosure. So the refit EXCLUDES the `prompt` spec from the schema-rendered grid and renders it in the composer, exactly as today. Rationale given to him and accepted: the Generate button lives with the prompt, and hoisting the prompt to the top of a settings grid would put the primary input and its action at opposite ends of the panel. Alternatives he was shown and chose against: accept the pure grouped layout (simplest code, but splits prompt from Generate), and reproduce today's order exactly (familiar, but hard-codes one legacy provider's layout into the general system that every future provider inherits). CONSEQUENCE: the Phase 4 gate 'visual parity' is hereby redefined for Tasks 11-14 as SAME CONTROLS, LABELS, DEFAULTS, BOUNDS AND SUBMITTED PAYLOAD - not same DOM order. T11-S01's visualParity.test.tsx must therefore be updated to pin the agreed order rather than today's, and that update is a deliberate, recorded change rather than a test weakened to fit the code. The payload parity test from Task 2 is unaffected and stays byte-exact.</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Answered</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>

--- a/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
+++ b/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
@@ -5359,7 +5359,7 @@
       </c>
       <c r="E76" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F76" s="13" t="n"/>
@@ -5373,7 +5373,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I76" s="15" t="n"/>
+      <c r="I76" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-10 Done. New file containers/media/__tests__/platform.test.tsx - 18 tests for behaviour that did not exist: tabs derived from declared tasks (incl. image_to_image, coupling C3, plus an unknown task rendering by id rather than being dropped), the provider selector, cross-provider routing, and cancel gating.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
@@ -5396,7 +5400,7 @@
       </c>
       <c r="E77" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F77" s="13" t="n"/>
@@ -5410,7 +5414,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I77" s="15" t="n"/>
+      <c r="I77" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-10 Done. RED observed for the right reasons: 'Unable to find an accessible element with the role tab', 'Unable to find a label with the text of: Provider', and no Cancel button. 15 of 18 failed; the 3 that passed were the negative cancel cases, vacuously.</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="26.4" customHeight="1">
       <c r="A78" s="6" t="inlineStr">
@@ -5433,7 +5441,7 @@
       </c>
       <c r="E78" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F78" s="13" t="n"/>
@@ -5447,7 +5455,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I78" s="15" t="n"/>
+      <c r="I78" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-10 Done. MODES, the Mode type and all eight bespoke control blocks deleted; 489 lines -&gt; 293. Tabs come from the tasks prop, controls from MediaParamGroups. Prompt stays in its own composer card per D10 - still schema-owned (validated and submitted like any param), only drawn elsewhere. PARITY REGRESSION CAUGHT BY THE REWRITTEN parity.test.tsx, not by review: the refit initially left device unset, where v1 defaulted it to fitness.required_device; the submitted body would have silently lost device: cuda:0. Fixed with an effect keyed on the model.</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="26.4" customHeight="1">
       <c r="A79" s="6" t="inlineStr">
@@ -5470,7 +5482,7 @@
       </c>
       <c r="E79" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F79" s="13" t="n"/>
@@ -5484,7 +5496,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I79" s="15" t="n"/>
+      <c r="I79" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-10 Done. MediaStudio now reads the provider store and the job manager: tasks unioned across enabled providers, models filtered by task, devices from the selected model's provider, header reads 'model . provider.label'. Also wires Task 8's materialisation, which the plan puts here - new hook useMediaJobAsset (7 tests) materialises a succeeded job exactly once and adds it to the library.</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="26.4" customHeight="1">
       <c r="A80" s="6" t="inlineStr">
@@ -5507,7 +5523,7 @@
       </c>
       <c r="E80" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F80" s="13" t="n"/>
@@ -5521,7 +5537,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I80" s="15" t="n"/>
+      <c r="I80" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-10 Done. MediaPreview takes a materialised MediaAsset, so toPreviewSrc has NO passthrough branch at all - the https: CSP bug is deleted rather than accommodated, per Q4. Added audio and an honest 'preview not available' for model3d/unknown instead of a broken player. 6 tests, one of which asserts no rendered src is ever http(s).</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
@@ -5544,7 +5564,7 @@
       </c>
       <c r="E81" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F81" s="13" t="n"/>
@@ -5558,7 +5578,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I81" s="15" t="n"/>
+      <c r="I81" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-10 Done. Per-provider health rows replace the single global worker state, each with its own Retry. Cancel renders only when the job manager reports cancellable AND the job is non-terminal - the fix for C11's no-op cancel.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
@@ -5581,7 +5605,7 @@
       </c>
       <c r="E82" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F82" s="13" t="n"/>
@@ -5591,7 +5615,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I82" s="15" t="n"/>
+      <c r="I82" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-10 Done. useAtomicMediaJob.ts and useAtomicMediaJob.test.tsx deleted; no consumer remained. MediaStudio.test.tsx rewritten to seed the REAL provider store instead of mocking the deleted hook (10 tests).</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="26.4" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
@@ -5614,7 +5642,7 @@
       </c>
       <c r="E83" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F83" s="13" t="n"/>
@@ -5628,7 +5656,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I83" s="15" t="n"/>
+      <c r="I83" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-10 Done. Media suite 832 passed / 56 files. FULL web suite 2442 passed / 11 skipped / 214 files, run from the repo root as make does. Measured baseline at HEAD with the changes stashed: 2416 / 212 files - so +26 tests and +2 files, no coverage lost. tsc --noEmit clean; eslint clean; test-quality guard PASSED after it caught two call-only-assertion tests, which were strengthened rather than allowlisted. NOTE for the next agent: running vitest with cwd=web-app makes 9 external-contracts tests fail with ENOENT - that test computes its repo root with endsWith('/web-app'), which is false on Windows backslash paths. Run from the repo root, as make does, and they pass. Pre-existing and unrelated; confirmed by reproducing it with all changes stashed.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
@@ -5651,7 +5683,7 @@
       </c>
       <c r="E84" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F84" s="13" t="n"/>
@@ -5665,7 +5697,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I84" s="15" t="n"/>
+      <c r="I84" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-10 Guard confirmed RED first, exit code 1 read from the script itself rather than a wrapper: 5 protected files changed, 2 missing (deleted). Re-baselined in its own isolated single-purpose commit, per Q1's rule.</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="26.4" customHeight="1">
       <c r="A85" s="6" t="inlineStr">

--- a/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
+++ b/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
@@ -1081,7 +1081,7 @@
       </c>
       <c r="B7" s="22" t="inlineStr">
         <is>
-          <t>642223616 feat(media): render generation parameters from schema - COMMITTED AND PUSHED 2026-09-10.</t>
+          <t>e5ee6f793 chore(guard): re-baseline the selective v2.0.32 protected surface - 2026-09-10.</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>Tasks 0-8 and 10 Done. Next is Task 11 (refit the Media Studio onto the platform) - it is the first task that EDITS THE PROTECTED FILES (MediaGenerationForm.tsx, MediaStudio.tsx, useAtomicMediaJob.ts), so it needs a guard re-baseline and the user's explicit authorisation for it under the Q1 rule. It is also the task that finally makes all of this visible on screen: everything built so far is working, tested plumbing that the user cannot yet see.</t>
+          <t>Tasks 0-8, 10 and 11 Done. Task 11 is finished and the Media Studio now runs entirely on the platform - this is the first time any of Tasks 1-10 is visible on screen. Next is Task 12 (provider and model management UI, gated only on Task 4, which is Done) or Task 13 (media library route, gated on Task 8, Done). Task 9 is still gated on Q3, which is OPEN. Before Task 13, settle D8 - the unresolved-seed gap - because re-run depends on it.</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="B11" s="22" t="inlineStr">
         <is>
-          <t>2026-09-09 for Task 7: make verify EXITCODE=0 in a VS x64 developer shell. PRE-FLIGHT MUST INCLUDE 'node scripts/check-test-quality.mjs' - lint, tsc and vitest all passed while that guard was red. Environment reminder: vcvars64.bat, GnuWin32 make on PATH, plus a printf-ONLY directory that also contains msys-2.0.dll / msys-intl-8.dll / msys-iconv-2.dll (printf.exe without its msys runtime cannot start and fails one Rust shell-contract test). Do NOT add Git's usr/bin wholesale. ALWAYS read the log's own EXITCODE line - a wrapper's exit code reported 0 on three runs that were actually red.</t>
+          <t>2026-09-10 for Task 11: make verify-fast EXITCODE=0 and make test-selective-v2032 EXITCODE=0, both read from the command's own exit code. Full web suite 2442 passed / 214 files from the REPO ROOT. WARNING: run vitest from the repo root, not from web-app - src/services/__tests__/external-contracts.test.ts computes its repo root with endsWith('/web-app'), which is false on Windows backslash paths, so 9 tests fail with ENOENT for no real reason. FULL make verify was NOT run on 2026-09-10: MSVC was not on the shell's PATH and Git's link.exe shadowed it. Task 11 touches no Rust, but the full gate is still owed.</t>
         </is>
       </c>
     </row>
@@ -1189,10 +1189,11 @@
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>Ask the user which of those three he wants. If the credential store: settle FIRST what keyring does on Linux with no Secret Service daemon - the crate's own docs acknowledge 'known issues' in headless environments and document no automatic fallback, so a fallback must be designed rather than discovered by a user. Do NOT silently downgrade to plaintext; surface the choice.</t>
-        </is>
-      </c>
-    </row>
+          <t>Run the full make verify in a VS x64 developer shell to close out Task 11 properly - it is the one gate this session could not run. Then ask the user which of Task 12 or Task 13 he wants next, and raise Q3 if Task 9 is being considered.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
@@ -1982,7 +1983,7 @@
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F14" s="13" t="n"/>
@@ -1996,7 +1997,11 @@
           <t>make verify-fast green; visual parity</t>
         </is>
       </c>
-      <c r="I14" s="13" t="n"/>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>refit + e5ee6f793 (guard re-baseline)</t>
+        </is>
+      </c>
       <c r="J14" s="14" t="inlineStr">
         <is>
           <t>EDITS THE PROTECTED FILES - Task 0 must be green first. Includes the payload-parity regression test.</t>
@@ -2004,7 +2009,7 @@
       </c>
       <c r="K14" s="15" t="inlineStr">
         <is>
-          <t>2026-09-10: S01 Done (visual-parity guard, no protected file touched). Both blockers CLEARED by the user on 2026-09-10. (1) AUTHORISED to proceed: S04-S08 edit SEVEN of the eleven protected files (MediaGenerationForm.tsx, MediaStudio.tsx, MediaPreview.tsx, MediaJobStatus.tsx, MediaStudio.test.tsx, useAtomicMediaJob.ts + its test, the last two deleted) and S10 re-baselines the guard - he gave the explicit ok for this specific task, re-baseline included, per Q1's rule. (2) Q4 ANSWERED: always materialise, CSP untouched. Verified while sizing the work, not assumed: tauri.conf.json img-src allows https: but media-src does NOT, so today's toPreviewSrc https: passthrough renders a remote IMAGE fine and silently blocks a remote VIDEO. That is the CSP bug the step note names.</t>
+          <t>2026-09-10: Task 11 COMPLETE, S01-S11 all Done. This is the task that made Tasks 1-10 visible: MODES and all eight bespoke control blocks deleted (489 lines -&gt; 293), tabs and controls now come from what providers declare, useAtomicMediaJob deleted, and Task 8's materialisation wired so generated files reach the screen. Fixes C3 (image_to_image unreachable), C5 (adding a parameter meant editing a frozen file), C10 (job died with the component) and C11 (cancel was a no-op). TWO REAL DEFECTS CAUGHT BY TESTS, NOT REVIEW: the refit initially dropped the device default, which would have silently changed every submitted body - found by the rewritten parity test; and the test-quality guard caught two of this task's own tests asserting nothing but mock invocation, which were strengthened rather than allowlisted. Payload parity is PROVEN end to end: parity.test.tsx drives the real refitted form through the real downcaster and asserts a byte-identical v1 body. Visual parity was redefined once, deliberately, under D10. Gate: make verify-fast EXITCODE=0, make test-selective-v2032 EXITCODE=0, media suite 832, full web suite 2442 (baseline 2416, so +26). FULL make verify NOT run in this session - it needs MSVC for the Rust side and the shell had Git's link.exe shadowing it; this task touches no Rust.</t>
         </is>
       </c>
     </row>
@@ -5699,7 +5704,7 @@
       </c>
       <c r="I84" s="15" t="inlineStr">
         <is>
-          <t>2026-09-10 Guard confirmed RED first, exit code 1 read from the script itself rather than a wrapper: 5 protected files changed, 2 missing (deleted). Re-baselined in its own isolated single-purpose commit, per Q1's rule.</t>
+          <t>2026-09-10 Guard confirmed RED first, exit code 1 read from the script itself rather than a wrapper: 5 protected files changed, 2 missing (deleted). Re-baselined in its own isolated single-purpose commit, per Q1's rule. BLOCKED BRIEFLY BY A TOOL GAP, recorded as D11: the re-baseline script throws 'Protected file missing' and writes nothing when a protected file has been DELETED, so the two useAtomicMediaJob entries had to be removed from the manifest by hand before it would run.</t>
         </is>
       </c>
     </row>
@@ -5724,7 +5729,7 @@
       </c>
       <c r="E85" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F85" s="13" t="n"/>
@@ -5738,7 +5743,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I85" s="15" t="n"/>
+      <c r="I85" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-10 Done, two commits as required. (1) feat(media): drive the Media Studio from the provider platform. (2) chore(guard): re-baseline the selective v2.0.32 protected surface - isolated and single-purpose per Q1, naming the five files re-hashed and the two removed. After the re-baseline: make verify-fast EXITCODE=0 and make test-selective-v2032 EXITCODE=0.</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="26.4" customHeight="1">
       <c r="A86" s="6" t="inlineStr">
@@ -7369,7 +7378,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7989,6 +7998,43 @@
         </is>
       </c>
       <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>D11</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>TOOL GAP, found while re-baselining for Task 11. scripts/rebaseline-selective-v2032.mjs cannot express the DELETION of a protected file: it iterates the manifest, throws 'Protected file missing' on the first entry whose file is absent, and writes nothing at all. A task that legitimately removes a protected file therefore cannot use the tool the plan tells it to use.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Nothing now - worked around. It will block the next task that deletes a protected file, in exactly the same way.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Task 0 wrote the script for files that CHANGE, which was the only case that had arisen; Task 11 is the first task to delete one. Worked around by removing the two useAtomicMediaJob entries from scripts/selective-v2032-protected.json by hand, then running the script to re-hash the remaining nine. Left as-is rather than fixed in passing: Q1 requires the re-baseline commit to be isolated and single-purpose, so changing the script in it would have broken that rule. The fix, if wanted, is a --drop &lt;path&gt; flag so a deletion is expressed in the tool and shows up in the diff rather than being hand-edited.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Agent judgement, 2026-09-10. Recorded rather than hidden, and named in the re-baseline commit message so the next agent meets it before the script does.</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Noted</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>

--- a/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
+++ b/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
@@ -604,7 +604,7 @@
     <row r="1" ht="17.4" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Atomic Media — Model-Agnostic Platform Tracker</t>
+          <t>Radium Media — Model-Agnostic Platform Tracker</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
     <row r="1">
       <c r="A1" s="18" t="inlineStr">
         <is>
-          <t>Atomic Media handover</t>
+          <t>Radium Media handover</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="B7" s="22" t="inlineStr">
         <is>
-          <t>e5ee6f793 chore(guard): re-baseline the selective v2.0.32 protected surface - 2026-09-10.</t>
+          <t>feature/atomic-code-foundation: 3a536db56 (Task 11 complete). SEPARATE UNMERGED BRANCH chore/rename-radium-chat: 450100bda (product rename). Both pushed 2026-09-10.</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>Tasks 0-8, 10 and 11 Done. Task 11 is finished and the Media Studio now runs entirely on the platform - this is the first time any of Tasks 1-10 is visible on screen. Next is Task 12 (provider and model management UI, gated only on Task 4, which is Done) or Task 13 (media library route, gated on Task 8, Done). Task 9 is still gated on Q3, which is OPEN. Before Task 13, settle D8 - the unresolved-seed gap - because re-run depends on it.</t>
+          <t>Tasks 0-8, 10 and 11 Done. Task 11 finished 2026-09-10 and the Media Studio now runs entirely on the platform - the first time any of Tasks 1-10 is visible on screen. NEXT: Task 12 (provider and model management UI, gated only on Task 4 which is Done) or Task 13 (media library route, gated on Task 8 which is Done). Before Task 13, settle D8 - the unresolved-seed gap - because 're-run' depends on it. Task 9 is PARKED: Q3 is answered but it is now blocked by D12, and nothing depends on it. READ D13 FIRST: the product was renamed to Radium Chat on an unmerged branch, so you will see both names.</t>
         </is>
       </c>
     </row>
@@ -1189,11 +1189,10 @@
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>Run the full make verify in a VS x64 developer shell to close out Task 11 properly - it is the one gate this session could not run. Then ask the user which of Task 12 or Task 13 he wants next, and raise Q3 if Task 9 is being considered.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
+          <t>Two things are owed. (1) Run the full make verify in a VS x64 developer shell to close out Task 11 - it is the one gate the 2026-09-10 session could not run, because MSVC was not on that shell's PATH and Git's link.exe shadowed it. Task 11 touches no Rust. (2) Ask the user whether to merge chore/rename-radium-chat, and whether he wants the %APPDATA% folder migration that would let productName change too. Then ask which of Task 12 or Task 13 he wants.</t>
+        </is>
+      </c>
+    </row>
     <row r="18">
       <c r="A18" s="20" t="inlineStr">
         <is>
@@ -1553,7 +1552,7 @@
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>Extract the Atomic Media Worker adapter</t>
+          <t>Extract the Radium Media Worker adapter</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -1695,7 +1694,7 @@
       </c>
       <c r="K8" s="15" t="inlineStr">
         <is>
-          <t>2026-09-09: Task 5 complete, T05-S01..S06 all Done. Committed on feature/atomic-code-foundation; NOT pushed yet. The abstraction held: conformance.ts was imported UNMODIFIED and the contract did not have to change. Atomic Media Worker 30/30, ComfyUI 58/58 (30 conformance + 28 ComfyUI-specific). Version validated against: ComfyUI 0.35.0 (comfyui_version.py on master, read 2026-09-09). Divergences recorded as D4: fixtures transcribed from source rather than captured live (no ComfyUI on this laptop), and no separate RED observed - four mutations used as evidence instead, each killing exactly one test after a real gap in the node-class guard test was found and closed. Gate: make verify EXITCODE=0, protected-surface guard verified, no protected file touched.</t>
+          <t>2026-09-09: Task 5 complete, T05-S01..S06 all Done. Committed on feature/atomic-code-foundation; NOT pushed yet. The abstraction held: conformance.ts was imported UNMODIFIED and the contract did not have to change. Radium Media Worker 30/30, ComfyUI 58/58 (30 conformance + 28 ComfyUI-specific). Version validated against: ComfyUI 0.35.0 (comfyui_version.py on master, read 2026-09-09). Divergences recorded as D4: fixtures transcribed from source rather than captured live (no ComfyUI on this laptop), and no separate RED observed - four mutations used as evidence instead, each killing exactly one test after a real gap in the node-class guard test was found and closed. Gate: make verify EXITCODE=0, protected-surface guard verified, no protected file touched.</t>
         </is>
       </c>
     </row>
@@ -1887,7 +1886,7 @@
       <c r="F12" s="13" t="n"/>
       <c r="G12" s="14" t="inlineStr">
         <is>
-          <t>Q3, Q5</t>
+          <t>Q3 ANSWERED - now blocked by D12</t>
         </is>
       </c>
       <c r="H12" s="14" t="inlineStr">
@@ -1903,7 +1902,7 @@
       </c>
       <c r="K12" s="15" t="inlineStr">
         <is>
-          <t>2026-09-09: still gated on Q3 (unanswered). Q5 was answered on 2026-09-09 but SCOPED to four credential-storage crates only - it is NOT approval for any dependency this task might want. Ask again, naming the crate and reason.</t>
+          <t>2026-09-10: Q3 ANSWERED - build it, default off, but NARROWED: adopt-or-start, graceful stop, status; NO auto-restart. Windows orphans to be fixed with a Job Object. THREE FINDINGS before any code: (1) REUSE, do not reinvent - src-tauri/src/core/mcp/helpers.rs already spawns and supervises child servers with CREATE_NO_WINDOW, Unix process groups, SIGTERM-&gt;wait-&gt;SIGKILL escalation and 'already gone' treated as success; the plan reads as greenfield Rust and it is not. (2) The plan's 'no orphan on app exit' test is only true for a GRACEFUL exit - cleanup runs from a destructor, which does not run when the app is force-killed or crashes, and on Windows nothing else covers it. For a GPU worker that means gigabytes of VRAM still held and port 13420 occupied by a zombie the app will not recognise next launch. A Job Object with kill-on-close is the only OS-level guarantee. It needs one extra FEATURE FLAG on windows-sys 0.60.2, which is ALREADY a dependency, so AGENTS.md rule 6 is not tripped - rule 6 covers new runtime dependencies, and this adds none. (3) BLOCKER D12: nothing in the repo knows how to start the worker.</t>
         </is>
       </c>
     </row>
@@ -2614,7 +2613,7 @@
       <c r="F8" s="13" t="n"/>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>chore(guard): re-baseline Atomic Media protected hashes</t>
+          <t>chore(guard): re-baseline Radium Media protected hashes</t>
         </is>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -3430,7 +3429,7 @@
       <c r="F28" s="13" t="n"/>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>feat(media): add Atomic Media Worker provider adapter</t>
+          <t>feat(media): add Radium Media Worker provider adapter</t>
         </is>
       </c>
       <c r="H28" s="6" t="inlineStr">
@@ -3932,7 +3931,7 @@
       </c>
       <c r="I40" s="15" t="inlineStr">
         <is>
-          <t>2026-09-09 Done. Both adapters pass conformance.ts UNMODIFIED - Atomic Media Worker 30/30, ComfyUI 58/58 (30 conformance + 28 ComfyUI-specific). No adapter-specific branch was needed and the contract did not have to change: the abstraction held. Mutation tested in place of a separate RED - four mutations (interrupt read as a failure; seed ceiling unclamped; node-class guard disabled; socket opened with a fresh client id) each killed exactly one test after a gap was found and closed. The node-class guard mutation initially killed NOTHING: the test was deleting LatentUpscale, which the exposed-input check already catches, so a SaveImage case was added - the guard only matters for classes a graph uses but never exposes.</t>
+          <t>2026-09-09 Done. Both adapters pass conformance.ts UNMODIFIED - Radium Media Worker 30/30, ComfyUI 58/58 (30 conformance + 28 ComfyUI-specific). No adapter-specific branch was needed and the contract did not have to change: the abstraction held. Mutation tested in place of a separate RED - four mutations (interrupt read as a failure; seed ceiling unclamped; node-class guard disabled; socket opened with a fresh client id) each killed exactly one test after a gap was found and closed. The node-class guard mutation initially killed NOTHING: the test was deleting LatentUpscale, which the exposed-input check already catches, so a SaveImage case was added - the guard only matters for classes a graph uses but never exposes.</t>
         </is>
       </c>
     </row>
@@ -7378,7 +7377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7509,7 +7508,7 @@
       </c>
       <c r="B4" s="14" t="inlineStr">
         <is>
-          <t>Should Atomic Chat supervise the worker process?</t>
+          <t>Should Radium Chat supervise the worker process?</t>
         </is>
       </c>
       <c r="C4" s="14" t="inlineStr">
@@ -7522,13 +7521,21 @@
           <t>Default-off behind a setting is the middle path. Today the user starts it by hand.</t>
         </is>
       </c>
-      <c r="E4" s="15" t="n"/>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>ANSWERED BY THE USER 2026-09-10: BUILD IT, DEFAULT OFF - but NARROWER than the plan's Task 9. Scope agreed: adopt-or-start, graceful stop, status. NO auto-restart-on-crash. Rationale he accepted: restart-on-crash holds most of the complexity and can actively hurt - a worker that dies from running the GPU out of memory just crashes again on restart, and he would rather be told than have it loop silently. He also chose to fix the Windows orphan hole properly with a Job Object rather than accept it. The default-off rationale is stronger than the plan's 'middle path': he starts the worker by hand today, so an app that also starts one would collide on port 13420 - default-off means nothing can break until he opts in.</t>
+        </is>
+      </c>
       <c r="F4" s="13" t="inlineStr">
         <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="G4" s="13" t="n"/>
+          <t>Answered</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="26.4" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
@@ -7878,7 +7885,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ANSWERED BY THE USER 2026-09-09, having been shown the alternatives (ship with three known failures; drop synchronous providers entirely; pause for review). Raised rather than decided alone because it changes the contract and touches Tasks 1, 3 and 5. No existing adapter's behaviour changed - the Atomic Media Worker and ComfyUI simply declare synchronous() false.</t>
+          <t>ANSWERED BY THE USER 2026-09-09, having been shown the alternatives (ship with three known failures; drop synchronous providers entirely; pause for review). Raised rather than decided alone because it changes the contract and touches Tasks 1, 3 and 5. No existing adapter's behaviour changed - the Radium Media Worker and ComfyUI simply declare synchronous() false.</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -8035,6 +8042,80 @@
         </is>
       </c>
       <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>D12</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BLOCKER FOUND IN TASK 9's PREMISE, before any code was written: nothing in the repository knows HOW to start the Radium Media Worker. The plan says so itself at section 0.1 - 'no sidecar entry, and no bundle rule - the worker is an external localhost process the user starts by hand' - but Task 9 Step 2 then requires a spawn test, and Step 3 a supervisor that spawns. There is no binary path, no command, no arguments, no working directory and no setting for any of them anywhere in src-tauri, tauri.conf.json or the web app. Verified by search, not assumed.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>The SPAWN half of Task 9. The adopt/status half is unaffected and needs no launch command at all.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Three ways to close it. (a) A setting where the user records the worker's executable and arguments once; honest and small, but he has to know the path and it makes 'start it for me' contingent on configuration. (b) Bundle the worker as a Tauri sidecar; solves it properly but is a large change the plan explicitly rules out - there is no bundle rule today. (c) Auto-detect common install locations; fragile guessing that fails silently on any non-standard install. RAISED WITH THE USER rather than picked, because it changes what the feature is worth to him: the ADOPT half - detect a running worker, report honest status, never spawn a second, never stop one he started himself - needs no path and is pure gain; the SPAWN half is only worth building if there is a sane way to learn the command.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Agent judgement to raise it, 2026-09-10. AWAITING the user, who was asked how he starts the worker today, since that determines which option is even feasible.</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>D13</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>PRODUCT RENAMED, on a SEPARATE BRANCH that is not merged. The app is now Radium Chat (formerly Atomic Chat) and the media feature is Radium Media. Done on 2026-09-10 at the user's instruction, on branch chore/rename-radium-chat, three commits: 502bbc5e1 the rename, 213964f52 an isolated guard re-baseline, 450100bda an assistant-instruction migration. NOT merged into feature/atomic-code-foundation.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Nothing in this plan. Recorded because the next agent will see two names in the wild and needs to know which is deliberate.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>WHAT WAS DELIBERATELY NOT RENAMED, and must stay that way: productName is still 'Atomic Chat' because on Windows the app data directory derives from it - %APPDATA%\Atomic Chat\data\ holds threads, models, extensions and settings - so renaming it points a new build at an empty folder and looks exactly like data loss. DEVELOP.md already warned that renaming productName, the Cargo package name or the identifier 'would break user-data migrations'. Consequence: the installer, the Start Menu shortcut and Add/Remove Programs still read Atomic Chat until a folder migration is written. Also untouched and verified at their exact original counts: identifier chat.atomic.app, provider id atomic-media-worker, AtomicMedia* types, the atomicMedia module, the Atomic-Chat repo and folder names, 259 AtomicBot-ai upstream references, and the atomic.chat domain. THE RENAME WAS NOT A FIND-AND-REPLACE: a first pass renamed strings that denote real PATHS, and 25 files had to be reverted - including the NSIS uninstaller's data-folder delete, make clean-windows-all which wipes app data, and live path construction in path.rs, process_reaper.rs, utils.ts and services/threads/default.ts. Four occurrences were split across a line break by the formatter, which a literal replace silently misses.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Done and pushed, 2026-09-10. Verification: full web suite 2442 passed / 214 files, make test-extensions EXITCODE=0, make verify-fast EXITCODE=0, protected-surface guard EXITCODE=0. Migration v3 in assistant-extension rewrites only the product name inside saved assistant instructions, never the whole field, so a user's own edits survive; 7 tests, mutation-checked, and the workspace gained vitest 3.2.4 plus a Makefile include with the user's explicit ok per AGENTS.md rule 6.</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Noted</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
@@ -8236,7 +8317,7 @@
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>2026-09-09: both adapters that exist pass conformance.ts unmodified - Atomic Media Worker 30/30, ComfyUI 58/58 (30 conformance + 28 ComfyUI-specific). Still Partial only because Task 6's remote adapter does not exist yet.</t>
+          <t>2026-09-09: both adapters that exist pass conformance.ts unmodified - Radium Media Worker 30/30, ComfyUI 58/58 (30 conformance + 28 ComfyUI-specific). Still Partial only because Task 6's remote adapter does not exist yet.</t>
         </is>
       </c>
     </row>

--- a/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
+++ b/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
@@ -731,7 +731,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Never commit the pre-existing dirty paths. As of 2026-09-09 there are eleven: downloads/index.html, extensions/yarn.lock, src-tauri/Cargo.lock, src-tauri/icons/icon.png, web-app/src/hooks/useModelSources.ts, web-app/src/lib/models.ts, web-app/src/lib/__tests__/models.test.ts, web-app/src/routes/hub/__tests__/huggingface-conversion.test.ts, web-app/src/services/models/default.ts, web-app/src/utils/__tests__/formatDate.test.ts, web-app/src/utils/getModelToStart.test.ts.</t>
+          <t>Superseded 2026-09-10. This item used to forbid committing eleven pre-existing dirty paths. The working tree is now CLEAN and all eleven are committed, so there is nothing to avoid staging. Check git status rather than trusting any list here; see the Handover sheet's Do-not-commit row.</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="B7" s="22" t="inlineStr">
         <is>
-          <t>feature/atomic-code-foundation: 3a536db56 (Task 11 complete). SEPARATE UNMERGED BRANCH chore/rename-radium-chat: 450100bda (product rename). Both pushed 2026-09-10.</t>
+          <t>feature/atomic-code-foundation: 31a4c52a4 - the merge that brings chore/rename-radium-chat into this branch, authorised by the user 2026-09-10. NOT PUSHED: HEAD is 4 commits ahead of origin/feature/atomic-code-foundation (the merge plus 502bbc5e1, 213964f52 and 450100bda arriving with it). The rename is now fully contained in this branch, so chore/rename-radium-chat can be deleted once this is pushed, and D13 is no longer a live warning about two names in the wild.</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>Tasks 0-8, 10 and 11 Done. Task 11 finished 2026-09-10 and the Media Studio now runs entirely on the platform - the first time any of Tasks 1-10 is visible on screen. NEXT: Task 12 (provider and model management UI, gated only on Task 4 which is Done) or Task 13 (media library route, gated on Task 8 which is Done). Before Task 13, settle D8 - the unresolved-seed gap - because 're-run' depends on it. Task 9 is PARKED: Q3 is answered but it is now blocked by D12, and nothing depends on it. READ D13 FIRST: the product was renamed to Radium Chat on an unmerged branch, so you will see both names.</t>
+          <t>Tasks 0-8, 10 and 11 Done. Task 11's outstanding gate is now CLOSED: full make verify EXITCODE=0 on 2026-09-10, run on the merged tree - the one thing the previous session could not do. NEXT: Task 12 (provider and model management UI), gated only on Task 4 which is Done - start at T12-S01. Task 13 after it, but settle D8 first because re-run-with-a-new-seed depends on it. Task 9 stays PARKED: Q3 is answered but D12's answer removes the task's premise rather than unblocking it - read D12. READ D14 BEFORE ESTIMATING ANYTHING: Task 6's cloud adapter is built but unusable, and no step in this plan covers what would fix it.</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="B9" s="22" t="inlineStr">
         <is>
-          <t>Q1, Q2, D3, D5, Q5 all Answered. Tasks 0-5 and 7 Done and pushed. D1/D2/D4/D6 Noted. Q3, Q4, Q6 still Open. Task 6 is now FULLY UNBLOCKED (cloud in scope; OS credential store; four keyring crates approved for credential storage only). Task 8 and Task 10 are also unblocked. Nothing is waiting on the user.</t>
+          <t>Q1-Q5 Answered; Q6 still OPEN. D3, D5, D7, D10 Answered. D1, D2, D4, D6, D8, D9, D11, D13 Noted. D12 answered by the user 2026-09-10, but the answer dissolves Task 9's premise instead of unblocking it. NEW 2026-09-10: D14 (hidden scope - credential storage) and D15 (tool gap - printf DLLs). Waiting on the user: authorisation to push; Q6; D8 before Task 13; and the D14 scope call.</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t>downloads/index.html; extensions/yarn.lock; src-tauri/icons/icon.png; web-app/src/lib/models.ts; web-app/src/hooks/useModelSources.ts; web-app/src/lib/__tests__/models.test.ts</t>
+          <t>NOTHING. This row is deliberately empty - a correction, not an omission. As of 2026-09-10 the working tree is CLEAN and all eleven formerly-dirty paths are committed; verified with git status on the real filesystem, not inferred. The standing instruction never to stage those eleven paths is OBSOLETE and has been removed from README item 6 and from the Never-stage-these-paths row below. Consequence for Task 17: T17-S08 (confirm the four pre-existing dirty paths are still dirty and uncommitted) can no longer pass as written and should be marked N/A with this row as the reason.</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="B11" s="22" t="inlineStr">
         <is>
-          <t>2026-09-10 for Task 11: make verify-fast EXITCODE=0 and make test-selective-v2032 EXITCODE=0, both read from the command's own exit code. Full web suite 2442 passed / 214 files from the REPO ROOT. WARNING: run vitest from the repo root, not from web-app - src/services/__tests__/external-contracts.test.ts computes its repo root with endsWith('/web-app'), which is false on Windows backslash paths, so 9 tests fail with ENOENT for no real reason. FULL make verify was NOT run on 2026-09-10: MSVC was not on the shell's PATH and Git's link.exe shadowed it. Task 11 touches no Rust, but the full gate is still owed.</t>
+          <t>2026-09-10, on the MERGED tree (31a4c52a4): full make verify EXITCODE=0, read from the command's own exit code. Legs: verify-fast; test-rust 903 passed / 0 failed (487+12+167+205+28+4); test-selective-v2032 printing 'Selective v2.0.32 boundaries verified'. Web suite 2600 passed / 16 skipped across 247 files from the REPO ROOT; extensions 250 and 276. That guard line is the load-bearing one: BOTH branches had re-baselined scripts/selective-v2032-protected.json, so the auto-merge could have been clean and still wrong - it was verified, not trusted. WARNING unchanged: run vitest from the repo root, not from web-app - src/services/__tests__/external-contracts.test.ts computes its repo root with endsWith of /web-app, false on Windows backslash paths, so 9 tests fail with ENOENT for no real reason.</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t>None. The two historic blockers are both fixed: the uncommitted model-catalog/GGUF test fixes are committed, and the missing generated app icons are now produced by the make app-icons target.</t>
+          <t>None. Task 11's gate is closed and the merged tree verifies green from a VS x64 developer shell.</t>
         </is>
       </c>
     </row>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="B14" s="22" t="inlineStr">
         <is>
-          <t>In this Codex shell, prepend PATH with C:\Users\Warwick\AppData\Local\Programs\GnuWin32\bin before running make. New terminals should inherit the user PATH.</t>
+          <t>In this Codex shell, prepend PATH with C:\Users\Warwick\AppData\Local\Programs\GnuWin32\bin before running make. New terminals should inherit the user PATH. CORRECTION 2026-09-10: the printf.exe-only directory named in the row below is NOT printf.exe on its own. Git's printf.exe is an MSYS binary and will not start without msys-2.0.dll, msys-iconv-2.dll and msys-intl-8.dll copied beside it - four files, not one. With only the .exe, Windows raises a msys-iconv-2.dll-was-not-found dialog and the Rust test shell_contract_covers_safe_execution_hard_block_denial_and_cancellation FAILS, because it runs printf SHELL_SENTINEL and asserts Ok. That failure looks exactly like a code regression and is not one. See D15.</t>
         </is>
       </c>
     </row>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="B15" s="22" t="inlineStr">
         <is>
-          <t>2026-09-09 make verify EXITCODE=0, re-run after the Task 1 contract landed in the working tree. Environment: VS x64 developer shell (vcvars64.bat) with a printf.exe-only directory appended to PATH (Git usr/bin as a whole must NOT be added, or make switches to sh and breaks the PowerShell stub-resources recipe, and Git link.exe shadows MSVC link.exe).</t>
+          <t>2026-09-10 make verify EXITCODE=0 on the merged tree 31a4c52a4. Environment: VS x64 developer shell (vcvars64.bat), GnuWin32\bin PREPENDED to PATH, and a directory containing printf.exe PLUS its three msys DLLs APPENDED (see D15 and the Command note row). Git usr/bin as a whole must NOT be added, or make switches to sh and breaks the PowerShell stub-resources recipe, and Git's link.exe shadows MSVC link.exe.</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>Two things are owed. (1) Run the full make verify in a VS x64 developer shell to close out Task 11 - it is the one gate the 2026-09-10 session could not run, because MSVC was not on that shell's PATH and Git's link.exe shadowed it. Task 11 touches no Rust. (2) Ask the user whether to merge chore/rename-radium-chat, and whether he wants the %APPDATA% folder migration that would let productName change too. Then ask which of Task 12 or Task 13 he wants.</t>
+          <t>ONE THING IS OWED RIGHT NOW: ask the user to authorise PUSHING. HEAD (31a4c52a4) is 4 commits ahead of origin, and the merge he authorised is sitting locally, fully verified and unpushed. Then start Task 12 at T12-S01. Also outstanding, none of it blocking Task 12: (1) the APPDATA folder migration that would let productName change too - raised, deliberately deferred, never answered; (2) Q6 sequencing; (3) D8, needed before Task 13; (4) D14 - whether to schedule the credential-store work Task 6 needs, or accept that cloud media providers remain unusable despite Q2 putting them in scope.</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="B25" s="22" t="inlineStr">
         <is>
-          <t>These are pre-existing dirty files that belong to other in-flight work (Decision Q6). Leave them dirty and unstaged unless the user specifically authorises otherwise: downloads/index.html; extensions/yarn.lock; src-tauri/Cargo.lock; src-tauri/icons/icon.png; web-app/src/hooks/useModelSources.ts; web-app/src/lib/models.ts; web-app/src/lib/__tests__/models.test.ts; web-app/src/routes/hub/__tests__/huggingface-conversion.test.ts; web-app/src/services/models/default.ts; web-app/src/utils/__tests__/formatDate.test.ts; web-app/src/utils/getModelToStart.test.ts</t>
+          <t>OBSOLETE as of 2026-09-10 - kept only so the next agent understands why the instruction disappeared. The eleven paths this row used to list are all committed and the working tree is clean. There are currently NO paths that must be left unstaged. Do not reinstate this list without checking git status first.</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="K14" s="15" t="inlineStr">
         <is>
-          <t>2026-09-10: Task 11 COMPLETE, S01-S11 all Done. This is the task that made Tasks 1-10 visible: MODES and all eight bespoke control blocks deleted (489 lines -&gt; 293), tabs and controls now come from what providers declare, useAtomicMediaJob deleted, and Task 8's materialisation wired so generated files reach the screen. Fixes C3 (image_to_image unreachable), C5 (adding a parameter meant editing a frozen file), C10 (job died with the component) and C11 (cancel was a no-op). TWO REAL DEFECTS CAUGHT BY TESTS, NOT REVIEW: the refit initially dropped the device default, which would have silently changed every submitted body - found by the rewritten parity test; and the test-quality guard caught two of this task's own tests asserting nothing but mock invocation, which were strengthened rather than allowlisted. Payload parity is PROVEN end to end: parity.test.tsx drives the real refitted form through the real downcaster and asserts a byte-identical v1 body. Visual parity was redefined once, deliberately, under D10. Gate: make verify-fast EXITCODE=0, make test-selective-v2032 EXITCODE=0, media suite 832, full web suite 2442 (baseline 2416, so +26). FULL make verify NOT run in this session - it needs MSVC for the Rust side and the shell had Git's link.exe shadowing it; this task touches no Rust.</t>
+          <t>2026-09-10: Task 11 COMPLETE, S01-S11 all Done. This is the task that made Tasks 1-10 visible: MODES and all eight bespoke control blocks deleted (489 lines -&gt; 293), tabs and controls now come from what providers declare, useAtomicMediaJob deleted, and Task 8's materialisation wired so generated files reach the screen. Fixes C3 (image_to_image unreachable), C5 (adding a parameter meant editing a frozen file), C10 (job died with the component) and C11 (cancel was a no-op). TWO REAL DEFECTS CAUGHT BY TESTS, NOT REVIEW: the refit initially dropped the device default, which would have silently changed every submitted body - found by the rewritten parity test; and the test-quality guard caught two of this task's own tests asserting nothing but mock invocation, which were strengthened rather than allowlisted. Payload parity is PROVEN end to end: parity.test.tsx drives the real refitted form through the real downcaster and asserts a byte-identical v1 body. Visual parity was redefined once, deliberately, under D10. Gate: make verify-fast EXITCODE=0, make test-selective-v2032 EXITCODE=0, media suite 832, full web suite 2442 (baseline 2416, so +26). FULL make verify NOT run in this session - it needs MSVC for the Rust side and the shell had Git's link.exe shadowing it; this task touches no Rust. | 2026-09-10 GATE CLOSED: the full make verify this task still owed has now been run and passed - EXITCODE=0, read from the command's own exit code, on the merged tree 31a4c52a4. Rust 903 passed / 0 failed, web 2600 passed / 16 skipped, extensions 250 and 276, protected-surface guard verified. The earlier session could not run it because MSVC was absent from that shell's PATH; the actual obstacle this time was a broken printf on PATH, not the Rust toolchain - see D15.</t>
         </is>
       </c>
     </row>
@@ -7377,7 +7377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8070,12 +8070,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Agent judgement to raise it, 2026-09-10. AWAITING the user, who was asked how he starts the worker today, since that determines which option is even feasible.</t>
+          <t>ANSWERED BY THE USER 2026-09-10: install the app and create a shortcut. Read carefully, this does not unblock Task 9 - it DISSOLVES ITS PREMISE. He does not start the media worker by hand at all, so there is no existing launch command to record, and option (a), a setting where the user names the command, has nothing to be seeded from. Only two honest paths remain, and both are the user's call rather than the agent's: (i) narrow Task 9 to adopt-or-status only - the app detects a worker already listening on 13420 and reports it, never launching one, which needs no launch command and is a genuinely small task; or (ii) bundle the worker with the app as a Tauri sidecar so that installing the app IS installing the worker, which matches what he described but is substantially more work than Task 9 as written and needs its own plan. NOT GUESSED - put back to the user.</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Answered</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8116,6 +8116,76 @@
         </is>
       </c>
       <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>D14</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>HIDDEN SCOPE, found 2026-09-10 by searching all 128 steps rather than by reading the plan's prose. Task 6 built the cloud/remote adapter and its own notes say it is NOT YET USABLE BY THE USER because no secret resolver is wired. The fix is the OS credential store the user chose in D3 and approved four crates for in Q5 (keyring 4.2 plus three platform backends). NO STEP ANYWHERE IN THIS PLAN COVERS THAT WORK. It is not in Task 6's six steps, not in Task 9's, and not in Tasks 12-17.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Makes Q2's answer undeliverable. The user said cloud media providers ARE in scope; finishing every remaining step of this plan still leaves them unusable, because a cloud provider reports unauthorised rather than sending a blank Authorization header. Also distorts any completion estimate drawn from the step counts.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Add it as an explicit task rather than letting it hide. Roughly a task's worth of Rust: keyring-core plus the Windows, macOS and Linux backends, a resolver wired into providerFactory, and tests. Alternative, if the user would rather have the visible product sooner: accept in writing that cloud providers stay unusable for now, finish Tasks 12/13/16/17, and schedule this afterwards. Either is defensible; leaving it undiscovered was not.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>D15</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>TOOL GAP, not a plan contradiction. The Handover sheet told the next agent to append a printf.exe-only directory to PATH. Taken literally that produces a printf that cannot start: Git's printf.exe is an MSYS binary needing msys-2.0.dll, msys-iconv-2.dll and msys-intl-8.dll beside it.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Nothing now - corrected in place on the Command note and Last-make-verify-output rows. It cost one wasted full verify on 2026-09-10 and produced a Windows error dialog the user saw and reported.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>The symptom is worth memorising because it MIMICS A CODE REGRESSION: make verify stops at test-rust with exactly one failure, core::agent::tools::contract_tests::shell_contract_covers_safe_execution_hard_block_denial_and_cancellation, asserting left: Error right: Ok. That test shells out to printf SHELL_SENTINEL. 486 other Rust tests pass. If that single test ever fails again, check printf on PATH before touching Rust code.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Agent judgement, 2026-09-10. Recorded rather than silently fixed, in the same spirit as D11, because the next agent on a fresh Windows shell will hit it identically.</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Noted</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>

--- a/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
+++ b/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
@@ -1081,7 +1081,7 @@
       </c>
       <c r="B7" s="22" t="inlineStr">
         <is>
-          <t>feature/atomic-code-foundation: 31a4c52a4 - the merge that brings chore/rename-radium-chat into this branch, authorised by the user 2026-09-10. NOT PUSHED: HEAD is 4 commits ahead of origin/feature/atomic-code-foundation (the merge plus 502bbc5e1, 213964f52 and 450100bda arriving with it). The rename is now fully contained in this branch, so chore/rename-radium-chat can be deleted once this is pushed, and D13 is no longer a live warning about two names in the wild.</t>
+          <t>feature/atomic-code-foundation: Task 12 commit (see the Tasks sheet). The rename merge 31a4c52a4 and the tracker commit f357805f6 were pushed earlier on 2026-09-10, so chore/rename-radium-chat is fully contained in this branch and can be deleted.</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>Tasks 0-8, 10 and 11 Done. Task 11's outstanding gate is now CLOSED: full make verify EXITCODE=0 on 2026-09-10, run on the merged tree - the one thing the previous session could not do. NEXT: Task 12 (provider and model management UI), gated only on Task 4 which is Done - start at T12-S01. Task 13 after it, but settle D8 first because re-run-with-a-new-seed depends on it. Task 9 stays PARKED: Q3 is answered but D12's answer removes the task's premise rather than unblocking it - read D12. READ D14 BEFORE ESTIMATING ANYTHING: Task 6's cloud adapter is built but unusable, and no step in this plan covers what would fix it.</t>
+          <t>Tasks 0-8, 10, 11 and 12 Done. NEXT: Task 13 (media library route), gated on Task 8 which is Done - but SETTLE D8 FIRST, because 're-run with a new seed' depends on a resolved seed the contract cannot currently carry. Task 9 stays PARKED (see D12). Tasks 14, 15, 16, 17 unstarted. READ D14 (cloud providers are built but unusable) and D16 (shared Progress primitive is inaccessible).</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="B11" s="22" t="inlineStr">
         <is>
-          <t>2026-09-10, on the MERGED tree (31a4c52a4): full make verify EXITCODE=0, read from the command's own exit code. Legs: verify-fast; test-rust 903 passed / 0 failed (487+12+167+205+28+4); test-selective-v2032 printing 'Selective v2.0.32 boundaries verified'. Web suite 2600 passed / 16 skipped across 247 files from the REPO ROOT; extensions 250 and 276. That guard line is the load-bearing one: BOTH branches had re-baselined scripts/selective-v2032-protected.json, so the auto-merge could have been clean and still wrong - it was verified, not trusted. WARNING unchanged: run vitest from the repo root, not from web-app - src/services/__tests__/external-contracts.test.ts computes its repo root with endsWith of /web-app, false on Windows backslash paths, so 9 tests fail with ENOENT for no real reason.</t>
+          <t>2026-09-10 for Task 12: full make verify EXITCODE=0, read from the command's own exit code. Web 2606 passed / 16 skipped (baseline 2600, so +6), extensions 250 and 276, Rust 903 passed / 0 failed, 'Selective v2.0.32 boundaries verified'. Run from a VS x64 developer shell with printf plus its three msys DLLs on PATH - see D15.</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>ONE THING IS OWED RIGHT NOW: ask the user to authorise PUSHING. HEAD (31a4c52a4) is 4 commits ahead of origin, and the merge he authorised is sitting locally, fully verified and unpushed. Then start Task 12 at T12-S01. Also outstanding, none of it blocking Task 12: (1) the APPDATA folder migration that would let productName change too - raised, deliberately deferred, never answered; (2) Q6 sequencing; (3) D8, needed before Task 13; (4) D14 - whether to schedule the credential-store work Task 6 needs, or accept that cloud media providers remain unusable despite Q2 putting them in scope.</t>
+          <t>Ask the user for a decision on D8 before starting Task 13, and on D14 before Task 17. Then Task 13. Still unanswered and not blocking: Q6 sequencing; the %APPDATA% folder migration; D16.</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F15" s="13" t="n"/>
@@ -2055,7 +2055,11 @@
           <t>Settings to Media. Follows the existing Settings to Providers layout.</t>
         </is>
       </c>
-      <c r="K15" s="15" t="n"/>
+      <c r="K15" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-10: Task 12 COMPLETE, T12-S01..S07 Done. New: containers/media/ProviderList.tsx, containers/media/ModelCatalog.tsx, services/media/secrets.ts, routes/settings/media/index.tsx, and one test file (6 tests). Settings &gt; Media is registered in the menu and the generated route tree. No protected file touched, no guard re-baseline needed. Gate: full make verify EXITCODE=0; web suite 2606 passed / 16 skipped, up exactly 6 from the 2600 baseline; Rust 903 unchanged; guard verified. MUTATION-TESTED, AND IT MATTERED: the first version of the API-key test left the adapter on the local worker, which needs no credential, so the entire secret path never executed and every security assertion passed vacuously. A mutation that leaked the key into the stored descriptor survived. The test now selects an authenticating adapter and asserts the pointer as well as the absence of the secret; four mutations each kill exactly one test. SECRETS ARE SESSION-ONLY - see D14. services/media/secrets.ts is a SEAM, not a store: the key is held in memory for the session and the UI says so. Persisting it would have meant contradicting D3 or inventing a security design nobody approved. NEW FINDING D16: the shared Progress primitive is inaccessible.</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="26.4" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
@@ -5769,10 +5773,14 @@
       </c>
       <c r="E86" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F86" s="13" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F86" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G86" s="14" t="inlineStr">
         <is>
           <t>Add a custom provider; bad URL isolates; enabling shows models; install progress; recoverable failure; masked API key</t>
@@ -5806,10 +5814,14 @@
       </c>
       <c r="E87" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F87" s="13" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F87" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G87" s="14" t="inlineStr">
         <is>
           <t>FAIL</t>
@@ -5843,10 +5855,14 @@
       </c>
       <c r="E88" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F88" s="13" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F88" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G88" s="14" t="inlineStr">
         <is>
           <t>Follow the existing Settings to Providers layout - do not invent a second visual language</t>
@@ -5880,10 +5896,14 @@
       </c>
       <c r="E89" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F89" s="13" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F89" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G89" s="14" t="inlineStr">
         <is>
           <t>Reuse existing download-progress primitives rather than adding new ones</t>
@@ -5917,10 +5937,14 @@
       </c>
       <c r="E90" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F90" s="13" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F90" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G90" s="14" t="n"/>
       <c r="H90" s="6" t="inlineStr">
         <is>
@@ -5950,10 +5974,14 @@
       </c>
       <c r="E91" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F91" s="13" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F91" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G91" s="14" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5987,10 +6015,14 @@
       </c>
       <c r="E92" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F92" s="13" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F92" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G92" s="14" t="inlineStr">
         <is>
           <t>feat(media): add media provider and model settings</t>
@@ -7377,7 +7409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8142,7 +8174,6 @@
           <t>Add it as an explicit task rather than letting it hide. Roughly a task's worth of Rust: keyring-core plus the Windows, macOS and Linux backends, a resolver wired into providerFactory, and tests. Alternative, if the user would rather have the visible product sooner: accept in writing that cloud providers stay unusable for now, finish Tasks 12/13/16/17, and schedule this afterwards. Either is defensible; leaving it undiscovered was not.</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>Open</t>
@@ -8186,6 +8217,43 @@
         </is>
       </c>
       <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>D16</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ACCESSIBILITY DEFECT in a SHARED primitive, found while building Task 12. web-app/src/components/ui/progress.tsx destructures `value` and uses it only to compute the indicator transform - it never forwards it to ProgressPrimitive.Root. Radix therefore renders every progress bar in the app with data-state=indeterminate and NO aria-valuenow, so the bar is decorative to a screen reader and announces no progress at all.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Not media-specific and not blocking. It affects every consumer of the primitive, which includes model downloads (DownloadButton, ModelDownloadAction, BackendUpdater) - i.e. the long operations where a progress announcement matters most.</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>One-line fix (pass `value` through to the Root), but it changes a primitive shared by several screens and has its own existing test, so it belongs in its own small change rather than being smuggled into Task 12. Deliberately NOT fixed here. Task 12's own UI spells the percentage out in text so the number is at least readable in the meantime.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Agent judgement, 2026-09-10. Recorded rather than silently fixed or silently ignored, per the same practice as D11 and D15.</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Noted</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>

--- a/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
+++ b/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
@@ -871,7 +871,7 @@
         </is>
       </c>
       <c r="B29" s="7">
-        <f>COUNTA(Tasks!A3:A20)</f>
+        <f>COUNTA(Tasks!A3:A40)</f>
         <v/>
       </c>
     </row>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="B30" s="7">
-        <f>COUNTIF(Tasks!E3:E20,"Done")</f>
+        <f>COUNTIF(Tasks!E3:E40,"Done")</f>
         <v/>
       </c>
     </row>
@@ -893,7 +893,7 @@
         </is>
       </c>
       <c r="B31" s="7">
-        <f>COUNTIF(Tasks!E3:E20,"Skipped")</f>
+        <f>COUNTIF(Tasks!E3:E40,"Skipped")</f>
         <v/>
       </c>
     </row>
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="B32" s="7">
-        <f>COUNTIF(Tasks!E3:E20,"Blocked")</f>
+        <f>COUNTIF(Tasks!E3:E40,"Blocked")</f>
         <v/>
       </c>
     </row>
@@ -926,7 +926,7 @@
         </is>
       </c>
       <c r="B34" s="7">
-        <f>COUNTA(Steps!A2:A129)</f>
+        <f>COUNTA(Steps!A2:A250)</f>
         <v/>
       </c>
     </row>
@@ -937,7 +937,7 @@
         </is>
       </c>
       <c r="B35" s="7">
-        <f>COUNTIF(Steps!E2:E129,"Done")</f>
+        <f>COUNTIF(Steps!E2:E250,"Done")</f>
         <v/>
       </c>
     </row>
@@ -948,7 +948,7 @@
         </is>
       </c>
       <c r="B36" s="7">
-        <f>COUNTIF(Steps!E2:E129,"Skipped")</f>
+        <f>COUNTIF(Steps!E2:E250,"Skipped")</f>
         <v/>
       </c>
     </row>
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="B38" s="7">
-        <f>COUNTIF(Decisions!F2:F50,"Open")</f>
+        <f>COUNTIF(Decisions!F2:F80,"Open")</f>
         <v/>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2286,6 +2286,55 @@
       </c>
       <c r="K20" s="15" t="n"/>
     </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Task 18</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>2 - Providers</t>
+        </is>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>Provider credential storage (OS keychain)</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="inlineStr"/>
+      <c r="G21" s="14" t="inlineStr">
+        <is>
+          <t>D3, Q5, D14 all answered - UNBLOCKED</t>
+        </is>
+      </c>
+      <c r="H21" s="14" t="inlineStr">
+        <is>
+          <t>Cloud provider authenticates against a real endpoint</t>
+        </is>
+      </c>
+      <c r="I21" s="13" t="inlineStr"/>
+      <c r="J21" s="14" t="inlineStr">
+        <is>
+          <t>ADDED 2026-09-10 from decision D14, which the user answered by scheduling it. NOT in the original plan - this is the gap that made Task 6 build a cloud adapter that could not hold a key.</t>
+        </is>
+      </c>
+      <c r="K21" s="15" t="inlineStr">
+        <is>
+          <t>Makes Q2 real. Task 6 shipped remoteHttp.ts but providerFactory builds it WITHOUT a secret resolver, so a cloud provider reports unauthorised rather than sending a blank Authorization header. Task 12 added services/media/secrets.ts as the single seam the UI hands a credential to, holding it in memory for the session only. This task replaces that backing store with the OS credential store chosen in D3 and the crates approved in Q5, then wires the resolver. Definition of done: a cloud provider configured with a key survives a relaunch and authenticates; the key is never in localStorage, never in the provider store, and never in the DOM.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A2:K20"/>
   <dataValidations count="1">
@@ -2303,7 +2352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I129"/>
+  <dimension ref="A1:I136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -7391,6 +7440,258 @@
         </is>
       </c>
       <c r="I129" s="15" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="6" t="inlineStr">
+        <is>
+          <t>T18-S01</t>
+        </is>
+      </c>
+      <c r="B130" s="6" t="inlineStr">
+        <is>
+          <t>Task 18</t>
+        </is>
+      </c>
+      <c r="C130" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D130" s="14" t="inlineStr">
+        <is>
+          <t>Write failing Rust tests for store/fetch/delete of a provider credential</t>
+        </is>
+      </c>
+      <c r="E130" s="13" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F130" s="13" t="inlineStr"/>
+      <c r="G130" s="14" t="inlineStr">
+        <is>
+          <t>Round-trip against the platform backend; a missing key is not an error</t>
+        </is>
+      </c>
+      <c r="H130" s="6" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="6" t="inlineStr">
+        <is>
+          <t>T18-S02</t>
+        </is>
+      </c>
+      <c r="B131" s="6" t="inlineStr">
+        <is>
+          <t>Task 18</t>
+        </is>
+      </c>
+      <c r="C131" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D131" s="14" t="inlineStr">
+        <is>
+          <t>Add the four approved keyring crates and the platform backends</t>
+        </is>
+      </c>
+      <c r="E131" s="13" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F131" s="13" t="inlineStr"/>
+      <c r="G131" s="14" t="inlineStr">
+        <is>
+          <t>Exactly the crates named in Q5 - no others without asking</t>
+        </is>
+      </c>
+      <c r="H131" s="6" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="6" t="inlineStr">
+        <is>
+          <t>T18-S03</t>
+        </is>
+      </c>
+      <c r="B132" s="6" t="inlineStr">
+        <is>
+          <t>Task 18</t>
+        </is>
+      </c>
+      <c r="C132" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D132" s="14" t="inlineStr">
+        <is>
+          <t>Expose Tauri commands, permitted explicitly in the capabilities file</t>
+        </is>
+      </c>
+      <c r="E132" s="13" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F132" s="13" t="inlineStr"/>
+      <c r="G132" s="14" t="inlineStr">
+        <is>
+          <t>media_secret_set / media_secret_get / media_secret_delete</t>
+        </is>
+      </c>
+      <c r="H132" s="6" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="6" t="inlineStr">
+        <is>
+          <t>T18-S04</t>
+        </is>
+      </c>
+      <c r="B133" s="6" t="inlineStr">
+        <is>
+          <t>Task 18</t>
+        </is>
+      </c>
+      <c r="C133" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D133" s="14" t="inlineStr">
+        <is>
+          <t>Replace the session-only backing store behind services/media/secrets.ts</t>
+        </is>
+      </c>
+      <c r="E133" s="13" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F133" s="13" t="inlineStr"/>
+      <c r="G133" s="14" t="inlineStr">
+        <is>
+          <t>Flip MEDIA_SECRET_PERSISTENCE to 'credential-store'; UI warning disappears</t>
+        </is>
+      </c>
+      <c r="H133" s="6" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="6" t="inlineStr">
+        <is>
+          <t>T18-S05</t>
+        </is>
+      </c>
+      <c r="B134" s="6" t="inlineStr">
+        <is>
+          <t>Task 18</t>
+        </is>
+      </c>
+      <c r="C134" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D134" s="14" t="inlineStr">
+        <is>
+          <t>Wire the resolver into providerFactory so remoteHttp can authenticate</t>
+        </is>
+      </c>
+      <c r="E134" s="13" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F134" s="13" t="inlineStr"/>
+      <c r="G134" s="14" t="inlineStr">
+        <is>
+          <t>Cloud provider stops reporting unauthorised</t>
+        </is>
+      </c>
+      <c r="H134" s="6" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="6" t="inlineStr">
+        <is>
+          <t>T18-S06</t>
+        </is>
+      </c>
+      <c r="B135" s="6" t="inlineStr">
+        <is>
+          <t>Task 18</t>
+        </is>
+      </c>
+      <c r="C135" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D135" s="14" t="inlineStr">
+        <is>
+          <t>Run cargo check, clippy, test, then full make verify</t>
+        </is>
+      </c>
+      <c r="E135" s="13" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F135" s="13" t="inlineStr"/>
+      <c r="G135" s="14" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H135" s="6" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="6" t="inlineStr">
+        <is>
+          <t>T18-S07</t>
+        </is>
+      </c>
+      <c r="B136" s="6" t="inlineStr">
+        <is>
+          <t>Task 18</t>
+        </is>
+      </c>
+      <c r="C136" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D136" s="14" t="inlineStr">
+        <is>
+          <t>Commit</t>
+        </is>
+      </c>
+      <c r="E136" s="13" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F136" s="13" t="inlineStr"/>
+      <c r="G136" s="14" t="inlineStr">
+        <is>
+          <t>feat(media): store provider credentials in the OS keychain</t>
+        </is>
+      </c>
+      <c r="H136" s="6" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I129"/>
@@ -7954,12 +8255,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Agent judgement, 2026-09-09. Flagged to the user rather than hidden, in the same spirit as D6 and D7. Covered by a test that asserts resolved_seed is undefined when the seed was left to the provider.</t>
+          <t>ANSWERED BY THE USER 2026-09-10: the CALLER resolves the seed, not the provider. Implemented the same day. resolveSeeds() in contract/params.ts fills any blank seed before submit; the job manager applies it and submits AND records the same resolved request, so provenance cannot drift from what was sent. The ComfyUI adapter no longer randomises - the behaviour change the user was told about and accepted - and an unresolved seed there now leaves the template's own value rather than inventing a number nobody records. No contract change was needed: a resolved seed is just a param with a value. 11 new tests (7 unit, 4 through the manager); four mutations each killed, including the one that matters most - recording the unresolved request while submitting the resolved one. REMAINING NARROW GAP, found while implementing and recorded rather than hidden: assets.ts resolvedSeed() reads params.seed by that literal key, while resolveSeeds() resolves whatever id the model's seed spec actually declares. For a model naming its seed something else (noise_seed, for instance), the app now KNOWS the number and sends it, but provenance.resolved_seed still records undefined. Not fixed here because MaterializeContext carries only the request and a model_label - threading the seed's param id through useMediaJobAsset would ripple past the scope of D8. Task 13 is the natural place to close it: the library detail view needs the model's specs for 're-run' anyway, so the id is in hand there. Every model in the fixtures and the curated catalog uses 'seed', so nothing is wrong today.</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Noted</t>
+          <t>Answered</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8174,9 +8475,14 @@
           <t>Add it as an explicit task rather than letting it hide. Roughly a task's worth of Rust: keyring-core plus the Windows, macOS and Linux backends, a resolver wired into providerFactory, and tests. Alternative, if the user would rather have the visible product sooner: accept in writing that cloud providers stay unusable for now, finish Tasks 12/13/16/17, and schedule this afterwards. Either is defensible; leaving it undiscovered was not.</t>
         </is>
       </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>ANSWERED BY THE USER 2026-09-10: SCHEDULE THE WORK. Cloud media providers are to be genuinely usable, consistent with Q2. Added to this tracker as TASK 18 rather than left as a decision note, because that is what hid it in the first place. Scope: the keyring crates approved in Q5 (keyring 4.2 plus the Windows, macOS and Linux backends), Tauri commands to store and fetch a provider credential, and a resolver wired into providerFactory so remoteHttp stops reporting unauthorised. web-app/src/services/media/secrets.ts is already the single seam the UI hands a key to, so this lands behind it: flip MEDIA_SECRET_PERSISTENCE to 'credential-store' and replace three functions.</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Answered</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">

--- a/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
+++ b/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
@@ -1093,7 +1093,7 @@
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>Tasks 0-8, 10, 11 and 12 Done. NEXT: Task 13 (media library route), gated on Task 8 which is Done - but SETTLE D8 FIRST, because 're-run with a new seed' depends on a resolved seed the contract cannot currently carry. Task 9 stays PARKED (see D12). Tasks 14, 15, 16, 17 unstarted. READ D14 (cloud providers are built but unusable) and D16 (shared Progress primitive is inaccessible).</t>
+          <t>Tasks 0-8 and 10-13 Done. NEXT: the user must answer D17 (authorise one protected-file change so the library's 're-run' actually reaches the studio) - it is the only thing standing between Task 13 being a viewer and being useful. After that: Task 18 (credential storage, scheduled by the user via D14), then Tasks 14, 15, 16 and finally 17. Task 9 stays PARKED (D12).</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="B11" s="22" t="inlineStr">
         <is>
-          <t>2026-09-10 for Task 12: full make verify EXITCODE=0, read from the command's own exit code. Web 2606 passed / 16 skipped (baseline 2600, so +6), extensions 250 and 276, Rust 903 passed / 0 failed, 'Selective v2.0.32 boundaries verified'. Run from a VS x64 developer shell with printf plus its three msys DLLs on PATH - see D15.</t>
+          <t>2026-09-10 for Task 13: full make verify EXITCODE=0. Web 2633 passed / 16 skipped, extensions 250 and 276, Rust 903 passed / 0 failed, guard verified. Run from a VS x64 developer shell with printf plus its three msys DLLs on PATH - see D15.</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>Ask the user for a decision on D8 before starting Task 13, and on D14 before Task 17. Then Task 13. Still unanswered and not blocking: Q6 sequencing; the %APPDATA% folder migration; D16.</t>
+          <t>Ask the user to answer D17 - it blocks nothing technically but leaves Task 13 half-useful. Then Task 18. Still open: Q6 sequencing; the APPDATA folder migration; D16 (shared Progress primitive is inaccessible).</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F16" s="13" t="n"/>
@@ -2104,7 +2104,11 @@
           <t>Seed the index with any existing image/video files to exercise the whole flow.</t>
         </is>
       </c>
-      <c r="K16" s="15" t="n"/>
+      <c r="K16" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-10: Task 13 COMPLETE, T13-S01..S06 Done. New: containers/media/MediaLibrary.tsx, containers/media/AssetDetail.tsx, services/media/rerun.ts, routes/media_.library.tsx, one test file (11 tests). Everything Task 8 recorded now has a screen. Gate: full make verify EXITCODE=0; web 2633 passed / 16 skipped (baseline 2618, so +15); Rust 903 unchanged; guard verified. Five mutations each kill a test. TWO THINGS CHANGED BEYOND THE PLAIN UI. (1) library.remove() was INDEX-ONLY - it forgot the generation and left the bytes on disk forever, unreachable from any UI. It now deletes the file and its thumbnail, tolerantly: a locked or already-missing file still removes the row, because an entry the user cannot delete is worse than a file that outlives its record. Note it deletes ADOPTED files too. 4 new tests. (2) 'Re-run' is HIDDEN when the seed was never recorded, rather than offered and dishonest; pre-D8 assets show 'not recorded' and only 'Re-run with a new seed'. NOT WIRED INTO THE STUDIO - see D17. The re-run handover exists but nothing consumes it, because MediaStudio.tsx is protected.</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="26.4" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
@@ -6105,10 +6109,14 @@
       </c>
       <c r="E93" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F93" s="13" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F93" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G93" s="14" t="inlineStr">
         <is>
           <t>Grid from index; filter by task/provider/date; provenance detail; re-run; re-run with new seed; delete; missing file placeholder</t>
@@ -6142,10 +6150,14 @@
       </c>
       <c r="E94" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F94" s="13" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F94" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G94" s="14" t="inlineStr">
         <is>
           <t>FAIL</t>
@@ -6179,10 +6191,14 @@
       </c>
       <c r="E95" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F95" s="13" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F95" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G95" s="14" t="inlineStr">
         <is>
           <t>Virtualise only if an existing primitive exists; otherwise paginate. No new dependency</t>
@@ -6216,10 +6232,14 @@
       </c>
       <c r="E96" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F96" s="13" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F96" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G96" s="14" t="n"/>
       <c r="H96" s="6" t="inlineStr">
         <is>
@@ -6249,10 +6269,14 @@
       </c>
       <c r="E97" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F97" s="13" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F97" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G97" s="14" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6286,10 +6310,14 @@
       </c>
       <c r="E98" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F98" s="13" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F98" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G98" s="14" t="inlineStr">
         <is>
           <t>feat(media): add the media library</t>
@@ -7710,7 +7738,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8560,6 +8588,39 @@
         </is>
       </c>
       <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>D17</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>AUTHORISATION NEEDED, not a contradiction. Task 13's library can hand a generation back to the studio - services/media/rerun.ts holds the handover - but NOTHING CONSUMES IT, because MediaStudio.tsx and routes/media.tsx are both frozen by the selective v2.0.32 protected surface. Reading the handover there, or adding a Library tab to the Media workspace, means editing a protected file, which under Q1 requires a guard re-baseline in an isolated commit AND the user's explicit authorisation for that specific change.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>The user-visible half of Task 13's 're-run'. Today the buttons navigate to Media but the form does not repopulate, so 're-run' is a viewer feature rather than a working one. Also why the library's only in-app link is from Settings &gt; Media rather than from the Media workspace where a user would look for it.</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Ask the user to authorise ONE protected-file change covering both: consume the pending re-run in MediaStudio, and add a Library entry point to the Media workspace. Then re-baseline the guard in its own single-purpose commit, exactly as Task 11 did. Deliberately NOT done unasked - the guard exists to make this a decision rather than a habit.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>

--- a/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
+++ b/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
@@ -1093,7 +1093,7 @@
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>Tasks 0-8 and 10-13 Done. NEXT: the user must answer D17 (authorise one protected-file change so the library's 're-run' actually reaches the studio) - it is the only thing standing between Task 13 being a viewer and being useful. After that: Task 18 (credential storage, scheduled by the user via D14), then Tasks 14, 15, 16 and finally 17. Task 9 stays PARKED (D12).</t>
+          <t>Tasks 0-8 and 10-13 and 18 Done. NEXT: Task 16 (documentation and ADRs) then Task 17 (final verification), per the user's chosen order on 2026-09-10: 18 -&gt; 16 -&gt; 17, with Tasks 14 and 15 DEFERRED by his decision, not forgotten. Task 9 stays PARKED (D12). Before Task 17 closes, Evidence row 10 must be worked: the credential store and the thumbnailer have both only ever run against fakes.</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="B11" s="22" t="inlineStr">
         <is>
-          <t>2026-09-10 for Task 13: full make verify EXITCODE=0. Web 2633 passed / 16 skipped, extensions 250 and 276, Rust 903 passed / 0 failed, guard verified. Run from a VS x64 developer shell with printf plus its three msys DLLs on PATH - see D15.</t>
+          <t>2026-09-10 for Task 18: full make verify EXITCODE=0. See the Tasks sheet for counts. Run from a VS x64 developer shell with printf plus its three msys DLLs on PATH - see D15.</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>Ask the user to answer D17 - it blocks nothing technically but leaves Task 13 half-useful. Then Task 18. Still open: Q6 sequencing; the APPDATA folder migration; D16 (shared Progress primitive is inaccessible).</t>
+          <t>Task 16 next. Note for whoever does it: AGENTS.md rule 4 says Rust work uses cargo check AND cargo clippy, but the Makefile has NO clippy target, so make verify never enforces it and 53 pre-existing clippy findings have accumulated repo-wide (none in media code). That gap between the stated rule and the actual gate is worth closing in Task 16 or 17, or recording as a deliberate exception. Still open: Q6 sequencing; the APPDATA folder migration; D16 (shared Progress primitive is inaccessible); D17 is now Answered and done.</t>
         </is>
       </c>
     </row>
@@ -2313,7 +2313,7 @@
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F21" s="13" t="inlineStr"/>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="K21" s="15" t="inlineStr">
         <is>
-          <t>Makes Q2 real. Task 6 shipped remoteHttp.ts but providerFactory builds it WITHOUT a secret resolver, so a cloud provider reports unauthorised rather than sending a blank Authorization header. Task 12 added services/media/secrets.ts as the single seam the UI hands a credential to, holding it in memory for the session only. This task replaces that backing store with the OS credential store chosen in D3 and the crates approved in Q5, then wires the resolver. Definition of done: a cloud provider configured with a key survives a relaunch and authenticates; the key is never in localStorage, never in the provider store, and never in the DOM.</t>
+          <t>2026-09-10: Task 18 COMPLETE, T18-S01..S07 Done. Cloud providers can now hold an API key, which is what makes Q2's answer real rather than nominal. New: src-tauri/src/core/media/{mod,secrets,commands}.rs and web-app/src/services/media/__tests__/secrets.test.ts; rewritten web-app/src/services/media/secrets.ts; providerFactory now passes a resolver to remoteHttp. 19 new tests (9 Rust, 10 TS). DEVIATION FROM Q5's LITERAL WORDING, flagged to the user: Q5 approved 'keyring 4.2 (core)'. The crate `keyring` at 4.2 is the ALL-IN-ONE CLI - its lib is `pub mod cli; pub use cli::*` - so depending on it would drag a command-line tool's dependency tree into the app. Used keyring-core 1.0 instead, which is the library the three approved platform stores already depend on and what '(core)' meant. Same family, same approval, fewer dependencies. Checked against crates.io rather than assumed. DESIGN NOTES: the OS call sits behind a trait with an in-memory impl, so cargo test can NEVER write to the developer's real Credential Manager. There is deliberately NO enumerate-credentials command. An error never contains the secret - asserted on both Display and Debug. A machine with no credential store (Linux without Secret Service) is reported BEFORE the user types a key. The Task 12 seam paid off exactly as designed: swapping session-memory for the OS store changed secrets.ts and one line of providerFactory; no component moved. GATE CAUGHT A REAL OMISSION: src/lib/__tests__/ipc-contract.test.ts pins the exact set of desktop-only IPC commands, and correctly failed until the four new ones were declared there with the reason. NOT VERIFIED AGAINST A REAL KEYCHAIN - see Evidence row 10.</t>
         </is>
       </c>
     </row>
@@ -7490,10 +7490,14 @@
       </c>
       <c r="E130" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F130" s="13" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F130" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G130" s="14" t="inlineStr">
         <is>
           <t>Round-trip against the platform backend; a missing key is not an error</t>
@@ -7526,10 +7530,14 @@
       </c>
       <c r="E131" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F131" s="13" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F131" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G131" s="14" t="inlineStr">
         <is>
           <t>Exactly the crates named in Q5 - no others without asking</t>
@@ -7562,10 +7570,14 @@
       </c>
       <c r="E132" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F132" s="13" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F132" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G132" s="14" t="inlineStr">
         <is>
           <t>media_secret_set / media_secret_get / media_secret_delete</t>
@@ -7598,10 +7610,14 @@
       </c>
       <c r="E133" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F133" s="13" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F133" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G133" s="14" t="inlineStr">
         <is>
           <t>Flip MEDIA_SECRET_PERSISTENCE to 'credential-store'; UI warning disappears</t>
@@ -7634,10 +7650,14 @@
       </c>
       <c r="E134" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F134" s="13" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F134" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G134" s="14" t="inlineStr">
         <is>
           <t>Cloud provider stops reporting unauthorised</t>
@@ -7670,10 +7690,14 @@
       </c>
       <c r="E135" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F135" s="13" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F135" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G135" s="14" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7706,10 +7730,14 @@
       </c>
       <c r="E136" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F136" s="13" t="inlineStr"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F136" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G136" s="14" t="inlineStr">
         <is>
           <t>feat(media): store provider credentials in the OS keychain</t>
@@ -8614,10 +8642,14 @@
           <t>Ask the user to authorise ONE protected-file change covering both: consume the pending re-run in MediaStudio, and add a Library entry point to the Media workspace. Then re-baseline the guard in its own single-purpose commit, exactly as Task 11 did. Deliberately NOT done unasked - the guard exists to make this a decision rather than a habit.</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>ANSWERED BY THE USER 2026-09-10: authorise ONE protected-file change covering both. Done the same day. 513421ab1 changed MediaGenerationForm.tsx (an optional initialParams), MediaStudio.tsx (consume the handover once; accept an injected libraryLink) and routes/media.tsx (supply the link); 0e437b531 re-baselined the guard in an isolated single-purpose commit naming exactly those three files. MediaStudio.test.tsx needed NO edit, because the link is injected rather than built with a router inside the component. The guard was run before re-baselining and named exactly the three changed files.</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Answered</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8996,7 +9028,7 @@
       <c r="F11" s="15" t="n"/>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>2026-09-09: add the Task 8 thumbnailer to this list. createBrowserThumbnailer() (canvas downscale to WebP for images, first-frame capture for video) cannot be exercised under jsdom, which implements neither HTMLCanvasElement.toBlob nor video decoding. Its failure path IS tested - a throwing thumbnailer still saves the asset. The success path needs a real WebView2.</t>
+          <t>2026-09-09: add the Task 8 thumbnailer to this list. createBrowserThumbnailer() (canvas downscale to WebP for images, first-frame capture for video) cannot be exercised under jsdom, which implements neither HTMLCanvasElement.toBlob nor video decoding. Its failure path IS tested - a throwing thumbnailer still saves the asset. The success path needs a real WebView2. | 2026-09-10: add the Task 18 credential store to this list. Every test runs against an in-memory CredentialStore, deliberately, so the suite cannot write to the machine that runs it. That means the REAL round trip - Windows Credential Manager, macOS Keychain, Linux Secret Service - has never actually executed. What still needs doing by hand in the running app: add a cloud provider with a key, restart the app, and confirm the key survives and the provider authenticates; then delete it and confirm it is gone from the OS store. Also unverified: the Linux no-Secret-Service path, which needs a box without one. Recorded rather than implied passed.</t>
         </is>
       </c>
     </row>

--- a/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
+++ b/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
@@ -1093,7 +1093,7 @@
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>Tasks 0-8 and 10-13 and 18 Done. NEXT: Task 16 (documentation and ADRs) then Task 17 (final verification), per the user's chosen order on 2026-09-10: 18 -&gt; 16 -&gt; 17, with Tasks 14 and 15 DEFERRED by his decision, not forgotten. Task 9 stays PARKED (D12). Before Task 17 closes, Evidence row 10 must be worked: the credential store and the thumbnailer have both only ever run against fakes.</t>
+          <t>Tasks 0-8, 10-13, 16 and 18 Done. ONLY TASK 17 REMAINS of the chosen path (the user chose 18 -&gt; 16 -&gt; 17 on 2026-09-10 and DEFERRED Tasks 14 and 15; Task 9 is PARKED under D12). Task 17 is mostly running commands that have all passed repeatedly - but T17-S08 is void (see the Do-not-commit row) and T17-S09 needs the GPU box. Before it can honestly close, Evidence rows 7-12 need working, and row 10 in particular: the credential store and the Task 8 thumbnailer have BOTH only ever run against fakes.</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>Task 16 next. Note for whoever does it: AGENTS.md rule 4 says Rust work uses cargo check AND cargo clippy, but the Makefile has NO clippy target, so make verify never enforces it and 53 pre-existing clippy findings have accumulated repo-wide (none in media code). That gap between the stated rule and the actual gate is worth closing in Task 16 or 17, or recording as a deliberate exception. Still open: Q6 sequencing; the APPDATA folder migration; D16 (shared Progress primitive is inaccessible); D17 is now Answered and done.</t>
+          <t>Task 17. Two things it cannot do on this laptop: T17-S09 (manual smoke against a real worker, GPU box) and the real-keychain round trip on Evidence row 10. Do not mark either passed. Still open: Q6 sequencing; the APPDATA folder migration; D16 (shared Progress primitive is inaccessible); and the gap that AGENTS.md rule 4 requires cargo clippy while the Makefile has no clippy target, so 53 pre-existing findings sit unenforced.</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F19" s="13" t="n"/>
@@ -2243,7 +2243,11 @@
           <t>Six ADRs. AGENTS.md must stay under 200 lines.</t>
         </is>
       </c>
-      <c r="K19" s="15" t="n"/>
+      <c r="K19" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-10: Task 16 COMPLETE, T16-S01..S05 Done. EIGHT ADRs, not six: the plan's six, plus the seventh it requires when Task 6 runs (cloud providers), plus credential storage - scope the original plan did not know it had (D14). New 'Radium Media platform' section in docs/decisions/INDEX.md. DEVELOP.md gained the media data path AND an explicit note that credentials are NOT in the data folder and are cleared by nothing in that table - an omission there would have actively misled. THREE CORRECTIONS rather than copy-forwards: (1) the ADR index claimed 215 records against 216 files - a pre-existing off-by-one, now set to the true 224 with a comment so it is not 'fixed' back. (2) The registry ADR is marked NOT YET IMPLEMENTED, because Task 15 is deferred; an ADR describing unbuilt code is worse than none. (3) AGENTS.md rule 9 was stale - it still told every agent that Task 0 is a hard gate and make verify is red until it lands, and that Q1 is open. Replaced with what is true now. AGENTS.md is 198 lines, inside the 200 target. Gate: full make verify EXITCODE=0; web 2649, Rust 496, guard verified.</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="26.4" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
@@ -6898,10 +6902,14 @@
       </c>
       <c r="E114" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F114" s="13" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F114" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G114" s="14" t="inlineStr">
         <is>
           <t>From docs/decisions/_TEMPLATE.md</t>
@@ -6935,10 +6943,14 @@
       </c>
       <c r="E115" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F115" s="13" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F115" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G115" s="14" t="inlineStr">
         <is>
           <t>One line each in docs/decisions/INDEX.md, correct section, bump the record count</t>
@@ -6972,10 +6984,14 @@
       </c>
       <c r="E116" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F116" s="13" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F116" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G116" s="14" t="inlineStr">
         <is>
           <t>Include factory-reset and uninstaller behaviour</t>
@@ -7009,10 +7025,14 @@
       </c>
       <c r="E117" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F117" s="13" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F117" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G117" s="14" t="inlineStr">
         <is>
           <t>At most one repository-map line plus a link</t>
@@ -7046,10 +7066,14 @@
       </c>
       <c r="E118" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F118" s="13" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F118" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G118" s="14" t="inlineStr">
         <is>
           <t>docs: record media platform decisions</t>
@@ -9049,11 +9073,19 @@
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F12" s="15" t="n"/>
-      <c r="G12" s="15" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+      <c r="G12" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-10: EIGHT ADRs written and indexed, not six. The plan's six, plus the seventh it mandates because Task 6 ran (cloud providers), plus credential storage from D14. All under a new 'Radium Media platform' section in docs/decisions/INDEX.md. The registry ADR is explicitly marked NOT YET IMPLEMENTED because Task 15 is deferred.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">

--- a/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
+++ b/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
@@ -1093,7 +1093,7 @@
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>Tasks 0-8, 10-13, 16 and 18 Done. ONLY TASK 17 REMAINS of the chosen path (the user chose 18 -&gt; 16 -&gt; 17 on 2026-09-10 and DEFERRED Tasks 14 and 15; Task 9 is PARKED under D12). Task 17 is mostly running commands that have all passed repeatedly - but T17-S08 is void (see the Do-not-commit row) and T17-S09 needs the GPU box. Before it can honestly close, Evidence rows 7-12 need working, and row 10 in particular: the credential store and the Task 8 thumbnailer have BOTH only ever run against fakes.</t>
+          <t>Tasks 0-8, 10-13, 16 and 18 Done. Task 17 is PARTIAL and correctly NOT marked Done: everything that can be run on a laptop has been run and passed, but T17-S09 needs the GPU box and Evidence rows 8 and 10 need a running app and real hardware. Read docs/superpowers/plans/2026-09-10-model-agnostic-media-platform-evidence.md first - it names what could NOT be produced instead of implying it passed. Tasks 14 and 15 are DEFERRED by the user's decision; Task 9 is PARKED under D12.</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>Task 17. Two things it cannot do on this laptop: T17-S09 (manual smoke against a real worker, GPU box) and the real-keychain round trip on Evidence row 10. Do not mark either passed. Still open: Q6 sequencing; the APPDATA folder migration; D16 (shared Progress primitive is inaccessible); and the gap that AGENTS.md rule 4 requires cargo clippy while the Makefile has no clippy target, so 53 pre-existing findings sit unenforced.</t>
+          <t>Nothing is waiting on the agent. WAITING ON THE USER / HARDWARE: (1) the GPU box, for T17-S09 and the screenshots; (2) a by-hand check that a cloud provider's API key really survives a restart - the OS credential store has NEVER been exercised, only its in-memory stand-in; (3) Q6 sequencing; (4) whether to schedule the deferred Tasks 14 and 15; (5) D16, the shared Progress primitive; (6) the APPDATA folder migration.</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="F20" s="13" t="n"/>
@@ -2292,7 +2292,11 @@
           <t>Step 9 (manual smoke against a real worker) is the only step that needs the GPU box.</t>
         </is>
       </c>
-      <c r="K20" s="15" t="n"/>
+      <c r="K20" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-10: Task 17 is PARTIAL and deliberately NOT marked Done. S01-S07 and S10-S11 Done; S08 is N/A (premise void); S09 is BLOCKED on the GPU box. Evidence report written to docs/superpowers/plans/2026-09-10-model-agnostic-media-platform-evidence.md against all twelve items of plan section 12. THREE ITEMS CANNOT BE PRODUCED HERE and are named rather than implied passed: item 8 (screenshots - needs a running app and the GPU box); item 10 (six manual steps, including the REAL credential-store round trip, which has never executed because every test uses the in-memory store by design); and item 9 is a disclosure, not a pass - EVERY media surface is English-only in all 14 locales because no media component imports useTranslation, which is Task 14, deferred by the user. Item 6 is VOID and item 7 turned out to be already enforced by verify-selective-v2032.mjs on every run. The task closes when the GPU box is available; nothing else blocks it.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -7107,10 +7111,14 @@
       </c>
       <c r="E119" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F119" s="13" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F119" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G119" s="14" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7144,10 +7152,14 @@
       </c>
       <c r="E120" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F120" s="13" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F120" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G120" s="14" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7181,10 +7193,14 @@
       </c>
       <c r="E121" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F121" s="13" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F121" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G121" s="14" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -7218,10 +7234,14 @@
       </c>
       <c r="E122" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F122" s="13" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F122" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G122" s="14" t="inlineStr">
         <is>
           <t>PASS including coverage floors</t>
@@ -7255,10 +7275,14 @@
       </c>
       <c r="E123" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F123" s="13" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F123" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G123" s="14" t="inlineStr">
         <is>
           <t>PASS with the final manifest</t>
@@ -7292,10 +7316,14 @@
       </c>
       <c r="E124" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F124" s="13" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F124" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G124" s="14" t="inlineStr">
         <is>
           <t>PASS. Report honestly if the local toolchain cannot run the Rust suites</t>
@@ -7329,10 +7357,14 @@
       </c>
       <c r="E125" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F125" s="13" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F125" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G125" s="14" t="inlineStr">
         <is>
           <t>Clean</t>
@@ -7366,10 +7398,14 @@
       </c>
       <c r="E126" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F126" s="13" t="n"/>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F126" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G126" s="14" t="inlineStr">
         <is>
           <t>downloads/index.html, extensions/yarn.lock, src-tauri/icons/icon.png, DownloadManegement.tsx</t>
@@ -7380,7 +7416,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I126" s="15" t="n"/>
+      <c r="I126" s="15" t="inlineStr">
+        <is>
+          <t>VOID. The premise is gone: the user authorised committing the pre-existing dirty paths, the tree is clean and all eleven are committed. Verified with git status, not inferred.</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="26.4" customHeight="1">
       <c r="A127" s="6" t="inlineStr">
@@ -7403,10 +7443,14 @@
       </c>
       <c r="E127" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F127" s="13" t="n"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="F127" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G127" s="14" t="inlineStr">
         <is>
           <t>Submit, watch, preview, library, re-run. THE ONLY STEP THAT NEEDS THE GPU BOX</t>
@@ -7417,7 +7461,11 @@
           <t>GPU box</t>
         </is>
       </c>
-      <c r="I127" s="15" t="n"/>
+      <c r="I127" s="15" t="inlineStr">
+        <is>
+          <t>BLOCKED ON HARDWARE: needs the GPU box. No end-to-end generation has ever run.</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="6" t="inlineStr">
@@ -7440,10 +7488,14 @@
       </c>
       <c r="E128" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F128" s="13" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F128" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G128" s="14" t="inlineStr">
         <is>
           <t>All 12 items on the Evidence sheet</t>
@@ -7477,10 +7529,14 @@
       </c>
       <c r="E129" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F129" s="13" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F129" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G129" s="14" t="inlineStr">
         <is>
           <t>test: verify the model-agnostic media platform</t>
@@ -8777,7 +8833,7 @@
       </c>
       <c r="G2" s="15" t="inlineStr">
         <is>
-          <t>contract: web-app/src/services/media/contract/{tasks,params,models,jobs,index,upcast}.ts + __tests__/{params,upcast}.test.ts, parity.test.tsx, fixtures/worker-v1-capabilities.json. v1 residue: services/atomicMedia/client{,.test}.ts. catalog: lib/models.ts, hooks/useModelSources.ts, services/models/default.ts (+3 test files). build: Makefile (app-icons). guard: scripts/selective-v2032-protected.json. docs: this tracker. No UI file changed.</t>
+          <t>contract: web-app/src/services/media/contract/{tasks,params,models,jobs,index,upcast}.ts + __tests__/{params,upcast}.test.ts, parity.test.tsx, fixtures/worker-v1-capabilities.json. v1 residue: services/atomicMedia/client{,.test}.ts. catalog: lib/models.ts, hooks/useModelSources.ts, services/models/default.ts (+3 test files). build: Makefile (app-icons). guard: scripts/selective-v2032-protected.json. docs: this tracker. No UI file changed. | 2026-09-10: See the evidence report, section 1. Registry layer NOT BUILT - Task 15 deferred.</t>
         </is>
       </c>
     </row>
@@ -8812,7 +8868,7 @@
       </c>
       <c r="G3" s="15" t="inlineStr">
         <is>
-          <t>make verify exit 0 on the working tree at every task boundary, AND on a from-scratch clean clone (2026-09-09). Latest run: web coverage 2368 passed / 16 skipped (up from 2234 at session start); extensions 250 + 276; Rust 487 + 12 + 167 + 205 + 28 + 4; coverage floor 9 critical files; selective-v2032 boundaries verified. Nothing skipped or unavailable. One run FAILED on lint (exit 2) from an omit-by-destructuring pattern leaving unused bindings; fixed and re-run green.</t>
+          <t>make verify exit 0 on the working tree at every task boundary, AND on a from-scratch clean clone (2026-09-09). Latest run: web coverage 2368 passed / 16 skipped (up from 2234 at session start); extensions 250 + 276; Rust 487 + 12 + 167 + 205 + 28 + 4; coverage floor 9 critical files; selective-v2032 boundaries verified. Nothing skipped or unavailable. One run FAILED on lint (exit 2) from an omit-by-destructuring pattern leaving unused bindings; fixed and re-run green. | 2026-09-10: MAKE_VERIFY_EXITCODE=0 at every task boundary; latest web 2649 / ext 250+276 / Rust 912. NAMED AS NOT RUN: cargo clippy is not in make verify at all, though AGENTS.md rule 4 requires it - 53 pre-existing findings repo-wide, none in media code.</t>
         </is>
       </c>
     </row>
@@ -8847,7 +8903,7 @@
       </c>
       <c r="G4" s="15" t="inlineStr">
         <is>
-          <t>parity.test.tsx - 6 tests, all passing. It renders the live MediaGenerationForm and asserts JSON.stringify equality of the submitted body across defaults, negative prompt + seed, a non-default resolution, the quantiser tie, and image_to_video with a reference image. Mutation-checked: flipping the tie-break from &lt;= to &lt; fails exactly one case, so the green is earned not vacuous.</t>
+          <t>parity.test.tsx - 6 tests, all passing. It renders the live MediaGenerationForm and asserts JSON.stringify equality of the submitted body across defaults, negative prompt + seed, a non-default resolution, the quantiser tie, and image_to_video with a reference image. Mutation-checked: flipping the tie-break from &lt;= to &lt; fails exactly one case, so the green is earned not vacuous. | 2026-09-10: parity.test.tsx drives the live form through the real downcaster; mutation-tested.</t>
         </is>
       </c>
     </row>
@@ -8868,7 +8924,7 @@
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F5" s="15" t="inlineStr">
@@ -8878,7 +8934,7 @@
       </c>
       <c r="G5" s="15" t="inlineStr">
         <is>
-          <t>2026-09-09: both adapters that exist pass conformance.ts unmodified - Radium Media Worker 30/30, ComfyUI 58/58 (30 conformance + 28 ComfyUI-specific). Still Partial only because Task 6's remote adapter does not exist yet.</t>
+          <t>2026-09-09: both adapters that exist pass conformance.ts unmodified - Radium Media Worker 30/30, ComfyUI 58/58 (30 conformance + 28 ComfyUI-specific). Still Partial only because Task 6's remote adapter does not exist yet. | 2026-09-10: All three adapters pass conformance.ts unmodified. Caveat D4: ComfyUI fixtures transcribed from 0.35.0 source, not captured live.</t>
         </is>
       </c>
     </row>
@@ -8913,7 +8969,7 @@
       </c>
       <c r="G6" s="15" t="inlineStr">
         <is>
-          <t>make test-selective-v2032 green. Re-baseline commits: Task 0 = 9e8249046 era (8 media files); Task 2 = 59ee8b7fb (exactly 2 entries - atomicMedia/client.ts and client.test.ts). Each re-baseline is an isolated commit containing only the manifest, per Q1.</t>
+          <t>make test-selective-v2032 green. Re-baseline commits: Task 0 = 9e8249046 era (8 media files); Task 2 = 59ee8b7fb (exactly 2 entries - atomicMedia/client.ts and client.test.ts). Each re-baseline is an isolated commit containing only the manifest, per Q1. | 2026-09-10: Green. Five isolated re-baseline commits listed by SHA in the evidence report, section 5.</t>
         </is>
       </c>
     </row>
@@ -8969,11 +9025,19 @@
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F8" s="15" t="n"/>
-      <c r="G8" s="15" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+      <c r="G8" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-10: Already enforced by the gate: verify-selective-v2032.mjs checks forbidden paths, documents and text on every run and prints "Selective v2.0.32 boundaries verified."</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="26.4" customHeight="1">
       <c r="A9" s="6" t="n">
@@ -8996,11 +9060,19 @@
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F9" s="15" t="n"/>
-      <c r="G9" s="15" t="n"/>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+      <c r="G9" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-10: NOT PRODUCED. Needs a running app and the GPU box. Nothing in this evidence set should be read as visual confirmation.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
@@ -9019,11 +9091,19 @@
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F10" s="15" t="n"/>
-      <c r="G10" s="15" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+      <c r="G10" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-10: DISCLOSURE, not a pass: EVERY media surface is English-only in all 14 locales. No media component imports useTranslation; all strings are hardcoded English. The one key added to locales/en/common.json falls back to English in cs, de-DE, es, fr, id, ja, ko, pl, pt-BR, ru, vn, zh-CN, zh-TW. Task 14, deferred by the user 2026-09-10 - a known deferral, not an oversight.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="26.4" customHeight="1">
       <c r="A11" s="6" t="n">
@@ -9104,11 +9184,19 @@
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F13" s="15" t="n"/>
-      <c r="G13" s="15" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+      <c r="G13" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-10: Listed per phase in the evidence report, section 12.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="24" t="inlineStr">

--- a/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
+++ b/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
@@ -1189,7 +1189,7 @@
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>Nothing is waiting on the agent. WAITING ON THE USER / HARDWARE: (1) the GPU box, for T17-S09 and the screenshots; (2) a by-hand check that a cloud provider's API key really survives a restart - the OS credential store has NEVER been exercised, only its in-memory stand-in; (3) Q6 sequencing; (4) whether to schedule the deferred Tasks 14 and 15; (5) D16, the shared Progress primitive; (6) the APPDATA folder migration.</t>
+          <t>WAITING ON THE USER: (1) authorise a protected-file change to finish Task 14 - about 13 strings in MediaStudio, MediaGenerationForm, MediaJobStatus and MediaPreview, same shape as D17: one change plus an isolated re-baseline. (2) The GPU box, for T17-S09 and the screenshots. (3) A by-hand check that a cloud API key survives a restart - the OS credential store has never been exercised. (4) Q6. (5) D16. (6) Task 15, still deferred. (7) The APPDATA folder migration.</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F17" s="13" t="n"/>
@@ -2153,7 +2153,11 @@
           <t>Pure text work. Disclose any locale shipped untranslated.</t>
         </is>
       </c>
-      <c r="K17" s="15" t="n"/>
+      <c r="K17" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-10: Task 14 PARTIAL, and deliberately not marked Done. Done: the key scheme, a new `media` namespace (locales/en/media.json, auto-discovered by the existing glob - no wiring needed), every string extracted from ProviderList, ModelCatalog, MediaLibrary, AssetDetail and both new routes, and T14-S05 wiring label_key/help_key in MediaParamField with three tests. S04 is N/A by the USER'S DECISION: the 13 other locales stay on English fallback, disclosed, rather than shipping unverifiable machine translations. S01 is PARTIAL: about 13 strings remain in the four guard-protected files and need his authorisation. TWO FINDINGS. (1) The app's translate() has NO PLURAL SUPPORT - it is a plain nested lookup, so i18next _one/_other suffixes never resolve. Avoided by making the one count string plural-neutral ('Models: {{count}}'); selecting the form in the component would have imposed English plural rules on ru/pl/cs, which need three. (2) The DEFAULT translation context returned the raw key and ignored defaultValue, so any component rendered outside TranslationProvider showed users literal keys like 'media:asset.reRun'. context.ts already imported i18next; it now delegates to it. That also made the media tests assert real resolved English through the real i18n path instead of mocked keys.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -6359,10 +6363,14 @@
       </c>
       <c r="E99" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F99" s="13" t="n"/>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="F99" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G99" s="14" t="inlineStr">
         <is>
           <t>Eight Media components plus the Task 12-13 surfaces</t>
@@ -6373,7 +6381,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I99" s="15" t="n"/>
+      <c r="I99" s="15" t="inlineStr">
+        <is>
+          <t>Every string extracted from the UNPROTECTED media surfaces. About 13 remain in the four guard-protected files (MediaStudio, MediaGenerationForm, MediaJobStatus, MediaPreview): Prompt, Model, Provider, Device, Online, Offline, Needs a key, Not checked, No media provider, Select a model to begin, Generated media, Generation task, Providers. Finishing them needs the user to authorise a protected-file change plus an isolated re-baseline, exactly as D17 did.</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="26.4" customHeight="1">
       <c r="A100" s="6" t="inlineStr">
@@ -6396,10 +6408,14 @@
       </c>
       <c r="E100" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F100" s="13" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F100" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G100" s="14" t="inlineStr">
         <is>
           <t>media:studio.*, form.*, task.*, param.*, status.*, library.*, provider.*, error.*</t>
@@ -6433,10 +6449,14 @@
       </c>
       <c r="E101" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F101" s="13" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F101" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G101" s="14" t="n"/>
       <c r="H101" s="6" t="inlineStr">
         <is>
@@ -6466,10 +6486,14 @@
       </c>
       <c r="E102" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F102" s="13" t="n"/>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F102" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G102" s="14" t="inlineStr">
         <is>
           <t>cs, de-DE, es, fr, id, ja, ko, pl, pt-BR, ru, vn, zh-CN, zh-TW. Disclose any left untranslated</t>
@@ -6480,7 +6504,11 @@
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I102" s="15" t="n"/>
+      <c r="I102" s="15" t="inlineStr">
+        <is>
+          <t>ANSWERED BY THE USER 2026-09-10: leave the 13 other locales on English fallback and DISCLOSE it, rather than ship machine translations neither he nor the agent can verify. No regression - it is what happens today - and the extraction means a translator can now drop files in with no code change. Recorded in the evidence report, item 9.</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="26.4" customHeight="1">
       <c r="A103" s="6" t="inlineStr">
@@ -6503,10 +6531,14 @@
       </c>
       <c r="E103" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F103" s="13" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F103" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G103" s="14" t="inlineStr">
         <is>
           <t>Fall back to the provider's label - third-party params will never have a locale entry</t>
@@ -6540,10 +6572,14 @@
       </c>
       <c r="E104" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F104" s="13" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F104" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G104" s="14" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6577,10 +6613,14 @@
       </c>
       <c r="E105" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F105" s="13" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F105" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G105" s="14" t="inlineStr">
         <is>
           <t>feat(media): localise the Media workspace</t>
@@ -7846,7 +7886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8733,6 +8773,43 @@
         </is>
       </c>
       <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>D18</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>UX DEFECT in shared i18n, found during Task 14 and DELIBERATELY NOT FIXED. The default value of TranslationContext is `t: (key) =&gt; key` - it returns the raw key and ignores `defaultValue` entirely. So any component rendered outside TranslationProvider shows the user literal text like `media:asset.reRun` instead of English. context.ts already imports the i18next instance and uses it only as a type; delegating to it is a one-line change.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Nothing today: the real app mounts everything inside TranslationProvider, so users do not see it. It bites any future component rendered outside the provider, and it is why component tests across this repo assert on raw keys rather than on what a user reads.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Give it its own small task. The agent DID make this change during Task 14 and the gate caught it: five unrelated tests broke - AgentWorkspaceLayout and AgentApprovalDialog among them - because they deliberately assert raw keys like 'chat:workspacePreview.generating'. Fixing the default therefore means updating those five tests as a deliberate act, not as collateral of an i18n task. Reverted; the media tests now delegate to the real i18n instance locally instead, which keeps the improvement inside the media feature.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Agent judgement, 2026-09-10. Recorded rather than either shipped quietly or dropped. Also a reminder that a change which conveniently makes your own tests pass deserves more suspicion, not less.</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Noted</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>

--- a/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
+++ b/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
@@ -1093,7 +1093,7 @@
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>Tasks 0-8, 10-13, 16 and 18 Done. Task 17 is PARTIAL and correctly NOT marked Done: everything that can be run on a laptop has been run and passed, but T17-S09 needs the GPU box and Evidence rows 8 and 10 need a running app and real hardware. Read docs/superpowers/plans/2026-09-10-model-agnostic-media-platform-evidence.md first - it names what could NOT be produced instead of implying it passed. Tasks 14 and 15 are DEFERRED by the user's decision; Task 9 is PARKED under D12.</t>
+          <t>Tasks 0-8, 10-13, 16 and 18 Done. Tasks 14, 15 and 17 are PARTIAL - each blocked only on something this machine cannot do, and each says so in its own notes. Task 9 is PARKED (D12). Read docs/superpowers/plans/2026-09-10-model-agnostic-media-platform-evidence.md before claiming anything is finished: it names what could NOT be produced rather than implying it passed.</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>WAITING ON THE USER: (1) authorise a protected-file change to finish Task 14 - about 13 strings in MediaStudio, MediaGenerationForm, MediaJobStatus and MediaPreview, same shape as D17: one change plus an isolated re-baseline. (2) The GPU box, for T17-S09 and the screenshots. (3) A by-hand check that a cloud API key survives a restart - the OS credential store has never been exercised. (4) Q6. (5) D16. (6) Task 15, still deferred. (7) The APPDATA folder migration.</t>
+          <t>Nothing is waiting on the agent. WAITING ON THE USER OR HARDWARE: (1) the GPU box - T17-S09 and the screenshots; (2) a by-hand check that a cloud API key survives a restart, since the OS credential store has only ever run against its in-memory stand-in; (3) authorise a protected-file change to finish Task 14's last ~13 strings, same shape as D17; (4) open the companion PR against atomic-chat-conf for T15-S06; (5) Q6; (6) D16 (Progress is inaccessible app-wide) and D18 (the default i18n context shows raw keys); (7) the APPDATA folder migration.</t>
         </is>
       </c>
     </row>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F18" s="13" t="n"/>
@@ -2202,7 +2202,11 @@
           <t>Structural clone of provider-registry.ts. Mocked fetch.</t>
         </is>
       </c>
-      <c r="K18" s="15" t="n"/>
+      <c r="K18" s="15" t="inlineStr">
+        <is>
+          <t>2026-09-10: Task 15 built and green, marked PARTIAL only because T15-S06's companion PR against atomic-chat-conf cannot be opened from here. New: services/media-registry.ts and its 13 tests; media-provider-store gained refreshRegistry(); ProviderList gained a 'Check for new providers' button; services/AGENTS.md gained section 3 with the failure-mode table and the schema. STRICTER THAN THE PROVIDER REGISTRY ON PURPOSE: that one can add a MODEL, this one can add a PROVIDER - i.e. a URL the app will send prompts to. Entries are DROPPED, never repaired, and three fields are forced regardless of payload: origin=registry (so an entry cannot claim builtin and make itself undeletable), auth.setting_key recomputed from the entry's own id (so a remote party cannot point the app at someone else's credential), and enabled=false. Unknown adapters, non-http(s) URLs and descriptors missing id/adapter are refused; a newer schema_version is refused ENTIRELY. A bundled provider always beats a remote entry with the same id. refreshRegistry only ever ADDS - a provider the user disabled or re-pointed survives untouched. SIX MUTATIONS, ALL KILLED - but one initially SURVIVED and exposed a fake test: the baseline-wins test used find(), which returns the FIRST match, so it passed even with two providers sharing an id. Now asserts exactly one. Second time today mutation testing caught a vacuous test. The gate also caught a real type error: narrowing an unknown through || widens it back to string, so auth.type was unvalidated on the one field that chooses which credential is read. Narrowed per branch rather than cast away.</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="26.4" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
@@ -6654,10 +6658,14 @@
       </c>
       <c r="E106" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F106" s="13" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F106" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G106" s="14" t="inlineStr">
         <is>
           <t>Fresh cache; fetch ok; fetch fail + stale cache; fetch fail no cache; schema too new; malformed; no Tauri fetch</t>
@@ -6691,10 +6699,14 @@
       </c>
       <c r="E107" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F107" s="13" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F107" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G107" s="14" t="inlineStr">
         <is>
           <t>FAIL</t>
@@ -6728,10 +6740,14 @@
       </c>
       <c r="E108" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F108" s="13" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F108" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G108" s="14" t="inlineStr">
         <is>
           <t>MEDIA_REGISTRY_SCHEMA_VERSION, TTL 1h, keys atomic_media_registry_cache_v1 / _ts_v1, clearMediaRegistryCache()</t>
@@ -6765,10 +6781,14 @@
       </c>
       <c r="E109" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F109" s="13" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F109" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G109" s="14" t="inlineStr">
         <is>
           <t>Reject unknown adapters, non-http(s) URLs, descriptors missing id/adapter. Remote input is untrusted</t>
@@ -6802,10 +6822,14 @@
       </c>
       <c r="E110" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F110" s="13" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F110" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G110" s="14" t="inlineStr">
         <is>
           <t>Mirror Settings to Providers</t>
@@ -6839,17 +6863,25 @@
       </c>
       <c r="E111" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F111" s="13" t="n"/>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="F111" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G111" s="14" t="n"/>
       <c r="H111" s="6" t="inlineStr">
         <is>
           <t>Laptop</t>
         </is>
       </c>
-      <c r="I111" s="15" t="n"/>
+      <c r="I111" s="15" t="inlineStr">
+        <is>
+          <t>Schema DOCUMENTED in services/AGENTS.md section 3, with the full failure-mode table. The companion PR against AtomicBot-ai/atomic-chat-conf is NOT OPENED - that is a second repository and outside this plan. Until a registry.json exists there, the loader simply falls back to the bundled baseline, which is the designed behaviour.</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
@@ -6872,10 +6904,14 @@
       </c>
       <c r="E112" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F112" s="13" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F112" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G112" s="14" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -6909,10 +6945,14 @@
       </c>
       <c r="E113" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F113" s="13" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F113" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G113" s="14" t="inlineStr">
         <is>
           <t>feat(media): load the media catalog from the remote registry</t>

--- a/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
+++ b/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
@@ -1093,7 +1093,7 @@
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>Tasks 0-8, 10-13, 16 and 18 Done. Tasks 14, 15 and 17 are PARTIAL - each blocked only on something this machine cannot do, and each says so in its own notes. Task 9 is PARKED (D12). Read docs/superpowers/plans/2026-09-10-model-agnostic-media-platform-evidence.md before claiming anything is finished: it names what could NOT be produced rather than implying it passed.</t>
+          <t>Tasks 0-8, 10-13, 16 and 18 Done. Task 9 SKIPPED with reasons (its narrowed scope already exists). Tasks 14, 15 and 17 are PARTIAL, each blocked only on something this machine cannot do. D16 and D18 fixed. Read docs/superpowers/plans/2026-09-10-model-agnostic-media-platform-evidence.md before claiming anything is finished - it names what could NOT be produced rather than implying it passed.</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>Nothing is waiting on the agent. WAITING ON THE USER OR HARDWARE: (1) the GPU box - T17-S09 and the screenshots; (2) a by-hand check that a cloud API key survives a restart, since the OS credential store has only ever run against its in-memory stand-in; (3) authorise a protected-file change to finish Task 14's last ~13 strings, same shape as D17; (4) open the companion PR against atomic-chat-conf for T15-S06; (5) Q6; (6) D16 (Progress is inaccessible app-wide) and D18 (the default i18n context shows raw keys); (7) the APPDATA folder migration.</t>
+          <t>Nothing is waiting on the agent, and nothing further can be done on a laptop. WAITING ON HARDWARE OR ANOTHER REPO: (1) the GPU box - T17-S09 and every screenshot; (2) a by-hand check that a cloud API key survives a restart, since the OS credential store has only ever run against its in-memory stand-in; (3) the companion PR against atomic-chat-conf for T15-S06; (4) real translators for the 13 non-English locales. WAITING ON THE USER: Q6 sequencing, and the APPDATA folder migration. KNOWN AND UNFIXED: AGENTS.md rule 4 requires cargo clippy but the Makefile has no clippy target, so 53 pre-existing findings sit unenforced; and external-contracts.test.ts fails 9 tests on Windows because it computes its repo root with endsWith('/web-app').</t>
         </is>
       </c>
     </row>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Skipped</t>
         </is>
       </c>
       <c r="F12" s="13" t="n"/>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="K12" s="15" t="inlineStr">
         <is>
-          <t>2026-09-10: Q3 ANSWERED - build it, default off, but NARROWED: adopt-or-start, graceful stop, status; NO auto-restart. Windows orphans to be fixed with a Job Object. THREE FINDINGS before any code: (1) REUSE, do not reinvent - src-tauri/src/core/mcp/helpers.rs already spawns and supervises child servers with CREATE_NO_WINDOW, Unix process groups, SIGTERM-&gt;wait-&gt;SIGKILL escalation and 'already gone' treated as success; the plan reads as greenfield Rust and it is not. (2) The plan's 'no orphan on app exit' test is only true for a GRACEFUL exit - cleanup runs from a destructor, which does not run when the app is force-killed or crashes, and on Windows nothing else covers it. For a GPU worker that means gigabytes of VRAM still held and port 13420 occupied by a zombie the app will not recognise next launch. A Job Object with kill-on-close is the only OS-level guarantee. It needs one extra FEATURE FLAG on windows-sys 0.60.2, which is ALREADY a dependency, so AGENTS.md rule 6 is not tripped - rule 6 covers new runtime dependencies, and this adds none. (3) BLOCKER D12: nothing in the repo knows how to start the worker.</t>
+          <t>2026-09-10: SKIPPED by the user's decision, with reasons. D12's answer narrowed this task to adopt-or-status: detect a worker already listening on 13420 and report its state, never launching one. THAT ALREADY EXISTS, and was built incidentally by earlier tasks: the atomicWorker adapter health-checks over HTTP (Task 3), the store keys health per provider (Task 4), and the UI shows Online/Offline with a retry button (Tasks 11-12). What a Rust supervisor would add beyond that is process identity, graceful stop and a Windows Job Object for orphan prevention - and all three are moot without spawn. There is no launch command (D12), so there is no process of ours to stop or orphan, and stopping a worker the user started by hand would be presumptuous. Building it would mean shipping code with no caller. REVERSIBLE: if the worker is ever bundled as a Tauri sidecar, the premise returns and this task should be reopened - see D12 option (ii).</t>
         </is>
       </c>
     </row>
@@ -2155,7 +2155,7 @@
       </c>
       <c r="K17" s="15" t="inlineStr">
         <is>
-          <t>2026-09-10: Task 14 PARTIAL, and deliberately not marked Done. Done: the key scheme, a new `media` namespace (locales/en/media.json, auto-discovered by the existing glob - no wiring needed), every string extracted from ProviderList, ModelCatalog, MediaLibrary, AssetDetail and both new routes, and T14-S05 wiring label_key/help_key in MediaParamField with three tests. S04 is N/A by the USER'S DECISION: the 13 other locales stay on English fallback, disclosed, rather than shipping unverifiable machine translations. S01 is PARTIAL: about 13 strings remain in the four guard-protected files and need his authorisation. TWO FINDINGS. (1) The app's translate() has NO PLURAL SUPPORT - it is a plain nested lookup, so i18next _one/_other suffixes never resolve. Avoided by making the one count string plural-neutral ('Models: {{count}}'); selecting the form in the component would have imposed English plural rules on ru/pl/cs, which need three. (2) The DEFAULT translation context returned the raw key and ignored defaultValue, so any component rendered outside TranslationProvider showed users literal keys like 'media:asset.reRun'. context.ts already imported i18next; it now delegates to it. That also made the media tests assert real resolved English through the real i18n path instead of mocked keys.</t>
+          <t>2026-09-10: Task 14 PARTIAL, and deliberately not marked Done. Done: the key scheme, a new `media` namespace (locales/en/media.json, auto-discovered by the existing glob - no wiring needed), every string extracted from ProviderList, ModelCatalog, MediaLibrary, AssetDetail and both new routes, and T14-S05 wiring label_key/help_key in MediaParamField with three tests. S04 is N/A by the USER'S DECISION: the 13 other locales stay on English fallback, disclosed, rather than shipping unverifiable machine translations. S01 is PARTIAL: about 13 strings remain in the four guard-protected files and need his authorisation. TWO FINDINGS. (1) The app's translate() has NO PLURAL SUPPORT - it is a plain nested lookup, so i18next _one/_other suffixes never resolve. Avoided by making the one count string plural-neutral ('Models: {{count}}'); selecting the form in the component would have imposed English plural rules on ru/pl/cs, which need three. (2) The DEFAULT translation context returned the raw key and ignored defaultValue, so any component rendered outside TranslationProvider showed users literal keys like 'media:asset.reRun'. context.ts already imported i18next; it now delegates to it. That also made the media tests assert real resolved English through the real i18n path instead of mocked keys. | 2026-09-10 UPDATE: the protected-file half is now DONE - the user authorised it, and the four frozen files were changed in 98f01fa11 with the guard re-baselined in its own isolated commit. Task 14 remains Partial for ONE reason only: the 13 non-English locales are still on English fallback by the user's decision, pending real translators. Every string in the feature is now a key, so that is a drop-in with no code change.</t>
         </is>
       </c>
     </row>
@@ -4886,10 +4886,14 @@
       </c>
       <c r="E62" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F62" s="13" t="n"/>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="F62" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G62" s="14" t="inlineStr">
         <is>
           <t>Skip the whole task if user-managed</t>
@@ -4923,10 +4927,14 @@
       </c>
       <c r="E63" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F63" s="13" t="n"/>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="F63" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G63" s="14" t="inlineStr">
         <is>
           <t>Spawn, health-gate, graceful stop, restart-on-crash with backoff ceiling, no orphan on exit</t>
@@ -4960,10 +4968,14 @@
       </c>
       <c r="E64" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F64" s="13" t="n"/>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="F64" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G64" s="14" t="inlineStr">
         <is>
           <t>src-tauri/src/core/media/supervisor.rs</t>
@@ -4997,10 +5009,14 @@
       </c>
       <c r="E65" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F65" s="13" t="n"/>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="F65" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G65" s="14" t="inlineStr">
         <is>
           <t>Permitted explicitly in the capabilities file</t>
@@ -5034,10 +5050,14 @@
       </c>
       <c r="E66" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F66" s="13" t="n"/>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="F66" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G66" s="14" t="inlineStr">
         <is>
           <t>PASS</t>
@@ -5071,10 +5091,14 @@
       </c>
       <c r="E67" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F67" s="13" t="n"/>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="F67" s="13" t="inlineStr">
+        <is>
+          <t>Warwick</t>
+        </is>
+      </c>
       <c r="G67" s="14" t="inlineStr">
         <is>
           <t>feat(media): supervise the local media worker process</t>
@@ -6367,7 +6391,7 @@
       </c>
       <c r="E99" s="13" t="inlineStr">
         <is>
-          <t>Partial</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F99" s="13" t="inlineStr">
@@ -6387,7 +6411,7 @@
       </c>
       <c r="I99" s="15" t="inlineStr">
         <is>
-          <t>Every string extracted from the UNPROTECTED media surfaces. About 13 remain in the four guard-protected files (MediaStudio, MediaGenerationForm, MediaJobStatus, MediaPreview): Prompt, Model, Provider, Device, Online, Offline, Needs a key, Not checked, No media provider, Select a model to begin, Generated media, Generation task, Providers. Finishing them needs the user to authorise a protected-file change plus an isolated re-baseline, exactly as D17 did.</t>
+          <t>COMPLETE 2026-09-10. The last 13 strings in the four guard-protected files were extracted under the authorisation the user gave that day. Every key carries its previous English as defaultValue, so rendered text is byte-identical and MediaStudio.test.tsx - itself protected - needed no edit.</t>
         </is>
       </c>
     </row>
@@ -8767,12 +8791,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Agent judgement, 2026-09-10. Recorded rather than silently fixed or silently ignored, per the same practice as D11 and D15.</t>
+          <t>FIXED 2026-09-10, authorised by the user. progress.tsx now forwards `value` to the Radix root, but only when it is in range: this component is deliberately tolerant of out-of-range input for its visual transform, and Radix logs an error outside max, so out-of-range stays indeterminate - the honest ARIA state for "no valid number". 5 new tests; the 10 existing ones untouched.</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Noted</t>
+          <t>Answered</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -8841,12 +8865,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Agent judgement, 2026-09-10. Recorded rather than either shipped quietly or dropped. Also a reminder that a change which conveniently makes your own tests pass deserves more suspicion, not less.</t>
+          <t>FIXED 2026-09-10, authorised by the user, on the second attempt. The first attempt during Task 14 was reverted because it broke unrelated tests. This time the blast radius was MEASURED first: the failing run showed 14 failures, but stashing the change proved external-contracts.test.ts fails 9 of them on HEAD by itself (the known Windows endsWith("/web-app") path bug). D18 accounted for exactly 5, in AgentApprovalDialog and AgentWorkspaceLayout, and those 5 were updated deliberately to assert the English a user reads instead of a raw key. Suites that mock the compat layer are unaffected - they bypass the context default entirely.</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Noted</t>
+          <t>Answered</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">

--- a/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
+++ b/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
@@ -1129,7 +1129,7 @@
       </c>
       <c r="B11" s="22" t="inlineStr">
         <is>
-          <t>2026-09-10 for Task 18: full make verify EXITCODE=0. See the Tasks sheet for counts. Run from a VS x64 developer shell with printf plus its three msys DLLs on PATH - see D15.</t>
+          <t>2026-09-10 for Task 18: full make verify EXITCODE=0. See the Tasks sheet for counts. Run from a VS x64 developer shell with printf plus its three msys DLLs on PATH - see D15. | 2026-09-10: THE 'RUN VITEST FROM THE REPO ROOT' WARNING IS RETIRED - its cause is fixed. external-contracts.test.ts computed its repo root with process.cwd().endsWith('/web-app'), which is ALWAYS false on Windows because cwd ends with a backslash. The root therefore stayed pointing at web-app and every fixture read failed with ENOENT: 9 tests that validate the pinned upstream registry contracts had never actually run on Windows. Now uses basename(cwd) === 'web-app', identical on Linux and macOS, and the 9 pass. Note make verify's own count is UNCHANGED at 2672, because that gate does not include this file - which is exactly why the bug survived.</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>Nothing is waiting on the agent, and nothing further can be done on a laptop. WAITING ON HARDWARE OR ANOTHER REPO: (1) the GPU box - T17-S09 and every screenshot; (2) a by-hand check that a cloud API key survives a restart, since the OS credential store has only ever run against its in-memory stand-in; (3) the companion PR against atomic-chat-conf for T15-S06; (4) real translators for the 13 non-English locales. WAITING ON THE USER: Q6 sequencing, and the APPDATA folder migration. KNOWN AND UNFIXED: AGENTS.md rule 4 requires cargo clippy but the Makefile has no clippy target, so 53 pre-existing findings sit unenforced; and external-contracts.test.ts fails 9 tests on Windows because it computes its repo root with endsWith('/web-app').</t>
+          <t>Nothing is waiting on the agent, and nothing further can be done on this machine. WAITING ON HARDWARE OR ANOTHER REPO: (1) the GPU box - T17-S09 and Evidence row 8, the only outstanding evidence row; (2) a by-hand check that a cloud API key survives a restart, since the OS credential store has only ever run against its in-memory stand-in; (3) the companion PR against atomic-chat-conf for T15-S06; (4) real translators for the 13 non-English locales - PARKED at the user's request 2026-09-10, and every string is already a key so it is a drop-in. WAITING ON THE USER: Q6 sequencing, and the APPDATA folder migration. KNOWN AND UNFIXED: AGENTS.md rule 4 requires cargo clippy but the Makefile has no clippy target, so 53 pre-existing findings sit unenforced. That is the last remaining gap between a stated rule and the actual gate.</t>
         </is>
       </c>
     </row>
@@ -9267,13 +9267,17 @@
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="F11" s="15" t="n"/>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>2026-09-09: add the Task 8 thumbnailer to this list. createBrowserThumbnailer() (canvas downscale to WebP for images, first-frame capture for video) cannot be exercised under jsdom, which implements neither HTMLCanvasElement.toBlob nor video decoding. Its failure path IS tested - a throwing thumbnailer still saves the asset. The success path needs a real WebView2. | 2026-09-10: add the Task 18 credential store to this list. Every test runs against an in-memory CredentialStore, deliberately, so the suite cannot write to the machine that runs it. That means the REAL round trip - Windows Credential Manager, macOS Keychain, Linux Secret Service - has never actually executed. What still needs doing by hand in the running app: add a cloud provider with a key, restart the app, and confirm the key survives and the provider authenticates; then delete it and confirm it is gone from the OS store. Also unverified: the Linux no-Secret-Service path, which needs a box without one. Recorded rather than implied passed.</t>
+          <t>2026-09-09: add the Task 8 thumbnailer to this list. createBrowserThumbnailer() (canvas downscale to WebP for images, first-frame capture for video) cannot be exercised under jsdom, which implements neither HTMLCanvasElement.toBlob nor video decoding. Its failure path IS tested - a throwing thumbnailer still saves the asset. The success path needs a real WebView2. | 2026-09-10: add the Task 18 credential store to this list. Every test runs against an in-memory CredentialStore, deliberately, so the suite cannot write to the machine that runs it. That means the REAL round trip - Windows Credential Manager, macOS Keychain, Linux Secret Service - has never actually executed. What still needs doing by hand in the running app: add a cloud provider with a key, restart the app, and confirm the key survives and the provider authenticates; then delete it and confirm it is gone from the OS store. Also unverified: the Linux no-Secret-Service path, which needs a box without one. Recorded rather than implied passed. | 2026-09-10 COMPLETE - this row is the LIST ITSELF, and the list is now written in full in docs/superpowers/plans/2026-09-10-model-agnostic-media-platform-evidence.md section 10. Six items, none of which this environment could perform: (1) GPU generation - no GPU here, so no end-to-end generation has EVER run; (2) a real ComfyUI - fixtures transcribed from 0.35.0 source, see D4; (3) the REAL credential store - every test uses the in-memory CredentialStore by design so cargo test cannot write to the machine running it, which means Windows Credential Manager / macOS Keychain / Linux Secret Service have never actually been touched. To close by hand: add a cloud provider with a key, restart the app, confirm it survives and authenticates, then delete it and confirm it is gone from the OS store; (4) the Linux no-Secret-Service path - needs a box without one; (5) the Task 8 canvas thumbnailer, as recorded above; (6) packaged-build CSP verification - needs an installed build. Marking this row Done means the DISCLOSURE is complete, NOT that the six steps were performed. They were not. Evidence row 8 (screenshots) remains Blocked for the same reasons.</t>
         </is>
       </c>
     </row>

--- a/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
+++ b/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
@@ -9201,17 +9201,17 @@
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F9" s="15" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Laptop (vite dev server, no Tauri)</t>
         </is>
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
-          <t>2026-09-10: NOT PRODUCED. Needs a running app and the GPU box. Nothing in this evidence set should be read as visual confirmation.</t>
+          <t>2026-09-10: FIRST VISUAL CONFIRMATION that the media surfaces render at all. The web app was run standalone on the vite dev server and driven in a browser - NOT the packaged Tauri app, so nothing here is a substitute for the real thing. What was seen on screen: (1) Settings &gt; Media - provider list, health badge, Refresh / Check for new providers / Add provider, the model catalogue card, and the 'Open the media library' link; (2) the Add-provider form - Name, Base URL, Adapter select, masked API key, and the credential-store-unavailable warning rendering correctly, because a browser has no Tauri IPC so media_secret_available fails and is caught - the exact Linux/no-Secret-Service path, degrading gracefully; (3) per-provider error isolation - 'Radium Media Worker is offline' shown against that provider only, with its own Retry, which is coupling C4 fixed and visible; (4) the media library route - filters and the 'Nothing here yet' empty state; (5) the Media Studio - the Library link from D17, the prompt composer positioned exactly as D10 decided, 'Generation preview', 'Select a model to begin', and the Providers panel. CONSOLE: 135 errors, every one of them Tauri (invoke/transformCallback undefined) or the refused worker connection. ZERO from media code. STILL NOT PRODUCED and still needing the GPU box: any image or video actually generated, single-provider parity against a real worker, two providers active at once, an unknown-parameter model rendering, and a library populated with real provenance. This row stays PARTIAL for that reason - what exists is proof the surfaces render, not proof the product works. | 2026-09-10 SECOND PASS, with a stub worker: a throwaway HTTP server on 127.0.0.1:13420 served /health and /capabilities from the existing worker-v1-capabilities.json fixture, so the app had real capabilities to render. This produced the single most useful piece of visual evidence in the whole plan - THE SCHEMA-DRIVEN FORM ACTUALLY DRAWING ITSELF. Seen on screen: tabs text_to_video and image_to_video (image_to_video is coupling C3, unreachable before Task 11); Provider, Model and Device (RTX 3090) selects; and the parameter groups the MODEL declares, not the UI - CORE (negative prompt), OUTPUT (Resolution 832x480 / 1280x704), SAMPLING (Steps, Guidance), MOTION (Frames, FPS), a 'Show advanced' disclosure with seed behind it exactly as D10 decided, then the prompt composer and Generate. Provider health read 'Online - v0.6.1'. Not one of those controls is written in the UI: they exist because the model's capabilities declare them, which is the entire point of Task 10. STILL NOT PRODUCED: any actual generation. The stub answers /health and /capabilities only - it never generates, so no image or video has been made, no job has been polled, nothing has been materialised to disk and the library has never held a real asset. This row therefore stays PARTIAL. Proof the surfaces render correctly is not proof the product works end to end; that still needs the GPU box.</t>
         </is>
       </c>
     </row>

--- a/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
+++ b/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
@@ -1093,7 +1093,7 @@
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>Tasks 0-8, 10-13, 16 and 18 Done. Task 9 SKIPPED with reasons (its narrowed scope already exists). Tasks 14, 15 and 17 are PARTIAL, each blocked only on something this machine cannot do. D16 and D18 fixed. Read docs/superpowers/plans/2026-09-10-model-agnostic-media-platform-evidence.md before claiming anything is finished - it names what could NOT be produced rather than implying it passed.</t>
+          <t>Tasks 0-8, 10-16 and 18 Done. Task 9 SKIPPED. Tasks 14, 15, 17 PARTIAL - each blocked only on hardware, another repo, or translators. NEW: TASK 19, a full sync to upstream v2.0.35, added 2026-09-11 when the user answered Q6. There are now NO open decisions. Task 19 is the next piece of work, and T19-S01 says to land PRs #3 and #2 first so the sync happens against a stable main.</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>Nothing is waiting on the agent, and nothing further can be done on this machine. WAITING ON HARDWARE OR ANOTHER REPO: (1) the GPU box - T17-S09 and Evidence row 8, the only outstanding evidence row; (2) a by-hand check that a cloud API key survives a restart, since the OS credential store has only ever run against its in-memory stand-in; (3) the companion PR against atomic-chat-conf for T15-S06; (4) real translators for the 13 non-English locales - PARKED at the user's request 2026-09-10, and every string is already a key so it is a drop-in. WAITING ON THE USER: Q6 sequencing, and the APPDATA folder migration. KNOWN AND UNFIXED: AGENTS.md rule 4 requires cargo clippy but the Makefile has no clippy target, so 53 pre-existing findings sit unenforced. That is the last remaining gap between a stated rule and the actual gate.</t>
+          <t>Task 19 (upstream sync) is next, but land PR #3 then PR #2 into main first. The prerequisite the user set - Media untouched - is MECHANICAL, not a promise: T19-S05 runs make test-selective-v2032 before anything else, and a failure there means a protected file moved in the merge. Do NOT re-baseline the guard to make it pass; that would defeat the only check standing between an upstream merge and the media platform. Still waiting on hardware or another repo: one GPU generation (T17-S09, Evidence 8); the atomic-chat-conf PR (T15-S06); translators for 13 locales. KNOWN AND UNFIXED: the release build degrades src-tauri/icons/icon.png (149710 -&gt; 56994 bytes) by overwriting the master with a generated variant - the same failure c54856d2e was meant to prevent, so that fix does not cover the release path. Never commit that file after a release build.</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2355,6 +2355,55 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Task 19</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>7 - Upstream</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="inlineStr">
+        <is>
+          <t>Full sync to upstream v2.0.35</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="inlineStr"/>
+      <c r="G22" s="14" t="inlineStr">
+        <is>
+          <t>Q6 answered - UNBLOCKED. Land PRs #3 then #2 first.</t>
+        </is>
+      </c>
+      <c r="H22" s="14" t="inlineStr">
+        <is>
+          <t>make test-selective-v2032 green BEFORE anything else, then full make verify</t>
+        </is>
+      </c>
+      <c r="I22" s="13" t="inlineStr"/>
+      <c r="J22" s="14" t="inlineStr">
+        <is>
+          <t>ADDED 2026-09-11 from the user's answer to Q6. Not in the original plan: this supersedes the selective v2.0.32 port. Upstream AtomicBot-ai/Atomic-Chat is on v2.0.35; this fork is on 2.0.23.</t>
+        </is>
+      </c>
+      <c r="K22" s="15" t="inlineStr">
+        <is>
+          <t>Scope measured on 2026-09-11, not estimated: 40 commits, 748 files, +81,458 / -9,707. A trial merge (run and aborted) produced FIFTEEN conflicts, 1-2 hunks each: Makefile, docs/decisions/INDEX.md, src-tauri/Info.plist, agent/ARCHITECTURE.md, agent/tools/web.rs, tests/test-quality-allowlist.json, left-sidebar/index.tsx, constants/localStorage.ts, ChatAgentModeSwitch.tsx, DownloadManegement.tsx, SettingsMenu.tsx, hooks/useModelSources.ts, lib/models.ts, routes/__root.tsx, services/models/localScan.ts. NO MEDIA FILE CONFLICTS and no protected file is touched upstream. Upstream content: inference context fitting and an OOM ladder (ATO-465), model scanning (ATO-458), onboarding rework (ATO-452/453/454/463), telemetry (ATO-456/457/459/468), a downloads panel (ATO-462/467), Linux Vulkan (ATO-464), MLX fixes (ATO-466) and agent-flow work. Nothing media.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A2:K20"/>
   <dataValidations count="1">
@@ -2372,7 +2421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I136"/>
+  <dimension ref="A1:I147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -7928,6 +7977,402 @@
         </is>
       </c>
       <c r="H136" s="6" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="6" t="inlineStr">
+        <is>
+          <t>T19-S01</t>
+        </is>
+      </c>
+      <c r="B137" s="6" t="inlineStr">
+        <is>
+          <t>Task 19</t>
+        </is>
+      </c>
+      <c r="C137" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D137" s="14" t="inlineStr">
+        <is>
+          <t>Land PR #3 then PR #2 into main first</t>
+        </is>
+      </c>
+      <c r="E137" s="13" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F137" s="13" t="inlineStr"/>
+      <c r="G137" s="14" t="inlineStr">
+        <is>
+          <t>The sync then happens against a stable main, and the guard is already protecting media when it does</t>
+        </is>
+      </c>
+      <c r="H137" s="6" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="6" t="inlineStr">
+        <is>
+          <t>T19-S02</t>
+        </is>
+      </c>
+      <c r="B138" s="6" t="inlineStr">
+        <is>
+          <t>Task 19</t>
+        </is>
+      </c>
+      <c r="C138" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D138" s="14" t="inlineStr">
+        <is>
+          <t>Branch chore/upstream-v2.0.35 off main; add the upstream remote if absent</t>
+        </is>
+      </c>
+      <c r="E138" s="13" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F138" s="13" t="inlineStr"/>
+      <c r="G138" s="14" t="inlineStr">
+        <is>
+          <t>git remote add upstream https://github.com/AtomicBot-ai/Atomic-Chat.git</t>
+        </is>
+      </c>
+      <c r="H138" s="6" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="6" t="inlineStr">
+        <is>
+          <t>T19-S03</t>
+        </is>
+      </c>
+      <c r="B139" s="6" t="inlineStr">
+        <is>
+          <t>Task 19</t>
+        </is>
+      </c>
+      <c r="C139" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D139" s="14" t="inlineStr">
+        <is>
+          <t>Merge upstream/main and expect the fifteen known conflicts</t>
+        </is>
+      </c>
+      <c r="E139" s="13" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F139" s="13" t="inlineStr"/>
+      <c r="G139" s="14" t="inlineStr">
+        <is>
+          <t>Anything conflicting OUTSIDE that list of 15 means the ground has moved - stop and re-measure</t>
+        </is>
+      </c>
+      <c r="H139" s="6" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="6" t="inlineStr">
+        <is>
+          <t>T19-S04</t>
+        </is>
+      </c>
+      <c r="B140" s="6" t="inlineStr">
+        <is>
+          <t>Task 19</t>
+        </is>
+      </c>
+      <c r="C140" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D140" s="14" t="inlineStr">
+        <is>
+          <t>Resolve conflicts; take UPSTREAM wholesale for clippy-only Rust churn</t>
+        </is>
+      </c>
+      <c r="E140" s="13" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F140" s="13" t="inlineStr"/>
+      <c r="G140" s="14" t="inlineStr">
+        <is>
+          <t>The 2026-09-10 clippy cleanup touched 17 Rust files in areas upstream rewrote. Do not hand-merge lint noise: take theirs and re-run cargo clippy --fix at S07, which regenerates it in minutes</t>
+        </is>
+      </c>
+      <c r="H140" s="6" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="6" t="inlineStr">
+        <is>
+          <t>T19-S05</t>
+        </is>
+      </c>
+      <c r="B141" s="6" t="inlineStr">
+        <is>
+          <t>Task 19</t>
+        </is>
+      </c>
+      <c r="C141" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D141" s="14" t="inlineStr">
+        <is>
+          <t>FIRST GATE: run make test-selective-v2032 before anything else</t>
+        </is>
+      </c>
+      <c r="E141" s="13" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F141" s="13" t="inlineStr"/>
+      <c r="G141" s="14" t="inlineStr">
+        <is>
+          <t>Must print "Selective v2.0.32 boundaries verified". THIS IS THE PREREQUISITE MADE MECHANICAL - if it fails, a protected media file moved in the merge. STOP and investigate; do not re-baseline to make it pass</t>
+        </is>
+      </c>
+      <c r="H141" s="6" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="6" t="inlineStr">
+        <is>
+          <t>T19-S06</t>
+        </is>
+      </c>
+      <c r="B142" s="6" t="inlineStr">
+        <is>
+          <t>Task 19</t>
+        </is>
+      </c>
+      <c r="C142" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D142" s="14" t="inlineStr">
+        <is>
+          <t>Run the full make verify</t>
+        </is>
+      </c>
+      <c r="E142" s="13" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F142" s="13" t="inlineStr"/>
+      <c r="G142" s="14" t="inlineStr">
+        <is>
+          <t>EXITCODE 0, read from the command own exit code. Now includes clippy-rust</t>
+        </is>
+      </c>
+      <c r="H142" s="6" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="6" t="inlineStr">
+        <is>
+          <t>T19-S07</t>
+        </is>
+      </c>
+      <c r="B143" s="6" t="inlineStr">
+        <is>
+          <t>Task 19</t>
+        </is>
+      </c>
+      <c r="C143" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D143" s="14" t="inlineStr">
+        <is>
+          <t>Re-run cargo clippy --fix and clear anything upstream introduced</t>
+        </is>
+      </c>
+      <c r="E143" s="13" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F143" s="13" t="inlineStr"/>
+      <c r="G143" s="14" t="inlineStr">
+        <is>
+          <t>Re-applies the S04 churn cheaply and catches new findings in 81k added lines</t>
+        </is>
+      </c>
+      <c r="H143" s="6" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="6" t="inlineStr">
+        <is>
+          <t>T19-S08</t>
+        </is>
+      </c>
+      <c r="B144" s="6" t="inlineStr">
+        <is>
+          <t>Task 19</t>
+        </is>
+      </c>
+      <c r="C144" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D144" s="14" t="inlineStr">
+        <is>
+          <t>Run the media suites and the opt-in credential hardware test</t>
+        </is>
+      </c>
+      <c r="E144" s="13" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F144" s="13" t="inlineStr"/>
+      <c r="G144" s="14" t="inlineStr">
+        <is>
+          <t>Media suites must be unchanged. Then the --ignored os_credential_store_round_trip against the real store</t>
+        </is>
+      </c>
+      <c r="H144" s="6" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="6" t="inlineStr">
+        <is>
+          <t>T19-S09</t>
+        </is>
+      </c>
+      <c r="B145" s="6" t="inlineStr">
+        <is>
+          <t>Task 19</t>
+        </is>
+      </c>
+      <c r="C145" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="D145" s="14" t="inlineStr">
+        <is>
+          <t>Smoke the built app, concentrating on INFERENCE not media</t>
+        </is>
+      </c>
+      <c r="E145" s="13" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F145" s="13" t="inlineStr"/>
+      <c r="G145" s="14" t="inlineStr">
+        <is>
+          <t>ATO-465 reworked context fitting, KV-cache estimation and OOM retry. That is the real behavioural risk of this merge - load a model and check context handling</t>
+        </is>
+      </c>
+      <c r="H145" s="6" t="inlineStr">
+        <is>
+          <t>Laptop + a model</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="6" t="inlineStr">
+        <is>
+          <t>T19-S10</t>
+        </is>
+      </c>
+      <c r="B146" s="6" t="inlineStr">
+        <is>
+          <t>Task 19</t>
+        </is>
+      </c>
+      <c r="C146" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D146" s="14" t="inlineStr">
+        <is>
+          <t>Bump the app version to 2.0.35</t>
+        </is>
+      </c>
+      <c r="E146" s="13" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F146" s="13" t="inlineStr"/>
+      <c r="G146" s="14" t="inlineStr">
+        <is>
+          <t>Otherwise the in-app updater keeps reporting an update that has already been taken</t>
+        </is>
+      </c>
+      <c r="H146" s="6" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="6" t="inlineStr">
+        <is>
+          <t>T19-S11</t>
+        </is>
+      </c>
+      <c r="B147" s="6" t="inlineStr">
+        <is>
+          <t>Task 19</t>
+        </is>
+      </c>
+      <c r="C147" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="D147" s="14" t="inlineStr">
+        <is>
+          <t>Commit and open the PR</t>
+        </is>
+      </c>
+      <c r="E147" s="13" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="F147" s="13" t="inlineStr"/>
+      <c r="G147" s="14" t="inlineStr">
+        <is>
+          <t>chore: sync with upstream v2.0.35</t>
+        </is>
+      </c>
+      <c r="H147" s="6" t="inlineStr">
         <is>
           <t>Laptop</t>
         </is>
@@ -8205,10 +8650,14 @@
           <t>Finish and land the selective work first, then branch this platform off the result. GGUF filtering is mid-flight in the tree right now.</t>
         </is>
       </c>
-      <c r="E7" s="15" t="n"/>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>ANSWERED BY THE USER 2026-09-11: FULL SYNC to upstream v2.0.35. The selective v2.0.32 port is SUPERSEDED - its remaining Tasks 5-13 are moot, because a full merge brings all of v2.0.32 plus ten further releases. He set one prerequisite: none of our work is lost and Media is left alone. MEASURED, NOT ASSUMED, on 2026-09-11 with a throwaway trial merge that was aborted afterwards: upstream is 40 commits and 748 files ahead (+81,458 / -9,707) from v2.0.23 to v2.0.35. It touches ZERO of the nine protected files and ZERO media files. A real merge produces only FIFTEEN conflicts, one or two hunks each, and NONE of them is a media file. The prerequisite is therefore verifiable rather than a promise: make test-selective-v2032 is the mechanical proof, and it must be run BEFORE anything else after the merge. The guard was built for exactly this moment - 'an upstream merge cannot silently redesign Media' - so this is the scenario it exists to police. THE REAL RISK IS NOT MEDIA. Upstream reworked inference context handling (ATO-465: context fitting, KV-cache estimation, an OOM retry ladder), model scanning (ATO-458) and onboarding. Those can change how models behave on this machine. That is what deserves scrutiny after the merge.</t>
+        </is>
+      </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Answered</t>
         </is>
       </c>
       <c r="G7" s="13" t="n"/>

--- a/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
+++ b/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
@@ -8003,7 +8003,7 @@
       </c>
       <c r="E137" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F137" s="13" t="inlineStr"/>
@@ -8017,6 +8017,11 @@
           <t>Laptop</t>
         </is>
       </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>PR #3 then PR #2 landed into main before branching.</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
@@ -8039,7 +8044,7 @@
       </c>
       <c r="E138" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F138" s="13" t="inlineStr"/>
@@ -8053,6 +8058,11 @@
           <t>Laptop</t>
         </is>
       </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Branched off main; upstream remote already present.</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="6" t="inlineStr">
@@ -8075,7 +8085,7 @@
       </c>
       <c r="E139" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F139" s="13" t="inlineStr"/>
@@ -8089,6 +8099,11 @@
           <t>Laptop</t>
         </is>
       </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Merged upstream/main @64758ea - v2.0.35 plus the 12 commits after the tag. 751 files changed.</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
@@ -8111,7 +8126,7 @@
       </c>
       <c r="E140" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F140" s="13" t="inlineStr"/>
@@ -8125,6 +8140,11 @@
           <t>Laptop</t>
         </is>
       </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>81 files needed a hand resolution. Judgement calls: SettingsMenu keeps Media and drops our MCP entry (upstream moved MCP to Connectors); models.ts restores mmproj into upstream new anchored regex; i18n/context.ts honours defaultValue; NavMain gains the standalone Media item.</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="6" t="inlineStr">
@@ -8147,7 +8167,7 @@
       </c>
       <c r="E141" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F141" s="13" t="inlineStr"/>
@@ -8161,6 +8181,11 @@
           <t>Laptop</t>
         </is>
       </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>PREREQUISITE HELD. "Selective v2.0.32 boundaries verified". Every Radium Media file is byte-identical to main; the two changed "media" paths are upstream own GAIA agent media tools, not ours.</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="6" t="inlineStr">
@@ -8183,7 +8208,7 @@
       </c>
       <c r="E142" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F142" s="13" t="inlineStr"/>
@@ -8197,6 +8222,11 @@
           <t>Laptop</t>
         </is>
       </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>verify-fast exit 0; clippy-rust exit 0; 823 Rust tests + plugins pass; selective guard passes; 3358 web tests pass (291 files, 0 failed).</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="6" t="inlineStr">
@@ -8219,7 +8249,7 @@
       </c>
       <c r="E143" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F143" s="13" t="inlineStr"/>
@@ -8233,6 +8263,11 @@
           <t>Laptop</t>
         </is>
       </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>cargo clippy --fix applied nothing (duplicate lib/lib-test suggestions block it), so the 18 findings were cleared by hand. 15 mechanical; the rest were dead-on-Windows-only code (sanitize_std_command, PTY test helpers) gated at their real cfg condition rather than deleted.</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="6" t="inlineStr">
@@ -8255,7 +8290,7 @@
       </c>
       <c r="E144" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F144" s="13" t="inlineStr"/>
@@ -8269,6 +8304,11 @@
           <t>Laptop</t>
         </is>
       </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Media suites unchanged and green inside the full web run. The --ignored os_credential_store_round_trip passes against the real Windows Credential Manager after the merge.</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="6" t="inlineStr">
@@ -8291,7 +8331,7 @@
       </c>
       <c r="E145" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="F145" s="13" t="inlineStr"/>
@@ -8305,6 +8345,11 @@
           <t>Laptop + a model</t>
         </is>
       </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>NOT DONE - needs a model on disk, which this machine does not have. ATO-465 reworked context fitting, KV-cache estimation and OOM retry, so this remains the one unverified behavioural risk of the sync. Must be smoked before any release build.</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="6" t="inlineStr">
@@ -8327,7 +8372,7 @@
       </c>
       <c r="E146" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F146" s="13" t="inlineStr"/>
@@ -8341,6 +8386,11 @@
           <t>Laptop</t>
         </is>
       </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>No bump needed: the merge brought package/tauri.conf/web-app to 2.0.35 and Cargo to 0.6.599, matching upstream exactly.</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="6" t="inlineStr">
@@ -8363,7 +8413,7 @@
       </c>
       <c r="E147" s="13" t="inlineStr">
         <is>
-          <t>Not started</t>
+          <t>In progress</t>
         </is>
       </c>
       <c r="F147" s="13" t="inlineStr"/>
@@ -8375,6 +8425,11 @@
       <c r="H147" s="6" t="inlineStr">
         <is>
           <t>Laptop</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Merge committed as a true two-parent merge commit. PR still to open.</t>
         </is>
       </c>
     </row>
@@ -8395,7 +8450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9325,6 +9380,80 @@
       <c r="G25" t="inlineStr">
         <is>
           <t>2026-09-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>D19</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>TEST-ENVIRONMENT DEFECT exposed by the v2.0.35 sync, fixed in web-app/src/test/setup.ts. jsdom supplies AbortSignal, but the fetch it installs is undici's, and undici brand-checks the signal against the AbortSignal class it captured BEFORE jsdom replaced the global. The two are different class objects, so every real fetch(url, {signal}) in the app died under vitest on "Expected signal to be an instance of AbortSignal".</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Two upstream DropdownModelProvider tests. The provider registry seeds from a bundled baseline that does NOT contain openai, so it depends on its network refresh to learn that openai is a catalogue provider. With the fetch dead, the refresh fell back to baseline, openai looked like a custom provider, and the picker showed a section for a cloud provider the user had never connected.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Translate rather than brand-check: run the fetch without the signal and race it against the signal's own abort event, so callers still see an AbortError at the right moment. Node's original classes are genuinely unreachable from inside the test realm - deleting the jsdom globals leaves undefined, and the classes reached via Request are jsdom's too. The honest cost is that the underlying request is no longer cancelled at the socket, which costs a test suite nothing.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>DONE 2026-09-11 as part of the sync. NOTE THE RESIDUAL RISK, which is upstream's design and not introduced here: those two tests now pass only when raw.githubusercontent.com is reachable, because that is where the registry learns about openai. They will fail offline. Worth raising upstream rather than working around locally.</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Answered</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>D20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>UPSTREAM TEST NOT PORTABLE TO WINDOWS, found by the v2.0.35 sync. process_tools_reject_unknown_ids_and_bad_signals spawns a real `sleep` through the agent PTY. Windows has no path for that spawn and no `sleep` program, so the test cannot pass here. Every sibling test in the file that spawns a process is already #[cfg(unix)]; this one was missed, probably because it is mostly error-path assertions with one spawn at the end.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>make verify on Windows. It was the last red test after the merge.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Split rather than gate wholesale. The unknown-id and bad-argument rejection assertions are portable and valuable, so they stay ungated and keep running on Windows; only the half that needs a process that really starts moves into a new #[cfg(unix)] test. proc_id_of is gated with it, since only spawning tests use it.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>DONE 2026-09-11. Costs a small divergence from upstream in their test file, which is merge debt to carry; the alternative was losing Windows coverage of the rejection paths entirely. Worth offering upstream as a patch.</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Answered</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>

--- a/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
+++ b/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
@@ -8413,7 +8413,7 @@
       </c>
       <c r="E147" s="13" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F147" s="13" t="inlineStr"/>
@@ -8429,7 +8429,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Merge committed as a true two-parent merge commit. PR still to open.</t>
+          <t>Merge committed as a true two-parent merge commit (c81c4ea9). PR #4 opened against walladanger/Atomic-Chat main.</t>
         </is>
       </c>
     </row>

--- a/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
+++ b/docs/superpowers/plans/2026-09-08-model-agnostic-atomic-media-platform-tracker.xlsx
@@ -1300,7 +1300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2404,6 +2404,53 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Task 20</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>8 - Independence</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Stop depending on upstream infrastructure</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Nothing blocks the first step - the updater is already done and merged into this branch.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>make test-hardening-contracts green (tests/no-auto-update.test.mjs), then each endpoint repointed or removed with its own guard</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>ADDED 2026-09-12 at the user's instruction: "NEVER auto update. If possible, take the feature offline", plus "go to the source... monitor the GitHub directly rather than using Atomic Chat's downloads". Prompted by the in-app update prompt, which was NOT a Radium update.</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>THE FINDING THAT STARTED IT: the Tauri updater endpoint was AtomicBot-ai/Atomic-Chat/releases - UPSTREAM's repo. Accepting an in-app update did not update Radium, it installed Atomic Chat over it, removing the media platform from the user's machine. Step 1 is DONE (see ADR 2026-09-12-radium-never-auto-updates.md). MEASURED, not assumed: 25 AtomicBot-ai endpoints remain across backend manifest, provider registry, media registry, model catalog, staff picks, recommended models and TurboQuant releases. IMPORTANT NUANCE ON 'go to the source', established by checking rather than reasoning: the atomic-chat-conf release assets are NOT byte-identical mirrors of ggml-org. Same tag, same 52 files, different bytes and different sha256 (35,079,269 vs 35,221,385 for win-vulkan-x64 at b10809). The difference is Authenticode: llama-server.exe is 'Valid, CN=AtomicMail Systems OU, Tallinn, EE' from the mirror and 'NotSigned' from ggml-org. So switching the BINARIES to source LOSES code signing and gains upstream-published sha256 (which GitHub does expose per asset via the API). That trade needs a signing certificate to win, so the binaries are the LAST thing to move, not the first. The manifests and registries - which are just JSON and carry no signature - are the cheap wins. Licence checked: Apache 2.0, so none of this is a licensing problem; the user's 'feels like stealing' worry is unfounded, and the mirror is a cost they carry, not one we impose (GitHub serves public-repo release bandwidth free).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A2:K20"/>
   <dataValidations count="1">
@@ -2421,7 +2468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I147"/>
+  <dimension ref="A1:I152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -8430,6 +8477,206 @@
       <c r="I147" t="inlineStr">
         <is>
           <t>Merge committed as a true two-parent merge commit (c81c4ea9). PR #4 opened against walladanger/Atomic-Chat main.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>T20-S01</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Task 20</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>1</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Remove the auto-updater entirely rather than repointing it</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>make test-hardening-contracts must stay green</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>DONE 2026-09-12 on branch feat/disable-auto-update. Removed the plugins.updater endpoint, the tauri-plugin-updater dependency and registration, the updater:* capabilities, the whole src-tauri/src/core/updater module, both desktop-only IPC commands, the Tauri updater service and the periodic check in DataProvider. AUTO_UPDATER_DISABLED is hardcoded in vite.config.ts, not read from env, so no build can re-enable it. useReleaseNotes deleted too - it fetched upstream's releases API and had no callers. The updater() seam stays bound to the existing no-op DefaultUpdaterService so callers still compile; the desktop service-hub test now pins that. New guard tests/no-auto-update.test.mjs locks all six properties. Verified: verify-fast exit 0, 816 Rust tests, selective guard intact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>T20-S02</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Task 20</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>2</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Fork atomic-chat-conf and repoint the JSON manifests</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Each repointed URL needs a test asserting the new host, so a silent revert fails</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>The cheap, high-value half: backends/manifest.json, backends/turboquant-manifest.json, providers/registry.json, media/registry.json, models/recommended.json, models/staff-picks.json. Plain JSON, no signatures involved, so forking costs nothing but a repo. Doing this also removes upstream control over WHICH provider and media entries the app offers - today a commit in their repo changes what Radium users see.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>T20-S03</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Task 20</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>3</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Decide the binary question: keep the signed mirror, or go to ggml-org unsigned</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Needs a decision record before any change; do not switch silently</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>THE REAL TRADE, and the reason this is its own step. Mirror = code-signed by AtomicMail Systems, hash-verified from their manifest, but rebuilt bytes we cannot check against upstream. Source = upstream bytes with a GitHub-published sha256, but unsigned, so SmartScreen and Defender treat them worse. Going to source is only clearly better once Radium has its own signing certificate. Recommend: keep the mirror until then, and revisit with S04.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>T20-S04</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Task 20</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>4</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Verify downloads against upstream digests wherever they are not signed</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>A download with no hash and no signature should fail, not warn</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Independent of S03 and worth doing either way. Two paths currently download UNVERIFIED: any backend whose tag is not mirrored (resolveBackendArchiveSource logs 'not mirrored... using the upstream CDN' and proceeds with no hash), and the cudart companion, which the code comments confirm is never mirrored - roughly 150MB of NVIDIA runtime DLLs from a third-party GitHub release with nothing checking them. GitHub's API exposes a sha256 digest per release asset, so these CAN be verified; nothing reads it today.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>T20-S05</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Task 20</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>5</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Decide what replaces the update channel, if anything</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Only if the user wants one - manual install is a valid permanent answer</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Radium currently has no way to tell a user a new build exists. That is the accepted cost of S01. Options: leave it manual; publish releases on walladanger/Atomic-Chat and point a NEW updater there; or a check that only notifies and never installs. Requires a signing key to be worth much. Supersede the S01 decision record rather than quietly reversing it.</t>
         </is>
       </c>
     </row>
@@ -8450,7 +8697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9454,6 +9701,80 @@
       <c r="G27" t="inlineStr">
         <is>
           <t>2026-09-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>D21</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>AUTO-UPDATE POINTED AT THE WRONG PROJECT. tauri.conf.json's updater endpoint was https://github.com/AtomicBot-ai/Atomic-Chat/releases/latest/download/latest.json - upstream's repository. Radium is a FORK, so 'update' did not mean a newer Radium: it meant installing Atomic Chat over the top, removing the media platform and every other fork change from the user's machine. The prompt was live in the shipped app; the user asked about it, which is the only reason it was found.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Everything. A single click by any user undoes the entire project on that machine. The v2.0.35 sync silences the prompt only until upstream tags 2.0.36.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Remove rather than repoint. A fork with no release channel has nothing to point at, and a dormant endpoint is one config edit from shipping the bug again. Take out the plugin, the endpoint, the capabilities, the Rust module, the IPC commands, the frontend service and the periodic check; hardcode AUTO_UPDATER_DISABLED so no build can undo it; add a guard test so re-adding one fails the build.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>ANSWERED BY THE USER 2026-09-12: 'add NEVER auto update. If possible, take the feature offline.' Done the same day on feat/disable-auto-update. ADR 2026-09-12-radium-never-auto-updates.md; guard tests/no-auto-update.test.mjs wired into make test-hardening-contracts. ACCEPTED COST, stated plainly: Radium now has no way to tell a user a build exists, and updates are manual. Tracked as Task 20 S05 rather than left implicit.</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Answered</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>D22</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>SHOULD RADIUM DOWNLOAD FROM THE SOURCE (ggml-org) INSTEAD OF ATOMIC CHAT'S MIRROR? Asked by the user, partly on an ethical worry - 'it almost feels like I'm stealing' - and partly for independence.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>25 runtime endpoints: backend manifests, provider registry, media registry, model catalog, staff picks, recommended models, TurboQuant releases.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Separate the ethics from the engineering, and check rather than reason. ETHICS: the licence is Apache 2.0, which permits this outright, and GitHub serves public-repo release bandwidth free, so the mirror costs AtomicBot-ai nothing per download. Nothing is being taken. ENGINEERING: split the JSON manifests (cheap, do it) from the binaries (expensive, do it last).</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>MEASURED 2026-09-12, and the result inverts the intuition. The atomic-chat-conf assets are NOT byte-identical mirrors: same tag and same 52 files, but 35,079,269 vs 35,221,385 bytes and different sha256 for win-vulkan-x64 at b10809. The difference is code signing - llama-server.exe reports 'Valid, CN=AtomicMail Systems OU, Tallinn, EE' from the mirror and 'NotSigned' from ggml-org. So 'going to the source' LOSES Authenticode and gains an upstream-published sha256 (GitHub exposes a digest per asset; nothing in this codebase reads it). The mirror is a service AtomicBot-ai pays for, not a cost imposed on them. RECOMMENDATION, for the user to accept or reject: repoint the JSON now (Task 20 S02), keep the signed binaries until Radium has its own certificate (S03), and add digest verification to the paths that today download with NO hash and NO signature at all - unmirrored backend tags and the ~150MB cudart companion (S04).</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Recommendation - awaiting the user</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
